--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -1,41 +1,908 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7547AC-67E1-4856-8D15-30D70D3C528D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="5055" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="ranking" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="292">
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Victories</t>
+  </si>
+  <si>
+    <t>Streak</t>
+  </si>
+  <si>
+    <t>Loses</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>Majors</t>
+  </si>
+  <si>
+    <t>Prestige</t>
+  </si>
+  <si>
+    <t>Tournaments Trophies</t>
+  </si>
+  <si>
+    <t>Tier</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>BonusType</t>
+  </si>
+  <si>
+    <t>BonusRemaining</t>
+  </si>
+  <si>
+    <t>LastUpdated</t>
+  </si>
+  <si>
+    <t>The MongolZ</t>
+  </si>
+  <si>
+    <t>Tier 2</t>
+  </si>
+  <si>
+    <t>AS/SIS/ESEA</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:37:50.179Z</t>
+  </si>
+  <si>
+    <t>Iluminar</t>
+  </si>
+  <si>
+    <t>Tier 3</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:37:58.230Z</t>
+  </si>
+  <si>
+    <t>Liquid</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:37:26.757Z</t>
+  </si>
+  <si>
+    <t>Titan</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:37:39.250Z</t>
+  </si>
+  <si>
+    <t>Nemiga</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:38:23.828Z</t>
+  </si>
+  <si>
+    <t>Eternal Fire</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>Elevate</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:38:40.257Z</t>
+  </si>
+  <si>
+    <t>PARIVISION</t>
+  </si>
+  <si>
+    <t>Vitality</t>
+  </si>
+  <si>
+    <t>Natus Vincere</t>
+  </si>
+  <si>
+    <t>Heroic</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:38:48.174Z</t>
+  </si>
+  <si>
+    <t>Copenhagen Flames</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:38:31.762Z</t>
+  </si>
+  <si>
+    <t>Verdant</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:29:24.671Z</t>
+  </si>
+  <si>
+    <t>Falcons</t>
+  </si>
+  <si>
+    <t>Spirit</t>
+  </si>
+  <si>
+    <t>Cloud9</t>
+  </si>
+  <si>
+    <t>Onyx Ravens</t>
+  </si>
+  <si>
+    <t>Bounty Hunters</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:28:59.888Z</t>
+  </si>
+  <si>
+    <t>The Huns</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:21:06.168Z</t>
+  </si>
+  <si>
+    <t>TYLOO</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:09:16.526Z</t>
+  </si>
+  <si>
+    <t>OG</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:09:03.691Z</t>
+  </si>
+  <si>
+    <t>BESTIA</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:29:16.752Z</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:28:17.433Z</t>
+  </si>
+  <si>
+    <t>hoorai</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:28:25.661Z</t>
+  </si>
+  <si>
+    <t>00 Nation</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>100 Thieves</t>
+  </si>
+  <si>
+    <t>Aether</t>
+  </si>
+  <si>
+    <t>AMKAL</t>
+  </si>
+  <si>
+    <t>Astana Dragons</t>
+  </si>
+  <si>
+    <t>Astralis Talent</t>
+  </si>
+  <si>
+    <t>Avangar</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>BIG Academy</t>
+  </si>
+  <si>
+    <t>Bravado</t>
+  </si>
+  <si>
+    <t>Copenhagen Wolves</t>
+  </si>
+  <si>
+    <t>Counter Logic Games</t>
+  </si>
+  <si>
+    <t>ENCE Academy</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>Flash</t>
+  </si>
+  <si>
+    <t>FLuffy Gangsters</t>
+  </si>
+  <si>
+    <t>FlyQuest RED</t>
+  </si>
+  <si>
+    <t>Fnatic</t>
+  </si>
+  <si>
+    <t>FORZE</t>
+  </si>
+  <si>
+    <t>Gambit</t>
+  </si>
+  <si>
+    <t>GATERON</t>
+  </si>
+  <si>
+    <t>GhoulsW</t>
+  </si>
+  <si>
+    <t>HAVU</t>
+  </si>
+  <si>
+    <t>Heroic Academy</t>
+  </si>
+  <si>
+    <t>Hesta</t>
+  </si>
+  <si>
+    <t>Immortals</t>
+  </si>
+  <si>
+    <t>Into the Beach</t>
+  </si>
+  <si>
+    <t>Kinguin</t>
+  </si>
+  <si>
+    <t>kONO</t>
+  </si>
+  <si>
+    <t>MAD Lions</t>
+  </si>
+  <si>
+    <t>MANA</t>
+  </si>
+  <si>
+    <t>MIBR Academy</t>
+  </si>
+  <si>
+    <t>Misfits</t>
+  </si>
+  <si>
+    <t>mousesports</t>
+  </si>
+  <si>
+    <t>MOUZ NXT</t>
+  </si>
+  <si>
+    <t>Movistar KOI</t>
+  </si>
+  <si>
+    <t>NIP Impact</t>
+  </si>
+  <si>
+    <t>Nordix</t>
+  </si>
+  <si>
+    <t>NOVAQ</t>
+  </si>
+  <si>
+    <t>paiN Academy</t>
+  </si>
+  <si>
+    <t>QMISTRY</t>
+  </si>
+  <si>
+    <t>Quantum Bellator Fire</t>
+  </si>
+  <si>
+    <t>Rogue</t>
+  </si>
+  <si>
+    <t>Shika</t>
+  </si>
+  <si>
+    <t>SKYFURY</t>
+  </si>
+  <si>
+    <t>Space Soldiers</t>
+  </si>
+  <si>
+    <t>Sprout</t>
+  </si>
+  <si>
+    <t>Tsunami</t>
+  </si>
+  <si>
+    <t>VeryGames</t>
+  </si>
+  <si>
+    <t>Vox Eminor</t>
+  </si>
+  <si>
+    <t>Wildcard Academy</t>
+  </si>
+  <si>
+    <t>Spirit Academy</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:49:35.870Z</t>
+  </si>
+  <si>
+    <t>True Rippers</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:47:38.886Z</t>
+  </si>
+  <si>
+    <t>FaZe</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:36:39.932Z</t>
+  </si>
+  <si>
+    <t>iBUYPOWER</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:36:34.302Z</t>
+  </si>
+  <si>
+    <t>GODSENT</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:39:32.364Z</t>
+  </si>
+  <si>
+    <t>M80</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:45:45.455Z</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:08:18.806Z</t>
+  </si>
+  <si>
+    <t>Orbit</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:08:33.993Z</t>
+  </si>
+  <si>
+    <t>Alliance</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:51:22.336Z</t>
+  </si>
+  <si>
+    <t>Homyno</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:51:16.607Z</t>
+  </si>
+  <si>
+    <t>MenaceGG</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:49:44.165Z</t>
+  </si>
+  <si>
+    <t>Solid</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:47:50.233Z</t>
+  </si>
+  <si>
+    <t>ENCE</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:34:19.604Z</t>
+  </si>
+  <si>
+    <t>Nexus</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:34:13.227Z</t>
+  </si>
+  <si>
+    <t>MIBR</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:39:50.018Z</t>
+  </si>
+  <si>
+    <t>Wizards</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:45:38.841Z</t>
+  </si>
+  <si>
+    <t>RED Canids</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:08:44.661Z</t>
+  </si>
+  <si>
+    <t>Rebels</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:28:39.554Z</t>
+  </si>
+  <si>
+    <t>FURIA</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:08:26.017Z</t>
+  </si>
+  <si>
+    <t>ad hoc</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:50:09.060Z</t>
+  </si>
+  <si>
+    <t>SAW</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:49:47.596Z</t>
+  </si>
+  <si>
+    <t>NomadS</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:49:35.489Z</t>
+  </si>
+  <si>
+    <t>Outsiders</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:49:27.811Z</t>
+  </si>
+  <si>
+    <t>Red Viperz</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:49:20.687Z</t>
+  </si>
+  <si>
+    <t>The Dice</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:49:12.765Z</t>
+  </si>
+  <si>
+    <t>Victores Sumus</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:49:00.243Z</t>
+  </si>
+  <si>
+    <t>ODDIK</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:48:52.026Z</t>
+  </si>
+  <si>
+    <t>Qiang</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:48:45.055Z</t>
+  </si>
+  <si>
+    <t>inSanitY</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:48:38.129Z</t>
+  </si>
+  <si>
+    <t>Sangal</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:48:28.102Z</t>
+  </si>
+  <si>
+    <t>9Pandas</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:48:17.012Z</t>
+  </si>
+  <si>
+    <t>Gods Reign</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:48:09.473Z</t>
+  </si>
+  <si>
+    <t>CatEvil</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:48:02.110Z</t>
+  </si>
+  <si>
+    <t>Carnival</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:47:49.161Z</t>
+  </si>
+  <si>
+    <t>Evil Geniuses</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:47:36.482Z</t>
+  </si>
+  <si>
+    <t>Vantage</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:47:28.286Z</t>
+  </si>
+  <si>
+    <t>ATOX</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:47:18.470Z</t>
+  </si>
+  <si>
+    <t>Skinvault</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:47:11.265Z</t>
+  </si>
+  <si>
+    <t>BC.Game</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:46:52.846Z</t>
+  </si>
+  <si>
+    <t>Wings Up</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:46:32.115Z</t>
+  </si>
+  <si>
+    <t>Lynn Vision</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:46:08.336Z</t>
+  </si>
+  <si>
+    <t>Tricked</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:45:42.234Z</t>
+  </si>
+  <si>
+    <t>3DMAX</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:39:02.710Z</t>
+  </si>
+  <si>
+    <t>Venom</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:38:39.010Z</t>
+  </si>
+  <si>
+    <t>ARCRED</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:38:03.598Z</t>
+  </si>
+  <si>
+    <t>GamerLegion</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:37:47.172Z</t>
+  </si>
+  <si>
+    <t>Passion UA</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:37:27.234Z</t>
+  </si>
+  <si>
+    <t>FlyQuest</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:37:20.280Z</t>
+  </si>
+  <si>
+    <t>Envy</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:37:05.560Z</t>
+  </si>
+  <si>
+    <t>BIG</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:36:43.463Z</t>
+  </si>
+  <si>
+    <t>Limitless</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:36:26.343Z</t>
+  </si>
+  <si>
+    <t>Galorys</t>
+  </si>
+  <si>
+    <t>2026-02-19T00:36:18.696Z</t>
+  </si>
+  <si>
+    <t>devils.one</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:23:30.347Z</t>
+  </si>
+  <si>
+    <t>Luminosity</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:23:18.851Z</t>
+  </si>
+  <si>
+    <t>Sharks</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:23:12.952Z</t>
+  </si>
+  <si>
+    <t>IHC</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:23:06.529Z</t>
+  </si>
+  <si>
+    <t>Kappa Bar</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:22:57.244Z</t>
+  </si>
+  <si>
+    <t>Complexity</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:22:48.652Z</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:22:39.402Z</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:22:32.047Z</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:22:20.745Z</t>
+  </si>
+  <si>
+    <t>KRU</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:22:06.663Z</t>
+  </si>
+  <si>
+    <t>Imperial</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:21:57.658Z</t>
+  </si>
+  <si>
+    <t>9z</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:21:44.273Z</t>
+  </si>
+  <si>
+    <t>paiN</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:21:14.058Z</t>
+  </si>
+  <si>
+    <t>Vexed</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:19:58.722Z</t>
+  </si>
+  <si>
+    <t>Dignitas</t>
+  </si>
+  <si>
+    <t>2026-02-19T21:54:17.535Z</t>
+  </si>
+  <si>
+    <t>LDLC</t>
+  </si>
+  <si>
+    <t>2026-02-19T21:53:53.691Z</t>
+  </si>
+  <si>
+    <t>Aravt</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:51:09.872Z</t>
+  </si>
+  <si>
+    <t>VP.Prodigy</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:51:03.784Z</t>
+  </si>
+  <si>
+    <t>Entropiq</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:49:25.044Z</t>
+  </si>
+  <si>
+    <t>Take Flyte</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:49:14.876Z</t>
+  </si>
+  <si>
+    <t>Underground</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:47:27.422Z</t>
+  </si>
+  <si>
+    <t>Virtus.pro</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:47:19.575Z</t>
+  </si>
+  <si>
+    <t>ShindeN</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:36:26.535Z</t>
+  </si>
+  <si>
+    <t>Permitta</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:36:17.329Z</t>
+  </si>
+  <si>
+    <t>Wildcard</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:34:08.116Z</t>
+  </si>
+  <si>
+    <t>Astralis</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:34:01.822Z</t>
+  </si>
+  <si>
+    <t>Bad News Eagles</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:45:27.335Z</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:39:18.535Z</t>
+  </si>
+  <si>
+    <t>ECSTATIC</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:39:12.540Z</t>
+  </si>
+  <si>
+    <t>TALON</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:27:14.538Z</t>
+  </si>
+  <si>
+    <t>NAVI Junior</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:27:03.939Z</t>
+  </si>
+  <si>
+    <t>Ninjas in Pyjamas</t>
+  </si>
+  <si>
+    <t>2026-02-19T21:53:46.615Z</t>
+  </si>
+  <si>
+    <t>MOUZ</t>
+  </si>
+  <si>
+    <t>2026-02-19T21:53:40.004Z</t>
+  </si>
+  <si>
+    <t>Aurora</t>
+  </si>
+  <si>
+    <t>2026-02-19T21:53:30.387Z</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>2026-02-19T21:53:23.315Z</t>
+  </si>
+  <si>
+    <t>Legacy</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:45:20.251Z</t>
+  </si>
+  <si>
+    <t>4 star</t>
+  </si>
+  <si>
+    <t>3 star</t>
+  </si>
+  <si>
+    <t>2 star</t>
+  </si>
+  <si>
+    <t>1 star</t>
+  </si>
+  <si>
+    <t>LGB</t>
+  </si>
+  <si>
+    <t>Chinggis Warriors</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +932,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,65 +1271,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M165"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q165"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Team</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Victories</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Streak</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Loses</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Points</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Majors</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Prestige</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Tournaments Trophies</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Tier</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Region</v>
-      </c>
-      <c r="K1" t="str">
-        <v>BonusType</v>
-      </c>
-      <c r="L1" t="str">
-        <v>BonusRemaining</v>
-      </c>
-      <c r="M1" t="str">
-        <v>LastUpdated</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Eternal Fire</v>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>286</v>
+      </c>
+      <c r="O1" t="s">
+        <v>287</v>
+      </c>
+      <c r="P1" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1089.987813233851</v>
+        <v>1103.5396883405394</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -465,570 +1356,570 @@
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J2" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K2" t="str">
-        <v>none</v>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2" t="str">
-        <v>2026-02-28T06:34:18.462Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>The MongolZ</v>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1094.2205166212659</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1093.7510210031935</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1090.4930427442032</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1088.1168262682929</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="D3">
+      <c r="E7">
+        <v>1073.614299461236</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>1072.1962700599079</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1063.3157624288613</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1062.7199050958704</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1062.0404218180502</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1060.4876942715719</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>1056.483574632495</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>1038.7190184710753</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>1088.1486255810032</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J3" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K3" t="str">
-        <v>none</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3" t="str">
-        <v>2026-02-28T06:35:10.120Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>1079.0636882193733</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J4" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K4" t="str">
-        <v>none</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2026-02-28T06:34:47.163Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PARIVISION</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1079.034808827365</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J5" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K5" t="str">
-        <v>none</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" t="str">
-        <v>2026-02-28T06:33:50.318Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Natus Vincere</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1078.2122233526832</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J6" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K6" t="str">
-        <v>none</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" t="str">
-        <v>2026-02-28T06:34:57.356Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Liquid</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>1077.5792194685605</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J7" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K7" t="str">
-        <v>none</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="str">
-        <v>2026-02-28T06:33:42.190Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Iluminar</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1077.4980831727503</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J8" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K8" t="str">
-        <v>none</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="str">
-        <v>2026-02-28T06:35:31.960Z</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Titan</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
+      <c r="E15">
+        <v>1034.4702257617066</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <v>2</v>
       </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>1074.7288694987144</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J9" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K9" t="str">
-        <v>none</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9" t="str">
-        <v>2026-02-28T06:34:01.405Z</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Nemiga</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>1074.4029464363696</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J10" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K10" t="str">
-        <v>none</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" t="str">
-        <v>2026-02-28T06:34:47.163Z</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Copenhagen Flames</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>1073.9176367912892</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J11" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K11" t="str">
-        <v>none</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" t="str">
-        <v>2026-02-28T06:33:50.318Z</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Elevate</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>1057.6882126347407</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J12" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K12" t="str">
-        <v>none</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="str">
-        <v>2026-02-28T06:34:57.356Z</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Spirit</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1046.2895676079393</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J13" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K13" t="str">
-        <v>none</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="str">
-        <v>2026-02-28T06:34:18.462Z</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Heroic</v>
-      </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1045.5676874676385</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J14" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K14" t="str">
-        <v>none</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" t="str">
-        <v>2026-02-28T06:34:01.405Z</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Cloud9</v>
-      </c>
-      <c r="B15">
-        <v>7</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>1044.5400283158262</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J15" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K15" t="str">
-        <v>none</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15" t="str">
-        <v>2026-02-28T06:33:42.190Z</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Onyx Ravens</v>
-      </c>
-      <c r="B16">
-        <v>7</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
       <c r="E16">
-        <v>1043.714837708515</v>
+        <v>1031.7815101827721</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1039,25 +1930,25 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J16" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K16" t="str">
-        <v>none</v>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
-      <c r="M16" t="str">
-        <v>2026-02-28T06:35:31.960Z</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Verdant</v>
+      <c r="M16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>43</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -1066,93 +1957,93 @@
         <v>0</v>
       </c>
       <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>1030.8261484839029</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>1028.7948309045817</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
         <v>4</v>
       </c>
-      <c r="E17">
-        <v>1038.7190184710753</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J17" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K17" t="str">
-        <v>none</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="str">
-        <v>2026-02-28T06:29:24.671Z</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Bounty Hunters</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-      <c r="E18">
+      <c r="E19">
         <v>1017.2412711985547</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J18" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K18" t="str">
-        <v>none</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" t="str">
-        <v>2026-02-28T06:28:59.888Z</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Falcons</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>1017.0361636029124</v>
-      </c>
       <c r="F19">
         <v>0</v>
       </c>
@@ -1162,25 +2053,25 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J19" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K19" t="str">
-        <v>none</v>
+      <c r="I19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>16</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="M19" t="str">
-        <v>2026-02-28T06:35:10.120Z</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>The Huns</v>
+      <c r="M19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1203,25 +2094,25 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J20" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K20" t="str">
-        <v>none</v>
+      <c r="I20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" t="s">
+        <v>16</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="M20" t="str">
-        <v>2026-02-18T21:21:06.168Z</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>TYLOO</v>
+      <c r="M20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>49</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -1233,7 +2124,7 @@
         <v>3</v>
       </c>
       <c r="E21">
-        <v>1014.128742285643</v>
+        <v>1014.1287422856431</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1244,25 +2135,25 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J21" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K21" t="str">
-        <v>none</v>
+      <c r="I21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>16</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
-      <c r="M21" t="str">
-        <v>2026-02-19T22:09:16.526Z</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>OG</v>
+      <c r="M21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>51</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -1285,25 +2176,25 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="I22" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J22" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K22" t="str">
-        <v>none</v>
+      <c r="I22" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" t="s">
+        <v>16</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
-      <c r="M22" t="str">
-        <v>2026-02-19T22:09:03.691Z</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>BESTIA</v>
+      <c r="M22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1326,25 +2217,25 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J23" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K23" t="str">
-        <v>none</v>
+      <c r="I23" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" t="s">
+        <v>16</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
-      <c r="M23" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>G2</v>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -1367,25 +2258,25 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J24" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K24" t="str">
-        <v>none</v>
+      <c r="I24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" t="s">
+        <v>16</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
-      <c r="M24" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>hoorai</v>
+      <c r="M24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>57</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -1408,25 +2299,25 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J25" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K25" t="str">
-        <v>none</v>
+      <c r="I25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" t="s">
+        <v>16</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
-      <c r="M25" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>00 Nation</v>
+      <c r="M25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>59</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1449,25 +2340,25 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J26" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K26" t="str">
-        <v>none</v>
+      <c r="I26" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" t="s">
+        <v>16</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>100 Thieves</v>
+      <c r="M26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>61</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1490,25 +2381,25 @@
       <c r="H27">
         <v>0</v>
       </c>
-      <c r="I27" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J27" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K27" t="str">
-        <v>none</v>
+      <c r="I27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s">
+        <v>16</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Aether</v>
+      <c r="M27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>62</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1531,25 +2422,25 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J28" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K28" t="str">
-        <v>none</v>
+      <c r="I28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
+        <v>16</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>AMKAL</v>
+      <c r="M28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>63</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1572,25 +2463,25 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J29" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K29" t="str">
-        <v>none</v>
+      <c r="I29" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" t="s">
+        <v>16</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Astana Dragons</v>
+      <c r="M29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>64</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1613,25 +2504,25 @@
       <c r="H30">
         <v>0</v>
       </c>
-      <c r="I30" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J30" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K30" t="str">
-        <v>none</v>
+      <c r="I30" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" t="s">
+        <v>16</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Astralis Talent</v>
+      <c r="M30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>65</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1654,25 +2545,25 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J31" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K31" t="str">
-        <v>none</v>
+      <c r="I31" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" t="s">
+        <v>16</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Avangar</v>
+      <c r="M31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>66</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1695,25 +2586,25 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J32" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K32" t="str">
-        <v>none</v>
+      <c r="I32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>B8</v>
+      <c r="M32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>67</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1736,25 +2627,25 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J33" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K33" t="str">
-        <v>none</v>
+      <c r="I33" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
+        <v>16</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>BIG Academy</v>
+      <c r="M33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>68</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1777,25 +2668,25 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J34" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K34" t="str">
-        <v>none</v>
+      <c r="I34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" t="s">
+        <v>16</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Bravado</v>
+      <c r="M34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>69</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1818,25 +2709,25 @@
       <c r="H35">
         <v>0</v>
       </c>
-      <c r="I35" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J35" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K35" t="str">
-        <v>none</v>
+      <c r="I35" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" t="s">
+        <v>16</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Copenhagen Wolves</v>
+      <c r="M35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>70</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1859,25 +2750,25 @@
       <c r="H36">
         <v>0</v>
       </c>
-      <c r="I36" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J36" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K36" t="str">
-        <v>none</v>
+      <c r="I36" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" t="s">
+        <v>16</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Counter Logic Games</v>
+      <c r="M36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>71</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1900,25 +2791,25 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J37" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K37" t="str">
-        <v>none</v>
+      <c r="I37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" t="s">
+        <v>16</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>ENCE Academy</v>
+      <c r="M37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>72</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1941,25 +2832,25 @@
       <c r="H38">
         <v>0</v>
       </c>
-      <c r="I38" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J38" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K38" t="str">
-        <v>none</v>
+      <c r="I38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" t="s">
+        <v>16</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>ESC</v>
+      <c r="M38" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>73</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1982,25 +2873,25 @@
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J39" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K39" t="str">
-        <v>none</v>
+      <c r="I39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" t="s">
+        <v>16</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Flash</v>
+      <c r="M39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2023,25 +2914,25 @@
       <c r="H40">
         <v>0</v>
       </c>
-      <c r="I40" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J40" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K40" t="str">
-        <v>none</v>
+      <c r="I40" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" t="s">
+        <v>16</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>FLuffy Gangsters</v>
+      <c r="M40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>75</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2064,25 +2955,25 @@
       <c r="H41">
         <v>0</v>
       </c>
-      <c r="I41" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J41" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K41" t="str">
-        <v>none</v>
+      <c r="I41" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" t="s">
+        <v>16</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>FlyQuest RED</v>
+      <c r="M41" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>76</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2105,25 +2996,25 @@
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J42" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K42" t="str">
-        <v>none</v>
+      <c r="I42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" t="s">
+        <v>16</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Fnatic</v>
+      <c r="M42" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>77</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2146,25 +3037,25 @@
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J43" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K43" t="str">
-        <v>none</v>
+      <c r="I43" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" t="s">
+        <v>16</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>FORZE</v>
+      <c r="M43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>78</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2187,25 +3078,25 @@
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J44" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K44" t="str">
-        <v>none</v>
+      <c r="I44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
-      <c r="M44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Gambit</v>
+      <c r="M44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>79</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2228,25 +3119,25 @@
       <c r="H45">
         <v>0</v>
       </c>
-      <c r="I45" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J45" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K45" t="str">
-        <v>none</v>
+      <c r="I45" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" t="s">
+        <v>16</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>GATERON</v>
+      <c r="M45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>80</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2269,25 +3160,25 @@
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J46" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K46" t="str">
-        <v>none</v>
+      <c r="I46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" t="s">
+        <v>16</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
-      <c r="M46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>GhoulsW</v>
+      <c r="M46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>81</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2310,25 +3201,25 @@
       <c r="H47">
         <v>0</v>
       </c>
-      <c r="I47" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J47" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K47" t="str">
-        <v>none</v>
+      <c r="I47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" t="s">
+        <v>16</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
-      <c r="M47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>HAVU</v>
+      <c r="M47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>82</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2351,25 +3242,25 @@
       <c r="H48">
         <v>0</v>
       </c>
-      <c r="I48" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J48" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K48" t="str">
-        <v>none</v>
+      <c r="I48" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" t="s">
+        <v>16</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
-      <c r="M48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Heroic Academy</v>
+      <c r="M48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>83</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2392,25 +3283,25 @@
       <c r="H49">
         <v>0</v>
       </c>
-      <c r="I49" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J49" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K49" t="str">
-        <v>none</v>
+      <c r="I49" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" t="s">
+        <v>29</v>
+      </c>
+      <c r="K49" t="s">
+        <v>16</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Hesta</v>
+      <c r="M49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>84</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2433,25 +3324,25 @@
       <c r="H50">
         <v>0</v>
       </c>
-      <c r="I50" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J50" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K50" t="str">
-        <v>none</v>
+      <c r="I50" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" t="s">
+        <v>16</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Immortals</v>
+      <c r="M50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>85</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2474,25 +3365,25 @@
       <c r="H51">
         <v>0</v>
       </c>
-      <c r="I51" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J51" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K51" t="str">
-        <v>none</v>
+      <c r="I51" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s">
+        <v>16</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Into the Beach</v>
+      <c r="M51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>86</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2515,25 +3406,25 @@
       <c r="H52">
         <v>0</v>
       </c>
-      <c r="I52" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J52" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K52" t="str">
-        <v>none</v>
+      <c r="I52" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" t="s">
+        <v>16</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
-      <c r="M52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Kinguin</v>
+      <c r="M52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>87</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2556,25 +3447,25 @@
       <c r="H53">
         <v>0</v>
       </c>
-      <c r="I53" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J53" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K53" t="str">
-        <v>none</v>
+      <c r="I53" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" t="s">
+        <v>16</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
-      <c r="M53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>kONO</v>
+      <c r="M53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>88</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2597,25 +3488,25 @@
       <c r="H54">
         <v>0</v>
       </c>
-      <c r="I54" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J54" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K54" t="str">
-        <v>none</v>
+      <c r="I54" t="s">
+        <v>19</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
+        <v>16</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
-      <c r="M54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>LGB eSports</v>
+      <c r="M54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>290</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -2638,25 +3529,25 @@
       <c r="H55">
         <v>0</v>
       </c>
-      <c r="I55" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J55" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K55" t="str">
-        <v>none</v>
+      <c r="I55" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" t="s">
+        <v>16</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>MAD Lions</v>
+      <c r="M55" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>89</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -2679,25 +3570,25 @@
       <c r="H56">
         <v>0</v>
       </c>
-      <c r="I56" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J56" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K56" t="str">
-        <v>none</v>
+      <c r="I56" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" t="s">
+        <v>29</v>
+      </c>
+      <c r="K56" t="s">
+        <v>16</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>MANA</v>
+      <c r="M56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>90</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -2720,25 +3611,25 @@
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J57" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K57" t="str">
-        <v>none</v>
+      <c r="I57" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" t="s">
+        <v>16</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>MIBR Academy</v>
+      <c r="M57" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>91</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -2761,25 +3652,25 @@
       <c r="H58">
         <v>0</v>
       </c>
-      <c r="I58" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J58" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K58" t="str">
-        <v>none</v>
+      <c r="I58" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" t="s">
+        <v>16</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Misfits</v>
+      <c r="M58" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>92</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -2802,25 +3693,25 @@
       <c r="H59">
         <v>0</v>
       </c>
-      <c r="I59" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J59" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K59" t="str">
-        <v>none</v>
+      <c r="I59" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" t="s">
+        <v>16</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>mousesports</v>
+      <c r="M59" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>93</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -2843,25 +3734,25 @@
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J60" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K60" t="str">
-        <v>none</v>
+      <c r="I60" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" t="s">
+        <v>29</v>
+      </c>
+      <c r="K60" t="s">
+        <v>16</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>MOUZ NXT</v>
+      <c r="M60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>94</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2884,25 +3775,25 @@
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J61" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K61" t="str">
-        <v>none</v>
+      <c r="I61" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" t="s">
+        <v>29</v>
+      </c>
+      <c r="K61" t="s">
+        <v>16</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
-      <c r="M61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Movistar KOI</v>
+      <c r="M61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>95</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2925,25 +3816,25 @@
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J62" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K62" t="str">
-        <v>none</v>
+      <c r="I62" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" t="s">
+        <v>29</v>
+      </c>
+      <c r="K62" t="s">
+        <v>16</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
-      <c r="M62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>NIP Impact</v>
+      <c r="M62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>96</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2966,25 +3857,25 @@
       <c r="H63">
         <v>0</v>
       </c>
-      <c r="I63" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J63" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K63" t="str">
-        <v>none</v>
+      <c r="I63" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" t="s">
+        <v>16</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Nordix</v>
+      <c r="M63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>97</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3007,25 +3898,25 @@
       <c r="H64">
         <v>0</v>
       </c>
-      <c r="I64" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J64" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K64" t="str">
-        <v>none</v>
+      <c r="I64" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" t="s">
+        <v>29</v>
+      </c>
+      <c r="K64" t="s">
+        <v>16</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>NOVAQ</v>
+      <c r="M64" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>98</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3048,25 +3939,25 @@
       <c r="H65">
         <v>0</v>
       </c>
-      <c r="I65" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J65" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K65" t="str">
-        <v>none</v>
+      <c r="I65" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" t="s">
+        <v>29</v>
+      </c>
+      <c r="K65" t="s">
+        <v>16</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
-      <c r="M65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>paiN Academy</v>
+      <c r="M65" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>99</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3089,25 +3980,25 @@
       <c r="H66">
         <v>0</v>
       </c>
-      <c r="I66" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J66" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K66" t="str">
-        <v>none</v>
+      <c r="I66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" t="s">
+        <v>16</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>QMISTRY</v>
+      <c r="M66" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>100</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -3130,25 +4021,25 @@
       <c r="H67">
         <v>0</v>
       </c>
-      <c r="I67" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J67" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K67" t="str">
-        <v>none</v>
+      <c r="I67" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" t="s">
+        <v>29</v>
+      </c>
+      <c r="K67" t="s">
+        <v>16</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Quantum Bellator Fire</v>
+      <c r="M67" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>101</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3171,25 +4062,25 @@
       <c r="H68">
         <v>0</v>
       </c>
-      <c r="I68" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J68" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K68" t="str">
-        <v>none</v>
+      <c r="I68" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" t="s">
+        <v>29</v>
+      </c>
+      <c r="K68" t="s">
+        <v>16</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Rogue</v>
+      <c r="M68" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>102</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -3212,25 +4103,25 @@
       <c r="H69">
         <v>0</v>
       </c>
-      <c r="I69" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J69" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K69" t="str">
-        <v>none</v>
+      <c r="I69" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" t="s">
+        <v>15</v>
+      </c>
+      <c r="K69" t="s">
+        <v>16</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
-      <c r="M69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Shika</v>
+      <c r="M69" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>103</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -3253,25 +4144,25 @@
       <c r="H70">
         <v>0</v>
       </c>
-      <c r="I70" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J70" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K70" t="str">
-        <v>none</v>
+      <c r="I70" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" t="s">
+        <v>16</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>SKYFURY</v>
+      <c r="M70" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>104</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -3294,25 +4185,25 @@
       <c r="H71">
         <v>0</v>
       </c>
-      <c r="I71" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J71" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K71" t="str">
-        <v>none</v>
+      <c r="I71" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" t="s">
+        <v>16</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
-      <c r="M71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Space Soldiers</v>
+      <c r="M71" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>105</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -3335,25 +4226,25 @@
       <c r="H72">
         <v>0</v>
       </c>
-      <c r="I72" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J72" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K72" t="str">
-        <v>none</v>
+      <c r="I72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72" t="s">
+        <v>16</v>
       </c>
       <c r="L72">
         <v>0</v>
       </c>
-      <c r="M72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Sprout</v>
+      <c r="M72" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>106</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -3376,25 +4267,25 @@
       <c r="H73">
         <v>0</v>
       </c>
-      <c r="I73" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J73" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K73" t="str">
-        <v>none</v>
+      <c r="I73" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73" t="s">
+        <v>16</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Tsunami</v>
+      <c r="M73" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>107</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -3417,25 +4308,25 @@
       <c r="H74">
         <v>0</v>
       </c>
-      <c r="I74" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J74" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K74" t="str">
-        <v>none</v>
+      <c r="I74" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" t="s">
+        <v>29</v>
+      </c>
+      <c r="K74" t="s">
+        <v>16</v>
       </c>
       <c r="L74">
         <v>0</v>
       </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>VeryGames</v>
+      <c r="M74" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>108</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -3458,25 +4349,25 @@
       <c r="H75">
         <v>0</v>
       </c>
-      <c r="I75" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J75" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K75" t="str">
-        <v>none</v>
+      <c r="I75" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75" t="s">
+        <v>16</v>
       </c>
       <c r="L75">
         <v>0</v>
       </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Vox Eminor</v>
+      <c r="M75" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>109</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -3499,25 +4390,25 @@
       <c r="H76">
         <v>0</v>
       </c>
-      <c r="I76" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J76" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K76" t="str">
-        <v>none</v>
+      <c r="I76" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" t="s">
+        <v>29</v>
+      </c>
+      <c r="K76" t="s">
+        <v>16</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
-      <c r="M76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Wildcard Academy</v>
+      <c r="M76" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>110</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -3540,25 +4431,25 @@
       <c r="H77">
         <v>0</v>
       </c>
-      <c r="I77" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J77" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K77" t="str">
-        <v>none</v>
+      <c r="I77" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" t="s">
+        <v>29</v>
+      </c>
+      <c r="K77" t="s">
+        <v>16</v>
       </c>
       <c r="L77">
         <v>0</v>
       </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Spirit Academy</v>
+      <c r="M77" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>111</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -3570,7 +4461,7 @@
         <v>2</v>
       </c>
       <c r="E78">
-        <v>999.7251809772306</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3581,25 +4472,25 @@
       <c r="H78">
         <v>0</v>
       </c>
-      <c r="I78" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J78" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K78" t="str">
-        <v>none</v>
+      <c r="I78" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
+        <v>16</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
-      <c r="M78" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>True Rippers</v>
+      <c r="M78" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>113</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -3611,7 +4502,7 @@
         <v>2</v>
       </c>
       <c r="E79">
-        <v>999.7251809772306</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3622,25 +4513,25 @@
       <c r="H79">
         <v>0</v>
       </c>
-      <c r="I79" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J79" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K79" t="str">
-        <v>none</v>
+      <c r="I79" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" t="s">
+        <v>29</v>
+      </c>
+      <c r="K79" t="s">
+        <v>16</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
-      <c r="M79" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>FaZe</v>
+      <c r="M79" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>115</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -3652,7 +4543,7 @@
         <v>2</v>
       </c>
       <c r="E80">
-        <v>999.7251809772306</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3663,25 +4554,25 @@
       <c r="H80">
         <v>0</v>
       </c>
-      <c r="I80" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J80" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K80" t="str">
-        <v>none</v>
+      <c r="I80" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" t="s">
+        <v>29</v>
+      </c>
+      <c r="K80" t="s">
+        <v>16</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
-      <c r="M80" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>iBUYPOWER</v>
+      <c r="M80" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>117</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -3693,7 +4584,7 @@
         <v>2</v>
       </c>
       <c r="E81">
-        <v>999.7251809772306</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3704,25 +4595,25 @@
       <c r="H81">
         <v>0</v>
       </c>
-      <c r="I81" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J81" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K81" t="str">
-        <v>none</v>
+      <c r="I81" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81" t="s">
+        <v>16</v>
       </c>
       <c r="L81">
         <v>0</v>
       </c>
-      <c r="M81" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>GODSENT</v>
+      <c r="M81" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>119</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -3734,7 +4625,7 @@
         <v>2</v>
       </c>
       <c r="E82">
-        <v>999.7251809772306</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -3745,25 +4636,25 @@
       <c r="H82">
         <v>0</v>
       </c>
-      <c r="I82" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J82" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K82" t="str">
-        <v>none</v>
+      <c r="I82" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82" t="s">
+        <v>16</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
-      <c r="M82" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>M80</v>
+      <c r="M82" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>121</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -3775,7 +4666,7 @@
         <v>2</v>
       </c>
       <c r="E83">
-        <v>999.672340544519</v>
+        <v>999.67234054451899</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -3786,25 +4677,25 @@
       <c r="H83">
         <v>0</v>
       </c>
-      <c r="I83" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J83" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K83" t="str">
-        <v>none</v>
+      <c r="I83" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" t="s">
+        <v>16</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
-      <c r="M83" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Chinggis Warrios</v>
+      <c r="M83" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>291</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -3816,7 +4707,7 @@
         <v>3</v>
       </c>
       <c r="E84">
-        <v>999.4408194717619</v>
+        <v>999.44081947176187</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -3827,25 +4718,25 @@
       <c r="H84">
         <v>0</v>
       </c>
-      <c r="I84" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J84" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K84" t="str">
-        <v>none</v>
+      <c r="I84" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" t="s">
+        <v>16</v>
       </c>
       <c r="L84">
         <v>0</v>
       </c>
-      <c r="M84" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Orbit</v>
+      <c r="M84" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>124</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -3857,7 +4748,7 @@
         <v>3</v>
       </c>
       <c r="E85">
-        <v>999.4186945376644</v>
+        <v>999.41869453766435</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -3868,25 +4759,25 @@
       <c r="H85">
         <v>0</v>
       </c>
-      <c r="I85" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J85" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K85" t="str">
-        <v>none</v>
+      <c r="I85" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" t="s">
+        <v>29</v>
+      </c>
+      <c r="K85" t="s">
+        <v>16</v>
       </c>
       <c r="L85">
         <v>0</v>
       </c>
-      <c r="M85" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Alliance</v>
+      <c r="M85" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>126</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -3898,7 +4789,7 @@
         <v>2</v>
       </c>
       <c r="E86">
-        <v>999.4088515186523</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -3909,25 +4800,25 @@
       <c r="H86">
         <v>0</v>
       </c>
-      <c r="I86" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J86" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K86" t="str">
-        <v>none</v>
+      <c r="I86" t="s">
+        <v>19</v>
+      </c>
+      <c r="J86" t="s">
+        <v>29</v>
+      </c>
+      <c r="K86" t="s">
+        <v>16</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
-      <c r="M86" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Homyno</v>
+      <c r="M86" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>128</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -3939,7 +4830,7 @@
         <v>2</v>
       </c>
       <c r="E87">
-        <v>999.4088515186523</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -3950,25 +4841,25 @@
       <c r="H87">
         <v>0</v>
       </c>
-      <c r="I87" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J87" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K87" t="str">
-        <v>none</v>
+      <c r="I87" t="s">
+        <v>19</v>
+      </c>
+      <c r="J87" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" t="s">
+        <v>16</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
-      <c r="M87" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>MenaceGG</v>
+      <c r="M87" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>130</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -3980,7 +4871,7 @@
         <v>2</v>
       </c>
       <c r="E88">
-        <v>999.4088515186523</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3991,25 +4882,25 @@
       <c r="H88">
         <v>0</v>
       </c>
-      <c r="I88" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J88" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K88" t="str">
-        <v>none</v>
+      <c r="I88" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" t="s">
+        <v>29</v>
+      </c>
+      <c r="K88" t="s">
+        <v>16</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
-      <c r="M88" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Solid</v>
+      <c r="M88" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>132</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -4021,7 +4912,7 @@
         <v>2</v>
       </c>
       <c r="E89">
-        <v>999.4088515186523</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -4032,25 +4923,25 @@
       <c r="H89">
         <v>0</v>
       </c>
-      <c r="I89" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J89" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K89" t="str">
-        <v>none</v>
+      <c r="I89" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" t="s">
+        <v>16</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
-      <c r="M89" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>ENCE</v>
+      <c r="M89" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>134</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -4062,7 +4953,7 @@
         <v>2</v>
       </c>
       <c r="E90">
-        <v>999.4088515186523</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -4073,25 +4964,25 @@
       <c r="H90">
         <v>0</v>
       </c>
-      <c r="I90" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J90" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K90" t="str">
-        <v>none</v>
+      <c r="I90" t="s">
+        <v>19</v>
+      </c>
+      <c r="J90" t="s">
+        <v>29</v>
+      </c>
+      <c r="K90" t="s">
+        <v>16</v>
       </c>
       <c r="L90">
         <v>0</v>
       </c>
-      <c r="M90" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Nexus</v>
+      <c r="M90" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>136</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -4103,7 +4994,7 @@
         <v>2</v>
       </c>
       <c r="E91">
-        <v>999.4088515186523</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -4114,25 +5005,25 @@
       <c r="H91">
         <v>0</v>
       </c>
-      <c r="I91" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J91" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K91" t="str">
-        <v>none</v>
+      <c r="I91" t="s">
+        <v>19</v>
+      </c>
+      <c r="J91" t="s">
+        <v>29</v>
+      </c>
+      <c r="K91" t="s">
+        <v>16</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
-      <c r="M91" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>MIBR</v>
+      <c r="M91" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>138</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -4144,7 +5035,7 @@
         <v>2</v>
       </c>
       <c r="E92">
-        <v>999.4088515186523</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4155,25 +5046,25 @@
       <c r="H92">
         <v>0</v>
       </c>
-      <c r="I92" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J92" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K92" t="str">
-        <v>none</v>
+      <c r="I92" t="s">
+        <v>19</v>
+      </c>
+      <c r="J92" t="s">
+        <v>20</v>
+      </c>
+      <c r="K92" t="s">
+        <v>16</v>
       </c>
       <c r="L92">
         <v>0</v>
       </c>
-      <c r="M92" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Wizards</v>
+      <c r="M92" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>140</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -4185,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="E93">
-        <v>999.4062521695108</v>
+        <v>999.40625216951082</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -4196,25 +5087,25 @@
       <c r="H93">
         <v>0</v>
       </c>
-      <c r="I93" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J93" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K93" t="str">
-        <v>none</v>
+      <c r="I93" t="s">
+        <v>19</v>
+      </c>
+      <c r="J93" t="s">
+        <v>20</v>
+      </c>
+      <c r="K93" t="s">
+        <v>16</v>
       </c>
       <c r="L93">
         <v>0</v>
       </c>
-      <c r="M93" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>RED Canids</v>
+      <c r="M93" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>142</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -4226,7 +5117,7 @@
         <v>3</v>
       </c>
       <c r="E94">
-        <v>999.3397745397444</v>
+        <v>999.33977453974444</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4237,25 +5128,25 @@
       <c r="H94">
         <v>0</v>
       </c>
-      <c r="I94" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J94" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K94" t="str">
-        <v>none</v>
+      <c r="I94" t="s">
+        <v>19</v>
+      </c>
+      <c r="J94" t="s">
+        <v>20</v>
+      </c>
+      <c r="K94" t="s">
+        <v>16</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
-      <c r="M94" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Rebels</v>
+      <c r="M94" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>144</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -4267,7 +5158,7 @@
         <v>5</v>
       </c>
       <c r="E95">
-        <v>999.3232682842747</v>
+        <v>999.32326828427472</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4278,25 +5169,25 @@
       <c r="H95">
         <v>0</v>
       </c>
-      <c r="I95" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J95" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K95" t="str">
-        <v>none</v>
+      <c r="I95" t="s">
+        <v>19</v>
+      </c>
+      <c r="J95" t="s">
+        <v>29</v>
+      </c>
+      <c r="K95" t="s">
+        <v>16</v>
       </c>
       <c r="L95">
         <v>0</v>
       </c>
-      <c r="M95" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>FURIA</v>
+      <c r="M95" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>146</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -4308,7 +5199,7 @@
         <v>3</v>
       </c>
       <c r="E96">
-        <v>985.3605394813516</v>
+        <v>985.36053948135157</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -4319,25 +5210,25 @@
       <c r="H96">
         <v>0</v>
       </c>
-      <c r="I96" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J96" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K96" t="str">
-        <v>none</v>
+      <c r="I96" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" t="s">
+        <v>20</v>
+      </c>
+      <c r="K96" t="s">
+        <v>16</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
-      <c r="M96" t="str">
-        <v>2026-02-19T22:08:26.017Z</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>ad hoc</v>
+      <c r="M96" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>148</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -4360,25 +5251,25 @@
       <c r="H97">
         <v>0</v>
       </c>
-      <c r="I97" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J97" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K97" t="str">
-        <v>none</v>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" t="s">
+        <v>16</v>
       </c>
       <c r="L97">
         <v>0</v>
       </c>
-      <c r="M97" t="str">
-        <v>2026-02-19T00:50:09.060Z</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>SAW</v>
+      <c r="M97" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>150</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -4401,25 +5292,25 @@
       <c r="H98">
         <v>0</v>
       </c>
-      <c r="I98" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J98" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K98" t="str">
-        <v>none</v>
+      <c r="I98" t="s">
+        <v>19</v>
+      </c>
+      <c r="J98" t="s">
+        <v>29</v>
+      </c>
+      <c r="K98" t="s">
+        <v>16</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
-      <c r="M98" t="str">
-        <v>2026-02-19T00:49:47.596Z</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>NomadS</v>
+      <c r="M98" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>152</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -4442,25 +5333,25 @@
       <c r="H99">
         <v>0</v>
       </c>
-      <c r="I99" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J99" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K99" t="str">
-        <v>none</v>
+      <c r="I99" t="s">
+        <v>19</v>
+      </c>
+      <c r="J99" t="s">
+        <v>15</v>
+      </c>
+      <c r="K99" t="s">
+        <v>16</v>
       </c>
       <c r="L99">
         <v>0</v>
       </c>
-      <c r="M99" t="str">
-        <v>2026-02-19T00:49:35.489Z</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Outsiders</v>
+      <c r="M99" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>154</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -4483,25 +5374,25 @@
       <c r="H100">
         <v>0</v>
       </c>
-      <c r="I100" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J100" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K100" t="str">
-        <v>none</v>
+      <c r="I100" t="s">
+        <v>19</v>
+      </c>
+      <c r="J100" t="s">
+        <v>29</v>
+      </c>
+      <c r="K100" t="s">
+        <v>16</v>
       </c>
       <c r="L100">
         <v>0</v>
       </c>
-      <c r="M100" t="str">
-        <v>2026-02-19T00:49:27.811Z</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Red Viperz</v>
+      <c r="M100" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>156</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4524,25 +5415,25 @@
       <c r="H101">
         <v>0</v>
       </c>
-      <c r="I101" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J101" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K101" t="str">
-        <v>none</v>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s">
+        <v>20</v>
+      </c>
+      <c r="K101" t="s">
+        <v>16</v>
       </c>
       <c r="L101">
         <v>0</v>
       </c>
-      <c r="M101" t="str">
-        <v>2026-02-19T00:49:20.687Z</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>The Dice</v>
+      <c r="M101" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>158</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -4565,25 +5456,25 @@
       <c r="H102">
         <v>0</v>
       </c>
-      <c r="I102" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J102" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K102" t="str">
-        <v>none</v>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" t="s">
+        <v>29</v>
+      </c>
+      <c r="K102" t="s">
+        <v>16</v>
       </c>
       <c r="L102">
         <v>0</v>
       </c>
-      <c r="M102" t="str">
-        <v>2026-02-19T00:49:12.765Z</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Victores Sumus</v>
+      <c r="M102" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>160</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -4606,25 +5497,25 @@
       <c r="H103">
         <v>0</v>
       </c>
-      <c r="I103" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J103" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K103" t="str">
-        <v>none</v>
+      <c r="I103" t="s">
+        <v>19</v>
+      </c>
+      <c r="J103" t="s">
+        <v>15</v>
+      </c>
+      <c r="K103" t="s">
+        <v>16</v>
       </c>
       <c r="L103">
         <v>0</v>
       </c>
-      <c r="M103" t="str">
-        <v>2026-02-19T00:49:00.243Z</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>ODDIK</v>
+      <c r="M103" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>162</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -4647,25 +5538,25 @@
       <c r="H104">
         <v>0</v>
       </c>
-      <c r="I104" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J104" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K104" t="str">
-        <v>none</v>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s">
+        <v>20</v>
+      </c>
+      <c r="K104" t="s">
+        <v>16</v>
       </c>
       <c r="L104">
         <v>0</v>
       </c>
-      <c r="M104" t="str">
-        <v>2026-02-19T00:48:52.026Z</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Qiang</v>
+      <c r="M104" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>164</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -4688,25 +5579,25 @@
       <c r="H105">
         <v>0</v>
       </c>
-      <c r="I105" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J105" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K105" t="str">
-        <v>none</v>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+      <c r="J105" t="s">
+        <v>29</v>
+      </c>
+      <c r="K105" t="s">
+        <v>16</v>
       </c>
       <c r="L105">
         <v>0</v>
       </c>
-      <c r="M105" t="str">
-        <v>2026-02-19T00:48:45.055Z</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>inSanitY</v>
+      <c r="M105" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>166</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -4729,25 +5620,25 @@
       <c r="H106">
         <v>0</v>
       </c>
-      <c r="I106" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J106" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K106" t="str">
-        <v>none</v>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+      <c r="J106" t="s">
+        <v>29</v>
+      </c>
+      <c r="K106" t="s">
+        <v>16</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
-      <c r="M106" t="str">
-        <v>2026-02-19T00:48:38.129Z</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Sangal</v>
+      <c r="M106" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>168</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -4770,25 +5661,25 @@
       <c r="H107">
         <v>0</v>
       </c>
-      <c r="I107" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J107" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K107" t="str">
-        <v>none</v>
+      <c r="I107" t="s">
+        <v>19</v>
+      </c>
+      <c r="J107" t="s">
+        <v>29</v>
+      </c>
+      <c r="K107" t="s">
+        <v>16</v>
       </c>
       <c r="L107">
         <v>0</v>
       </c>
-      <c r="M107" t="str">
-        <v>2026-02-19T00:48:28.102Z</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>9Pandas</v>
+      <c r="M107" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>170</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -4811,25 +5702,25 @@
       <c r="H108">
         <v>0</v>
       </c>
-      <c r="I108" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J108" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K108" t="str">
-        <v>none</v>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+      <c r="J108" t="s">
+        <v>29</v>
+      </c>
+      <c r="K108" t="s">
+        <v>16</v>
       </c>
       <c r="L108">
         <v>0</v>
       </c>
-      <c r="M108" t="str">
-        <v>2026-02-19T00:48:17.012Z</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Gods Reign</v>
+      <c r="M108" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>172</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -4852,25 +5743,25 @@
       <c r="H109">
         <v>0</v>
       </c>
-      <c r="I109" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J109" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K109" t="str">
-        <v>none</v>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+      <c r="J109" t="s">
+        <v>29</v>
+      </c>
+      <c r="K109" t="s">
+        <v>16</v>
       </c>
       <c r="L109">
         <v>0</v>
       </c>
-      <c r="M109" t="str">
-        <v>2026-02-19T00:48:09.473Z</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>CatEvil</v>
+      <c r="M109" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>174</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -4893,25 +5784,25 @@
       <c r="H110">
         <v>0</v>
       </c>
-      <c r="I110" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J110" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K110" t="str">
-        <v>none</v>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+      <c r="J110" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110" t="s">
+        <v>16</v>
       </c>
       <c r="L110">
         <v>0</v>
       </c>
-      <c r="M110" t="str">
-        <v>2026-02-19T00:48:02.110Z</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>Carnival</v>
+      <c r="M110" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>176</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -4934,25 +5825,25 @@
       <c r="H111">
         <v>0</v>
       </c>
-      <c r="I111" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J111" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K111" t="str">
-        <v>none</v>
+      <c r="I111" t="s">
+        <v>19</v>
+      </c>
+      <c r="J111" t="s">
+        <v>29</v>
+      </c>
+      <c r="K111" t="s">
+        <v>16</v>
       </c>
       <c r="L111">
         <v>0</v>
       </c>
-      <c r="M111" t="str">
-        <v>2026-02-19T00:47:49.161Z</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>Evil Geniuses</v>
+      <c r="M111" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>178</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -4975,25 +5866,25 @@
       <c r="H112">
         <v>0</v>
       </c>
-      <c r="I112" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J112" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K112" t="str">
-        <v>none</v>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+      <c r="J112" t="s">
+        <v>29</v>
+      </c>
+      <c r="K112" t="s">
+        <v>16</v>
       </c>
       <c r="L112">
         <v>0</v>
       </c>
-      <c r="M112" t="str">
-        <v>2026-02-19T00:47:36.482Z</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Vantage</v>
+      <c r="M112" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>180</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -5016,25 +5907,25 @@
       <c r="H113">
         <v>0</v>
       </c>
-      <c r="I113" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J113" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K113" t="str">
-        <v>none</v>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+      <c r="J113" t="s">
+        <v>29</v>
+      </c>
+      <c r="K113" t="s">
+        <v>16</v>
       </c>
       <c r="L113">
         <v>0</v>
       </c>
-      <c r="M113" t="str">
-        <v>2026-02-19T00:47:28.286Z</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>ATOX</v>
+      <c r="M113" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>182</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -5057,25 +5948,25 @@
       <c r="H114">
         <v>0</v>
       </c>
-      <c r="I114" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J114" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K114" t="str">
-        <v>none</v>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+      <c r="J114" t="s">
+        <v>15</v>
+      </c>
+      <c r="K114" t="s">
+        <v>16</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
-      <c r="M114" t="str">
-        <v>2026-02-19T00:47:18.470Z</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>Skinvault</v>
+      <c r="M114" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>184</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -5098,25 +5989,25 @@
       <c r="H115">
         <v>0</v>
       </c>
-      <c r="I115" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J115" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K115" t="str">
-        <v>none</v>
+      <c r="I115" t="s">
+        <v>19</v>
+      </c>
+      <c r="J115" t="s">
+        <v>29</v>
+      </c>
+      <c r="K115" t="s">
+        <v>16</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
-      <c r="M115" t="str">
-        <v>2026-02-19T00:47:11.265Z</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>BC.Game</v>
+      <c r="M115" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>186</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -5139,25 +6030,25 @@
       <c r="H116">
         <v>0</v>
       </c>
-      <c r="I116" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J116" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K116" t="str">
-        <v>none</v>
+      <c r="I116" t="s">
+        <v>19</v>
+      </c>
+      <c r="J116" t="s">
+        <v>29</v>
+      </c>
+      <c r="K116" t="s">
+        <v>16</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
-      <c r="M116" t="str">
-        <v>2026-02-19T00:46:52.846Z</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>Wings Up</v>
+      <c r="M116" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>188</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -5180,25 +6071,25 @@
       <c r="H117">
         <v>0</v>
       </c>
-      <c r="I117" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J117" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K117" t="str">
-        <v>none</v>
+      <c r="I117" t="s">
+        <v>19</v>
+      </c>
+      <c r="J117" t="s">
+        <v>15</v>
+      </c>
+      <c r="K117" t="s">
+        <v>16</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
-      <c r="M117" t="str">
-        <v>2026-02-19T00:46:32.115Z</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>Lynn Vision</v>
+      <c r="M117" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>190</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -5221,25 +6112,25 @@
       <c r="H118">
         <v>0</v>
       </c>
-      <c r="I118" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J118" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K118" t="str">
-        <v>none</v>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+      <c r="J118" t="s">
+        <v>15</v>
+      </c>
+      <c r="K118" t="s">
+        <v>16</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
-      <c r="M118" t="str">
-        <v>2026-02-19T00:46:08.336Z</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>Tricked</v>
+      <c r="M118" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>192</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -5262,25 +6153,25 @@
       <c r="H119">
         <v>0</v>
       </c>
-      <c r="I119" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J119" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K119" t="str">
-        <v>none</v>
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+      <c r="J119" t="s">
+        <v>29</v>
+      </c>
+      <c r="K119" t="s">
+        <v>16</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
-      <c r="M119" t="str">
-        <v>2026-02-19T00:45:42.234Z</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>3DMAX</v>
+      <c r="M119" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>194</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -5303,25 +6194,25 @@
       <c r="H120">
         <v>0</v>
       </c>
-      <c r="I120" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J120" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K120" t="str">
-        <v>none</v>
+      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+      <c r="J120" t="s">
+        <v>29</v>
+      </c>
+      <c r="K120" t="s">
+        <v>16</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
-      <c r="M120" t="str">
-        <v>2026-02-19T00:39:02.710Z</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>Venom</v>
+      <c r="M120" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>196</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -5344,25 +6235,25 @@
       <c r="H121">
         <v>0</v>
       </c>
-      <c r="I121" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J121" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K121" t="str">
-        <v>none</v>
+      <c r="I121" t="s">
+        <v>19</v>
+      </c>
+      <c r="J121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K121" t="s">
+        <v>16</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
-      <c r="M121" t="str">
-        <v>2026-02-19T00:38:39.010Z</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>ARCRED</v>
+      <c r="M121" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>198</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -5385,25 +6276,25 @@
       <c r="H122">
         <v>0</v>
       </c>
-      <c r="I122" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J122" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K122" t="str">
-        <v>none</v>
+      <c r="I122" t="s">
+        <v>19</v>
+      </c>
+      <c r="J122" t="s">
+        <v>29</v>
+      </c>
+      <c r="K122" t="s">
+        <v>16</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
-      <c r="M122" t="str">
-        <v>2026-02-19T00:38:03.598Z</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>GamerLegion</v>
+      <c r="M122" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>200</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -5426,25 +6317,25 @@
       <c r="H123">
         <v>0</v>
       </c>
-      <c r="I123" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J123" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K123" t="str">
-        <v>none</v>
+      <c r="I123" t="s">
+        <v>19</v>
+      </c>
+      <c r="J123" t="s">
+        <v>20</v>
+      </c>
+      <c r="K123" t="s">
+        <v>16</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
-      <c r="M123" t="str">
-        <v>2026-02-19T00:37:47.172Z</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>Passion UA</v>
+      <c r="M123" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>202</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -5467,25 +6358,25 @@
       <c r="H124">
         <v>0</v>
       </c>
-      <c r="I124" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J124" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K124" t="str">
-        <v>none</v>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+      <c r="J124" t="s">
+        <v>29</v>
+      </c>
+      <c r="K124" t="s">
+        <v>16</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
-      <c r="M124" t="str">
-        <v>2026-02-19T00:37:27.234Z</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>FlyQuest</v>
+      <c r="M124" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>204</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -5508,25 +6399,25 @@
       <c r="H125">
         <v>0</v>
       </c>
-      <c r="I125" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J125" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K125" t="str">
-        <v>none</v>
+      <c r="I125" t="s">
+        <v>19</v>
+      </c>
+      <c r="J125" t="s">
+        <v>15</v>
+      </c>
+      <c r="K125" t="s">
+        <v>16</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
-      <c r="M125" t="str">
-        <v>2026-02-19T00:37:20.280Z</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>Envy</v>
+      <c r="M125" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>206</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -5549,25 +6440,25 @@
       <c r="H126">
         <v>0</v>
       </c>
-      <c r="I126" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J126" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K126" t="str">
-        <v>none</v>
+      <c r="I126" t="s">
+        <v>19</v>
+      </c>
+      <c r="J126" t="s">
+        <v>29</v>
+      </c>
+      <c r="K126" t="s">
+        <v>16</v>
       </c>
       <c r="L126">
         <v>0</v>
       </c>
-      <c r="M126" t="str">
-        <v>2026-02-19T00:37:05.560Z</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>BIG</v>
+      <c r="M126" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>208</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -5590,25 +6481,25 @@
       <c r="H127">
         <v>0</v>
       </c>
-      <c r="I127" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J127" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K127" t="str">
-        <v>none</v>
+      <c r="I127" t="s">
+        <v>19</v>
+      </c>
+      <c r="J127" t="s">
+        <v>29</v>
+      </c>
+      <c r="K127" t="s">
+        <v>16</v>
       </c>
       <c r="L127">
         <v>0</v>
       </c>
-      <c r="M127" t="str">
-        <v>2026-02-19T00:36:43.463Z</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>Limitless</v>
+      <c r="M127" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>210</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -5631,25 +6522,25 @@
       <c r="H128">
         <v>0</v>
       </c>
-      <c r="I128" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J128" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K128" t="str">
-        <v>none</v>
+      <c r="I128" t="s">
+        <v>19</v>
+      </c>
+      <c r="J128" t="s">
+        <v>29</v>
+      </c>
+      <c r="K128" t="s">
+        <v>16</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
-      <c r="M128" t="str">
-        <v>2026-02-19T00:36:26.343Z</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Galorys</v>
+      <c r="M128" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>212</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -5672,25 +6563,25 @@
       <c r="H129">
         <v>0</v>
       </c>
-      <c r="I129" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J129" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K129" t="str">
-        <v>none</v>
+      <c r="I129" t="s">
+        <v>19</v>
+      </c>
+      <c r="J129" t="s">
+        <v>20</v>
+      </c>
+      <c r="K129" t="s">
+        <v>16</v>
       </c>
       <c r="L129">
         <v>0</v>
       </c>
-      <c r="M129" t="str">
-        <v>2026-02-19T00:36:18.696Z</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>devils.one</v>
+      <c r="M129" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>214</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -5713,25 +6604,25 @@
       <c r="H130">
         <v>0</v>
       </c>
-      <c r="I130" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J130" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K130" t="str">
-        <v>none</v>
+      <c r="I130" t="s">
+        <v>19</v>
+      </c>
+      <c r="J130" t="s">
+        <v>15</v>
+      </c>
+      <c r="K130" t="s">
+        <v>16</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
-      <c r="M130" t="str">
-        <v>2026-02-18T21:23:30.347Z</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>Luminosity</v>
+      <c r="M130" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>216</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -5754,25 +6645,25 @@
       <c r="H131">
         <v>0</v>
       </c>
-      <c r="I131" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J131" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K131" t="str">
-        <v>none</v>
+      <c r="I131" t="s">
+        <v>19</v>
+      </c>
+      <c r="J131" t="s">
+        <v>29</v>
+      </c>
+      <c r="K131" t="s">
+        <v>16</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
-      <c r="M131" t="str">
-        <v>2026-02-18T21:23:18.851Z</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>Sharks</v>
+      <c r="M131" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>218</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -5795,25 +6686,25 @@
       <c r="H132">
         <v>0</v>
       </c>
-      <c r="I132" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J132" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K132" t="str">
-        <v>none</v>
+      <c r="I132" t="s">
+        <v>19</v>
+      </c>
+      <c r="J132" t="s">
+        <v>20</v>
+      </c>
+      <c r="K132" t="s">
+        <v>16</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
-      <c r="M132" t="str">
-        <v>2026-02-18T21:23:12.952Z</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>IHC</v>
+      <c r="M132" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>220</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -5836,25 +6727,25 @@
       <c r="H133">
         <v>0</v>
       </c>
-      <c r="I133" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J133" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K133" t="str">
-        <v>none</v>
+      <c r="I133" t="s">
+        <v>19</v>
+      </c>
+      <c r="J133" t="s">
+        <v>15</v>
+      </c>
+      <c r="K133" t="s">
+        <v>16</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
-      <c r="M133" t="str">
-        <v>2026-02-18T21:23:06.529Z</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>Kappa Bar</v>
+      <c r="M133" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>222</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -5877,25 +6768,25 @@
       <c r="H134">
         <v>0</v>
       </c>
-      <c r="I134" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J134" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K134" t="str">
-        <v>none</v>
+      <c r="I134" t="s">
+        <v>19</v>
+      </c>
+      <c r="J134" t="s">
+        <v>29</v>
+      </c>
+      <c r="K134" t="s">
+        <v>16</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
-      <c r="M134" t="str">
-        <v>2026-02-18T21:22:57.244Z</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>Complexity</v>
+      <c r="M134" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>224</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -5918,25 +6809,25 @@
       <c r="H135">
         <v>0</v>
       </c>
-      <c r="I135" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J135" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K135" t="str">
-        <v>none</v>
+      <c r="I135" t="s">
+        <v>19</v>
+      </c>
+      <c r="J135" t="s">
+        <v>20</v>
+      </c>
+      <c r="K135" t="s">
+        <v>16</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
-      <c r="M135" t="str">
-        <v>2026-02-18T21:22:48.652Z</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>Case</v>
+      <c r="M135" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>226</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -5959,25 +6850,25 @@
       <c r="H136">
         <v>0</v>
       </c>
-      <c r="I136" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J136" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K136" t="str">
-        <v>none</v>
+      <c r="I136" t="s">
+        <v>19</v>
+      </c>
+      <c r="J136" t="s">
+        <v>29</v>
+      </c>
+      <c r="K136" t="s">
+        <v>16</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
-      <c r="M136" t="str">
-        <v>2026-02-18T21:22:39.402Z</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>Mythic</v>
+      <c r="M136" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>228</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -6000,25 +6891,25 @@
       <c r="H137">
         <v>0</v>
       </c>
-      <c r="I137" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J137" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K137" t="str">
-        <v>none</v>
+      <c r="I137" t="s">
+        <v>19</v>
+      </c>
+      <c r="J137" t="s">
+        <v>20</v>
+      </c>
+      <c r="K137" t="s">
+        <v>16</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
-      <c r="M137" t="str">
-        <v>2026-02-18T21:22:32.047Z</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>Enemy</v>
+      <c r="M137" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>230</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -6041,25 +6932,25 @@
       <c r="H138">
         <v>0</v>
       </c>
-      <c r="I138" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J138" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K138" t="str">
-        <v>none</v>
+      <c r="I138" t="s">
+        <v>19</v>
+      </c>
+      <c r="J138" t="s">
+        <v>29</v>
+      </c>
+      <c r="K138" t="s">
+        <v>16</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
-      <c r="M138" t="str">
-        <v>2026-02-18T21:22:20.745Z</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>KRU</v>
+      <c r="M138" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>232</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -6082,25 +6973,25 @@
       <c r="H139">
         <v>0</v>
       </c>
-      <c r="I139" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J139" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K139" t="str">
-        <v>none</v>
+      <c r="I139" t="s">
+        <v>19</v>
+      </c>
+      <c r="J139" t="s">
+        <v>20</v>
+      </c>
+      <c r="K139" t="s">
+        <v>16</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
-      <c r="M139" t="str">
-        <v>2026-02-18T21:22:06.663Z</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>Imperial</v>
+      <c r="M139" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>234</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -6123,25 +7014,25 @@
       <c r="H140">
         <v>0</v>
       </c>
-      <c r="I140" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J140" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K140" t="str">
-        <v>none</v>
+      <c r="I140" t="s">
+        <v>19</v>
+      </c>
+      <c r="J140" t="s">
+        <v>20</v>
+      </c>
+      <c r="K140" t="s">
+        <v>16</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
-      <c r="M140" t="str">
-        <v>2026-02-18T21:21:57.658Z</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>9z</v>
+      <c r="M140" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>236</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -6164,25 +7055,25 @@
       <c r="H141">
         <v>0</v>
       </c>
-      <c r="I141" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J141" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K141" t="str">
-        <v>none</v>
+      <c r="I141" t="s">
+        <v>19</v>
+      </c>
+      <c r="J141" t="s">
+        <v>20</v>
+      </c>
+      <c r="K141" t="s">
+        <v>16</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
-      <c r="M141" t="str">
-        <v>2026-02-18T21:21:44.273Z</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>paiN</v>
+      <c r="M141" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>238</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -6205,25 +7096,25 @@
       <c r="H142">
         <v>0</v>
       </c>
-      <c r="I142" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J142" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K142" t="str">
-        <v>none</v>
+      <c r="I142" t="s">
+        <v>19</v>
+      </c>
+      <c r="J142" t="s">
+        <v>20</v>
+      </c>
+      <c r="K142" t="s">
+        <v>16</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
-      <c r="M142" t="str">
-        <v>2026-02-18T21:21:14.058Z</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>Vexed</v>
+      <c r="M142" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>240</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -6246,25 +7137,25 @@
       <c r="H143">
         <v>0</v>
       </c>
-      <c r="I143" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J143" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K143" t="str">
-        <v>none</v>
+      <c r="I143" t="s">
+        <v>19</v>
+      </c>
+      <c r="J143" t="s">
+        <v>29</v>
+      </c>
+      <c r="K143" t="s">
+        <v>16</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
-      <c r="M143" t="str">
-        <v>2026-02-18T21:19:58.722Z</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>Dignitas</v>
+      <c r="M143" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>242</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -6276,7 +7167,7 @@
         <v>2</v>
       </c>
       <c r="E144">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -6287,25 +7178,25 @@
       <c r="H144">
         <v>0</v>
       </c>
-      <c r="I144" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J144" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K144" t="str">
-        <v>none</v>
+      <c r="I144" t="s">
+        <v>19</v>
+      </c>
+      <c r="J144" t="s">
+        <v>29</v>
+      </c>
+      <c r="K144" t="s">
+        <v>16</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
-      <c r="M144" t="str">
-        <v>2026-02-19T21:54:17.535Z</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>LDLC</v>
+      <c r="M144" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>244</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -6317,7 +7208,7 @@
         <v>2</v>
       </c>
       <c r="E145">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -6328,25 +7219,25 @@
       <c r="H145">
         <v>0</v>
       </c>
-      <c r="I145" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J145" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K145" t="str">
-        <v>none</v>
+      <c r="I145" t="s">
+        <v>19</v>
+      </c>
+      <c r="J145" t="s">
+        <v>29</v>
+      </c>
+      <c r="K145" t="s">
+        <v>16</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
-      <c r="M145" t="str">
-        <v>2026-02-19T21:53:53.691Z</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>Aravt</v>
+      <c r="M145" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>246</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -6358,7 +7249,7 @@
         <v>2</v>
       </c>
       <c r="E146">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -6369,25 +7260,25 @@
       <c r="H146">
         <v>0</v>
       </c>
-      <c r="I146" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J146" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K146" t="str">
-        <v>none</v>
+      <c r="I146" t="s">
+        <v>19</v>
+      </c>
+      <c r="J146" t="s">
+        <v>29</v>
+      </c>
+      <c r="K146" t="s">
+        <v>16</v>
       </c>
       <c r="L146">
         <v>0</v>
       </c>
-      <c r="M146" t="str">
-        <v>2026-02-19T02:51:09.872Z</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>VP.Prodigy</v>
+      <c r="M146" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>248</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -6399,7 +7290,7 @@
         <v>2</v>
       </c>
       <c r="E147">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -6410,25 +7301,25 @@
       <c r="H147">
         <v>0</v>
       </c>
-      <c r="I147" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J147" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K147" t="str">
-        <v>none</v>
+      <c r="I147" t="s">
+        <v>19</v>
+      </c>
+      <c r="J147" t="s">
+        <v>29</v>
+      </c>
+      <c r="K147" t="s">
+        <v>16</v>
       </c>
       <c r="L147">
         <v>0</v>
       </c>
-      <c r="M147" t="str">
-        <v>2026-02-19T02:51:03.784Z</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>Entropiq</v>
+      <c r="M147" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>250</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -6440,7 +7331,7 @@
         <v>2</v>
       </c>
       <c r="E148">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -6451,25 +7342,25 @@
       <c r="H148">
         <v>0</v>
       </c>
-      <c r="I148" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J148" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K148" t="str">
-        <v>none</v>
+      <c r="I148" t="s">
+        <v>19</v>
+      </c>
+      <c r="J148" t="s">
+        <v>20</v>
+      </c>
+      <c r="K148" t="s">
+        <v>16</v>
       </c>
       <c r="L148">
         <v>0</v>
       </c>
-      <c r="M148" t="str">
-        <v>2026-02-19T02:49:25.044Z</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>Take Flyte</v>
+      <c r="M148" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>252</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -6481,7 +7372,7 @@
         <v>2</v>
       </c>
       <c r="E149">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -6492,25 +7383,25 @@
       <c r="H149">
         <v>0</v>
       </c>
-      <c r="I149" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J149" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K149" t="str">
-        <v>none</v>
+      <c r="I149" t="s">
+        <v>19</v>
+      </c>
+      <c r="J149" t="s">
+        <v>20</v>
+      </c>
+      <c r="K149" t="s">
+        <v>16</v>
       </c>
       <c r="L149">
         <v>0</v>
       </c>
-      <c r="M149" t="str">
-        <v>2026-02-19T02:49:14.876Z</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>Underground</v>
+      <c r="M149" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>254</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -6522,7 +7413,7 @@
         <v>2</v>
       </c>
       <c r="E150">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -6533,25 +7424,25 @@
       <c r="H150">
         <v>0</v>
       </c>
-      <c r="I150" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J150" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K150" t="str">
-        <v>none</v>
+      <c r="I150" t="s">
+        <v>19</v>
+      </c>
+      <c r="J150" t="s">
+        <v>29</v>
+      </c>
+      <c r="K150" t="s">
+        <v>16</v>
       </c>
       <c r="L150">
         <v>0</v>
       </c>
-      <c r="M150" t="str">
-        <v>2026-02-19T02:47:27.422Z</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>Virtus.pro</v>
+      <c r="M150" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>256</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -6563,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="E151">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -6574,25 +7465,25 @@
       <c r="H151">
         <v>0</v>
       </c>
-      <c r="I151" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J151" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K151" t="str">
-        <v>none</v>
+      <c r="I151" t="s">
+        <v>19</v>
+      </c>
+      <c r="J151" t="s">
+        <v>29</v>
+      </c>
+      <c r="K151" t="s">
+        <v>16</v>
       </c>
       <c r="L151">
         <v>0</v>
       </c>
-      <c r="M151" t="str">
-        <v>2026-02-19T02:47:19.575Z</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>ShindeN</v>
+      <c r="M151" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>258</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -6604,7 +7495,7 @@
         <v>2</v>
       </c>
       <c r="E152">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -6615,25 +7506,25 @@
       <c r="H152">
         <v>0</v>
       </c>
-      <c r="I152" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J152" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K152" t="str">
-        <v>none</v>
+      <c r="I152" t="s">
+        <v>19</v>
+      </c>
+      <c r="J152" t="s">
+        <v>29</v>
+      </c>
+      <c r="K152" t="s">
+        <v>16</v>
       </c>
       <c r="L152">
         <v>0</v>
       </c>
-      <c r="M152" t="str">
-        <v>2026-02-19T02:36:26.535Z</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Permitta</v>
+      <c r="M152" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>260</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -6645,7 +7536,7 @@
         <v>2</v>
       </c>
       <c r="E153">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -6656,25 +7547,25 @@
       <c r="H153">
         <v>0</v>
       </c>
-      <c r="I153" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J153" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K153" t="str">
-        <v>none</v>
+      <c r="I153" t="s">
+        <v>19</v>
+      </c>
+      <c r="J153" t="s">
+        <v>29</v>
+      </c>
+      <c r="K153" t="s">
+        <v>16</v>
       </c>
       <c r="L153">
         <v>0</v>
       </c>
-      <c r="M153" t="str">
-        <v>2026-02-19T02:36:17.329Z</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>Wildcard</v>
+      <c r="M153" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>262</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -6686,7 +7577,7 @@
         <v>2</v>
       </c>
       <c r="E154">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -6697,25 +7588,25 @@
       <c r="H154">
         <v>0</v>
       </c>
-      <c r="I154" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J154" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K154" t="str">
-        <v>none</v>
+      <c r="I154" t="s">
+        <v>19</v>
+      </c>
+      <c r="J154" t="s">
+        <v>15</v>
+      </c>
+      <c r="K154" t="s">
+        <v>16</v>
       </c>
       <c r="L154">
         <v>0</v>
       </c>
-      <c r="M154" t="str">
-        <v>2026-02-19T02:34:08.116Z</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>Astralis</v>
+      <c r="M154" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>264</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -6727,7 +7618,7 @@
         <v>2</v>
       </c>
       <c r="E155">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -6738,25 +7629,25 @@
       <c r="H155">
         <v>0</v>
       </c>
-      <c r="I155" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J155" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K155" t="str">
-        <v>none</v>
+      <c r="I155" t="s">
+        <v>19</v>
+      </c>
+      <c r="J155" t="s">
+        <v>29</v>
+      </c>
+      <c r="K155" t="s">
+        <v>16</v>
       </c>
       <c r="L155">
         <v>0</v>
       </c>
-      <c r="M155" t="str">
-        <v>2026-02-19T02:34:01.822Z</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>Bad News Eagles</v>
+      <c r="M155" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>266</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -6768,7 +7659,7 @@
         <v>2</v>
       </c>
       <c r="E156">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -6779,25 +7670,25 @@
       <c r="H156">
         <v>0</v>
       </c>
-      <c r="I156" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J156" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K156" t="str">
-        <v>none</v>
+      <c r="I156" t="s">
+        <v>19</v>
+      </c>
+      <c r="J156" t="s">
+        <v>20</v>
+      </c>
+      <c r="K156" t="s">
+        <v>16</v>
       </c>
       <c r="L156">
         <v>0</v>
       </c>
-      <c r="M156" t="str">
-        <v>2026-02-19T01:45:27.335Z</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>SK</v>
+      <c r="M156" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>268</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -6809,7 +7700,7 @@
         <v>2</v>
       </c>
       <c r="E157">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -6820,25 +7711,25 @@
       <c r="H157">
         <v>0</v>
       </c>
-      <c r="I157" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J157" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K157" t="str">
-        <v>none</v>
+      <c r="I157" t="s">
+        <v>19</v>
+      </c>
+      <c r="J157" t="s">
+        <v>15</v>
+      </c>
+      <c r="K157" t="s">
+        <v>16</v>
       </c>
       <c r="L157">
         <v>0</v>
       </c>
-      <c r="M157" t="str">
-        <v>2026-02-19T01:39:18.535Z</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>ECSTATIC</v>
+      <c r="M157" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>270</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -6850,7 +7741,7 @@
         <v>2</v>
       </c>
       <c r="E158">
-        <v>984.7039370196626</v>
+        <v>984.70393701966259</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6861,25 +7752,25 @@
       <c r="H158">
         <v>0</v>
       </c>
-      <c r="I158" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J158" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K158" t="str">
-        <v>none</v>
+      <c r="I158" t="s">
+        <v>19</v>
+      </c>
+      <c r="J158" t="s">
+        <v>29</v>
+      </c>
+      <c r="K158" t="s">
+        <v>16</v>
       </c>
       <c r="L158">
         <v>0</v>
       </c>
-      <c r="M158" t="str">
-        <v>2026-02-19T01:39:12.540Z</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>TALON</v>
+      <c r="M158" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>272</v>
       </c>
       <c r="B159">
         <v>4</v>
@@ -6891,7 +7782,7 @@
         <v>5</v>
       </c>
       <c r="E159">
-        <v>983.9905713816794</v>
+        <v>983.99057138167939</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -6902,25 +7793,25 @@
       <c r="H159">
         <v>0</v>
       </c>
-      <c r="I159" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J159" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K159" t="str">
-        <v>none</v>
+      <c r="I159" t="s">
+        <v>19</v>
+      </c>
+      <c r="J159" t="s">
+        <v>15</v>
+      </c>
+      <c r="K159" t="s">
+        <v>16</v>
       </c>
       <c r="L159">
         <v>0</v>
       </c>
-      <c r="M159" t="str">
-        <v>2026-02-28T06:27:14.538Z</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>NAVI Junior</v>
+      <c r="M159" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>274</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -6932,7 +7823,7 @@
         <v>6</v>
       </c>
       <c r="E160">
-        <v>983.2698348870488</v>
+        <v>983.26983488704877</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -6943,25 +7834,25 @@
       <c r="H160">
         <v>0</v>
       </c>
-      <c r="I160" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J160" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K160" t="str">
-        <v>none</v>
+      <c r="I160" t="s">
+        <v>19</v>
+      </c>
+      <c r="J160" t="s">
+        <v>29</v>
+      </c>
+      <c r="K160" t="s">
+        <v>16</v>
       </c>
       <c r="L160">
         <v>0</v>
       </c>
-      <c r="M160" t="str">
-        <v>2026-02-28T06:27:03.939Z</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>Ninjas in Pyjamas</v>
+      <c r="M160" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>276</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -6984,25 +7875,25 @@
       <c r="H161">
         <v>0</v>
       </c>
-      <c r="I161" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J161" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K161" t="str">
-        <v>none</v>
+      <c r="I161" t="s">
+        <v>19</v>
+      </c>
+      <c r="J161" t="s">
+        <v>29</v>
+      </c>
+      <c r="K161" t="s">
+        <v>16</v>
       </c>
       <c r="L161">
         <v>0</v>
       </c>
-      <c r="M161" t="str">
-        <v>2026-02-19T21:53:46.615Z</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>MOUZ</v>
+      <c r="M161" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>278</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -7025,25 +7916,25 @@
       <c r="H162">
         <v>0</v>
       </c>
-      <c r="I162" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J162" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K162" t="str">
-        <v>none</v>
+      <c r="I162" t="s">
+        <v>19</v>
+      </c>
+      <c r="J162" t="s">
+        <v>29</v>
+      </c>
+      <c r="K162" t="s">
+        <v>16</v>
       </c>
       <c r="L162">
         <v>0</v>
       </c>
-      <c r="M162" t="str">
-        <v>2026-02-19T21:53:40.004Z</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>Aurora</v>
+      <c r="M162" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>280</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -7066,25 +7957,25 @@
       <c r="H163">
         <v>0</v>
       </c>
-      <c r="I163" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J163" t="str">
-        <v>AS/SIS/ESEA</v>
-      </c>
-      <c r="K163" t="str">
-        <v>none</v>
+      <c r="I163" t="s">
+        <v>19</v>
+      </c>
+      <c r="J163" t="s">
+        <v>29</v>
+      </c>
+      <c r="K163" t="s">
+        <v>16</v>
       </c>
       <c r="L163">
         <v>0</v>
       </c>
-      <c r="M163" t="str">
-        <v>2026-02-19T21:53:30.387Z</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>Reason</v>
+      <c r="M163" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>282</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -7107,25 +7998,25 @@
       <c r="H164">
         <v>0</v>
       </c>
-      <c r="I164" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J164" t="str">
-        <v>EU</v>
-      </c>
-      <c r="K164" t="str">
-        <v>none</v>
+      <c r="I164" t="s">
+        <v>19</v>
+      </c>
+      <c r="J164" t="s">
+        <v>29</v>
+      </c>
+      <c r="K164" t="s">
+        <v>16</v>
       </c>
       <c r="L164">
         <v>0</v>
       </c>
-      <c r="M164" t="str">
-        <v>2026-02-19T21:53:23.315Z</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v>Legacy</v>
+      <c r="M164" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>284</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -7137,7 +8028,7 @@
         <v>3</v>
       </c>
       <c r="E165">
-        <v>957.5159098824421</v>
+        <v>957.51590988244209</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -7148,25 +8039,26 @@
       <c r="H165">
         <v>0</v>
       </c>
-      <c r="I165" t="str">
-        <v>Tier 3</v>
-      </c>
-      <c r="J165" t="str">
-        <v>AM</v>
-      </c>
-      <c r="K165" t="str">
-        <v>none</v>
+      <c r="I165" t="s">
+        <v>19</v>
+      </c>
+      <c r="J165" t="s">
+        <v>20</v>
+      </c>
+      <c r="K165" t="s">
+        <v>16</v>
       </c>
       <c r="L165">
         <v>0</v>
       </c>
-      <c r="M165" t="str">
-        <v>2026-02-19T01:45:20.251Z</v>
+      <c r="M165" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M165"/>
+    <ignoredError sqref="A1:M1 A56:I83 B55:I55 A85:I165 B84:I84 A2:I54 K2:M54 K56:M83 K55:M55 K85:M165 K84:M84" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7547AC-67E1-4856-8D15-30D70D3C528D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93750565-95F6-43EB-B7EC-8BC119098A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5055" yWindow="2505" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5745" yWindow="3195" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ranking" sheetId="1" r:id="rId1"/>
@@ -235,9 +235,6 @@
     <t>Copenhagen Wolves</t>
   </si>
   <si>
-    <t>Counter Logic Games</t>
-  </si>
-  <si>
     <t>ENCE Academy</t>
   </si>
   <si>
@@ -896,6 +893,9 @@
   </si>
   <si>
     <t>Chinggis Warriors</t>
+  </si>
+  <si>
+    <t>Counter Logic</t>
   </si>
 </sst>
 </file>
@@ -1319,16 +1319,16 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O1" t="s">
         <v>286</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>287</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>288</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -2768,7 +2768,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>291</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2850,7 +2850,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3424,7 +3424,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3588,7 +3588,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3629,7 +3629,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3998,7 +3998,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4367,7 +4367,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -4449,7 +4449,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4485,12 +4485,12 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4526,12 +4526,12 @@
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4567,12 +4567,12 @@
         <v>0</v>
       </c>
       <c r="M80" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -4608,12 +4608,12 @@
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -4649,12 +4649,12 @@
         <v>0</v>
       </c>
       <c r="M82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -4690,12 +4690,12 @@
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -4731,12 +4731,12 @@
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -4772,12 +4772,12 @@
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4813,12 +4813,12 @@
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4854,12 +4854,12 @@
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -4895,12 +4895,12 @@
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -4936,12 +4936,12 @@
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -4977,12 +4977,12 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -5018,12 +5018,12 @@
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -5059,12 +5059,12 @@
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -5100,12 +5100,12 @@
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -5141,12 +5141,12 @@
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -5182,12 +5182,12 @@
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -5223,12 +5223,12 @@
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5264,12 +5264,12 @@
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5305,12 +5305,12 @@
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5346,12 +5346,12 @@
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5387,12 +5387,12 @@
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5428,12 +5428,12 @@
         <v>0</v>
       </c>
       <c r="M101" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5469,12 +5469,12 @@
         <v>0</v>
       </c>
       <c r="M102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5510,12 +5510,12 @@
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5551,12 +5551,12 @@
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5592,12 +5592,12 @@
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -5633,12 +5633,12 @@
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -5674,12 +5674,12 @@
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -5715,12 +5715,12 @@
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -5756,12 +5756,12 @@
         <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -5797,12 +5797,12 @@
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -5838,12 +5838,12 @@
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -5879,12 +5879,12 @@
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -5920,12 +5920,12 @@
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -5961,12 +5961,12 @@
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6002,12 +6002,12 @@
         <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6043,12 +6043,12 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6084,12 +6084,12 @@
         <v>0</v>
       </c>
       <c r="M117" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6125,12 +6125,12 @@
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6166,12 +6166,12 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6207,12 +6207,12 @@
         <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6248,12 +6248,12 @@
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6289,12 +6289,12 @@
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6330,12 +6330,12 @@
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6371,12 +6371,12 @@
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -6412,12 +6412,12 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -6453,12 +6453,12 @@
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -6494,12 +6494,12 @@
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -6535,12 +6535,12 @@
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -6576,12 +6576,12 @@
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -6617,12 +6617,12 @@
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -6658,12 +6658,12 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -6699,12 +6699,12 @@
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -6740,12 +6740,12 @@
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -6781,12 +6781,12 @@
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -6822,12 +6822,12 @@
         <v>0</v>
       </c>
       <c r="M135" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -6863,12 +6863,12 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -6904,12 +6904,12 @@
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -6945,12 +6945,12 @@
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -6986,12 +6986,12 @@
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -7027,12 +7027,12 @@
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -7068,12 +7068,12 @@
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -7109,12 +7109,12 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -7150,12 +7150,12 @@
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7191,12 +7191,12 @@
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7232,12 +7232,12 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7273,12 +7273,12 @@
         <v>0</v>
       </c>
       <c r="M146" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7314,12 +7314,12 @@
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7355,12 +7355,12 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7396,12 +7396,12 @@
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7437,12 +7437,12 @@
         <v>0</v>
       </c>
       <c r="M150" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7478,12 +7478,12 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7519,12 +7519,12 @@
         <v>0</v>
       </c>
       <c r="M152" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7560,12 +7560,12 @@
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7601,12 +7601,12 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7642,12 +7642,12 @@
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7683,12 +7683,12 @@
         <v>0</v>
       </c>
       <c r="M156" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7724,12 +7724,12 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7765,12 +7765,12 @@
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B159">
         <v>4</v>
@@ -7806,12 +7806,12 @@
         <v>0</v>
       </c>
       <c r="M159" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -7847,12 +7847,12 @@
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -7888,12 +7888,12 @@
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -7929,12 +7929,12 @@
         <v>0</v>
       </c>
       <c r="M162" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -7970,12 +7970,12 @@
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -8011,12 +8011,12 @@
         <v>0</v>
       </c>
       <c r="M164" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -8052,13 +8052,13 @@
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M1 A56:I83 B55:I55 A85:I165 B84:I84 A2:I54 K2:M54 K56:M83 K55:M55 K85:M165 K84:M84" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M1 A56:I83 B55:I55 A85:I165 B84:I84 A2:I36 K2:M54 K56:M83 K55:M55 K85:M165 K84:M84 A38:I54 B37:I37" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckkil\Documents\GitHub\ck-tools\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93750565-95F6-43EB-B7EC-8BC119098A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70671D8-D42B-4A3C-A7AD-60F89E1B5E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5745" yWindow="3195" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ranking" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="292">
   <si>
     <t>Team</t>
   </si>
@@ -61,6 +61,18 @@
     <t>LastUpdated</t>
   </si>
   <si>
+    <t>4 star</t>
+  </si>
+  <si>
+    <t>3 star</t>
+  </si>
+  <si>
+    <t>2 star</t>
+  </si>
+  <si>
+    <t>1 star</t>
+  </si>
+  <si>
     <t>The MongolZ</t>
   </si>
   <si>
@@ -73,102 +85,105 @@
     <t>none</t>
   </si>
   <si>
-    <t>2026-02-28T06:37:50.179Z</t>
+    <t>2026-03-21T04:31:17.566Z</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Iluminar</t>
   </si>
   <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:31:26.612Z</t>
+  </si>
+  <si>
+    <t>Nemiga</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:31:46.138Z</t>
+  </si>
+  <si>
+    <t>Elevate</t>
+  </si>
+  <si>
     <t>Tier 3</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:37:58.230Z</t>
+    <t>2026-03-21T04:32:15.700Z</t>
+  </si>
+  <si>
+    <t>Vitality</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:31:36.203Z</t>
   </si>
   <si>
     <t>Liquid</t>
   </si>
   <si>
-    <t>2026-02-28T06:37:26.757Z</t>
-  </si>
-  <si>
     <t>Titan</t>
   </si>
   <si>
-    <t>2026-02-28T06:37:39.250Z</t>
-  </si>
-  <si>
-    <t>Nemiga</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:38:23.828Z</t>
+    <t>Copenhagen Flames</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:32:33.790Z</t>
   </si>
   <si>
     <t>Eternal Fire</t>
   </si>
   <si>
-    <t>EU</t>
-  </si>
-  <si>
-    <t>Elevate</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:38:40.257Z</t>
+    <t>2026-03-21T04:31:59.142Z</t>
+  </si>
+  <si>
+    <t>Falcons</t>
   </si>
   <si>
     <t>PARIVISION</t>
   </si>
   <si>
-    <t>Vitality</t>
-  </si>
-  <si>
     <t>Natus Vincere</t>
   </si>
   <si>
+    <t>Cloud9</t>
+  </si>
+  <si>
+    <t>2026-03-21T04:32:26.020Z</t>
+  </si>
+  <si>
     <t>Heroic</t>
   </si>
   <si>
-    <t>2026-02-28T06:38:48.174Z</t>
-  </si>
-  <si>
-    <t>Copenhagen Flames</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:38:31.762Z</t>
-  </si>
-  <si>
     <t>Verdant</t>
   </si>
   <si>
     <t>2026-02-28T06:29:24.671Z</t>
   </si>
   <si>
-    <t>Falcons</t>
+    <t>Bounty Hunters</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:28:59.888Z</t>
   </si>
   <si>
     <t>Spirit</t>
   </si>
   <si>
-    <t>Cloud9</t>
+    <t>The Huns</t>
+  </si>
+  <si>
+    <t>2026-02-18T21:21:06.168Z</t>
   </si>
   <si>
     <t>Onyx Ravens</t>
   </si>
   <si>
-    <t>Bounty Hunters</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:28:59.888Z</t>
-  </si>
-  <si>
-    <t>The Huns</t>
-  </si>
-  <si>
-    <t>2026-02-18T21:21:06.168Z</t>
-  </si>
-  <si>
     <t>TYLOO</t>
   </si>
   <si>
@@ -202,9 +217,6 @@
     <t>00 Nation</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>100 Thieves</t>
   </si>
   <si>
@@ -286,6 +298,9 @@
     <t>kONO</t>
   </si>
   <si>
+    <t>LGB</t>
+  </si>
+  <si>
     <t>MAD Lions</t>
   </si>
   <si>
@@ -388,6 +403,9 @@
     <t>2026-02-19T01:45:45.455Z</t>
   </si>
   <si>
+    <t>Chinggis Warriors</t>
+  </si>
+  <si>
     <t>2026-02-19T22:08:18.806Z</t>
   </si>
   <si>
@@ -875,24 +893,6 @@
   </si>
   <si>
     <t>2026-02-19T01:45:20.251Z</t>
-  </si>
-  <si>
-    <t>4 star</t>
-  </si>
-  <si>
-    <t>3 star</t>
-  </si>
-  <si>
-    <t>2 star</t>
-  </si>
-  <si>
-    <t>1 star</t>
-  </si>
-  <si>
-    <t>LGB</t>
-  </si>
-  <si>
-    <t>Chinggis Warriors</t>
   </si>
   <si>
     <t>Counter Logic</t>
@@ -1275,7 +1275,7 @@
   <dimension ref="A1:Q165"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1319,33 +1319,33 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>285</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>286</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>287</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>288</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1103.5396883405394</v>
+        <v>1118.935353572816</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1357,77 +1357,101 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1110.4490389924551</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1094.2205166212659</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1093.7510210031935</v>
+        <v>1102.2670104875274</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1439,36 +1463,48 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1090.4930427442032</v>
+        <v>1087.1014484109633</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1480,36 +1516,48 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1088.1168262682929</v>
+        <v>1077.6235341337183</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1521,36 +1569,48 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>1073.614299461236</v>
+        <v>1077.5224986320043</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1562,36 +1622,48 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>1072.1962700599079</v>
+        <v>1075.2807088818799</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1603,77 +1675,101 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>1070.290679853573</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" t="s">
         <v>32</v>
       </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1063.3157624288613</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>29</v>
-      </c>
       <c r="K9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>1062.7199050958704</v>
+        <v>1056.9314284733287</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1685,36 +1781,48 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>39</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>1062.0404218180502</v>
+        <v>1051.4823754499648</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1726,36 +1834,48 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1060.4876942715719</v>
+        <v>1048.6990812898496</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1767,36 +1887,48 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>1056.483574632495</v>
+        <v>1048.1641215202962</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1808,36 +1940,48 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>38</v>
+        <v>27</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>1038.7190184710753</v>
+        <v>1045.8673946600638</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1849,36 +1993,48 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" t="s">
         <v>19</v>
       </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
       <c r="K14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>40</v>
+        <v>44</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15">
-        <v>1034.4702257617066</v>
+        <v>1045.2899043783382</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1890,36 +2046,48 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>38</v>
+        <v>33</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <v>4</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
       <c r="E16">
-        <v>1031.7815101827721</v>
+        <v>1038.7190184710753</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1931,159 +2099,207 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="N16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>1017.2412711985547</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>1016.7402640066111</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1015</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" t="s">
+        <v>22</v>
+      </c>
+      <c r="O19" t="s">
+        <v>22</v>
+      </c>
+      <c r="P19" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20">
         <v>7</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17">
-        <v>1030.8261484839029</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18">
-        <v>1028.7948309045817</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" t="s">
-        <v>16</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19">
-        <v>5</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19">
-        <v>1017.2412711985547</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>1015</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2095,24 +2311,36 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="N20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -2136,24 +2364,36 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" t="s">
         <v>19</v>
       </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="N21" t="s">
+        <v>22</v>
+      </c>
+      <c r="O21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -2177,24 +2417,36 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J22" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="N22" t="s">
+        <v>22</v>
+      </c>
+      <c r="O22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P22" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -2218,24 +2470,36 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="N23" t="s">
+        <v>22</v>
+      </c>
+      <c r="O23" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -2259,24 +2523,36 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="N24" t="s">
+        <v>22</v>
+      </c>
+      <c r="O24" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -2300,24 +2576,36 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="N25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O25" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2341,24 +2629,36 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J26" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O26" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2382,24 +2682,36 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s">
+        <v>22</v>
+      </c>
+      <c r="O27" t="s">
+        <v>22</v>
+      </c>
+      <c r="P27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2423,24 +2735,36 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J28" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K28" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2464,24 +2788,36 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K29" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s">
+        <v>22</v>
+      </c>
+      <c r="O29" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2505,24 +2841,36 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J30" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s">
+        <v>22</v>
+      </c>
+      <c r="O30" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2546,24 +2894,36 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s">
+        <v>22</v>
+      </c>
+      <c r="O31" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2587,24 +2947,36 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" t="s">
         <v>19</v>
       </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
       <c r="K32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s">
+        <v>22</v>
+      </c>
+      <c r="O32" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2628,24 +3000,36 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N33" t="s">
+        <v>22</v>
+      </c>
+      <c r="O33" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2669,24 +3053,36 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J34" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N34" t="s">
+        <v>22</v>
+      </c>
+      <c r="O34" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2710,24 +3106,36 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35" t="s">
         <v>19</v>
       </c>
-      <c r="J35" t="s">
-        <v>15</v>
-      </c>
       <c r="K35" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N35" t="s">
+        <v>22</v>
+      </c>
+      <c r="O35" t="s">
+        <v>22</v>
+      </c>
+      <c r="P35" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2751,22 +3159,34 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J36" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N36" t="s">
+        <v>22</v>
+      </c>
+      <c r="O36" t="s">
+        <v>22</v>
+      </c>
+      <c r="P36" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>291</v>
       </c>
@@ -2792,24 +3212,36 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J37" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K37" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N37" t="s">
+        <v>22</v>
+      </c>
+      <c r="O37" t="s">
+        <v>22</v>
+      </c>
+      <c r="P37" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2833,24 +3265,36 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J38" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
+        <v>22</v>
+      </c>
+      <c r="O38" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2874,24 +3318,36 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J39" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K39" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N39" t="s">
+        <v>22</v>
+      </c>
+      <c r="O39" t="s">
+        <v>22</v>
+      </c>
+      <c r="P39" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2915,24 +3371,36 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J40" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K40" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N40" t="s">
+        <v>22</v>
+      </c>
+      <c r="O40" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2956,24 +3424,36 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J41" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N41" t="s">
+        <v>22</v>
+      </c>
+      <c r="O41" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2997,24 +3477,36 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J42" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N42" t="s">
+        <v>22</v>
+      </c>
+      <c r="O42" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3038,24 +3530,36 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J43" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N43" t="s">
+        <v>22</v>
+      </c>
+      <c r="O43" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3079,24 +3583,36 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
+        <v>29</v>
+      </c>
+      <c r="J44" t="s">
         <v>19</v>
       </c>
-      <c r="J44" t="s">
-        <v>15</v>
-      </c>
       <c r="K44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N44" t="s">
+        <v>22</v>
+      </c>
+      <c r="O44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3120,24 +3636,36 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J45" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N45" t="s">
+        <v>22</v>
+      </c>
+      <c r="O45" t="s">
+        <v>22</v>
+      </c>
+      <c r="P45" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3161,24 +3689,36 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" t="s">
         <v>19</v>
       </c>
-      <c r="J46" t="s">
-        <v>15</v>
-      </c>
       <c r="K46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N46" t="s">
+        <v>22</v>
+      </c>
+      <c r="O46" t="s">
+        <v>22</v>
+      </c>
+      <c r="P46" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3202,24 +3742,36 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J47" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K47" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N47" t="s">
+        <v>22</v>
+      </c>
+      <c r="O47" t="s">
+        <v>22</v>
+      </c>
+      <c r="P47" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3243,24 +3795,36 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J48" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K48" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3284,24 +3848,36 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J49" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K49" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N49" t="s">
+        <v>22</v>
+      </c>
+      <c r="O49" t="s">
+        <v>22</v>
+      </c>
+      <c r="P49" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3325,24 +3901,36 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J50" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K50" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N50" t="s">
+        <v>22</v>
+      </c>
+      <c r="O50" t="s">
+        <v>22</v>
+      </c>
+      <c r="P50" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3366,24 +3954,36 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N51" t="s">
+        <v>22</v>
+      </c>
+      <c r="O51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P51" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3407,24 +4007,36 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J52" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K52" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N52" t="s">
+        <v>22</v>
+      </c>
+      <c r="O52" t="s">
+        <v>22</v>
+      </c>
+      <c r="P52" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3448,24 +4060,36 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J53" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K53" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N53" t="s">
+        <v>22</v>
+      </c>
+      <c r="O53" t="s">
+        <v>22</v>
+      </c>
+      <c r="P53" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3489,24 +4113,36 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" t="s">
         <v>19</v>
       </c>
-      <c r="J54" t="s">
-        <v>15</v>
-      </c>
       <c r="K54" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N54" t="s">
+        <v>22</v>
+      </c>
+      <c r="O54" t="s">
+        <v>22</v>
+      </c>
+      <c r="P54" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>289</v>
+        <v>92</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3530,24 +4166,36 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
+        <v>29</v>
+      </c>
+      <c r="J55" t="s">
         <v>19</v>
       </c>
-      <c r="J55" t="s">
-        <v>15</v>
-      </c>
       <c r="K55" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N55" t="s">
+        <v>22</v>
+      </c>
+      <c r="O55" t="s">
+        <v>22</v>
+      </c>
+      <c r="P55" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3571,24 +4219,36 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J56" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N56" t="s">
+        <v>22</v>
+      </c>
+      <c r="O56" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3612,24 +4272,36 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K57" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N57" t="s">
+        <v>22</v>
+      </c>
+      <c r="O57" t="s">
+        <v>22</v>
+      </c>
+      <c r="P57" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3653,24 +4325,36 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K58" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N58" t="s">
+        <v>22</v>
+      </c>
+      <c r="O58" t="s">
+        <v>22</v>
+      </c>
+      <c r="P58" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3694,24 +4378,36 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J59" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K59" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N59" t="s">
+        <v>22</v>
+      </c>
+      <c r="O59" t="s">
+        <v>22</v>
+      </c>
+      <c r="P59" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3735,24 +4431,36 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J60" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K60" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N60" t="s">
+        <v>22</v>
+      </c>
+      <c r="O60" t="s">
+        <v>22</v>
+      </c>
+      <c r="P60" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3776,24 +4484,36 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J61" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K61" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N61" t="s">
+        <v>22</v>
+      </c>
+      <c r="O61" t="s">
+        <v>22</v>
+      </c>
+      <c r="P61" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3817,24 +4537,36 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J62" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K62" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N62" t="s">
+        <v>22</v>
+      </c>
+      <c r="O62" t="s">
+        <v>22</v>
+      </c>
+      <c r="P62" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3858,24 +4590,36 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J63" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K63" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N63" t="s">
+        <v>22</v>
+      </c>
+      <c r="O63" t="s">
+        <v>22</v>
+      </c>
+      <c r="P63" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3899,24 +4643,36 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J64" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K64" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N64" t="s">
+        <v>22</v>
+      </c>
+      <c r="O64" t="s">
+        <v>22</v>
+      </c>
+      <c r="P64" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3940,24 +4696,36 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J65" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K65" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N65" t="s">
+        <v>22</v>
+      </c>
+      <c r="O65" t="s">
+        <v>22</v>
+      </c>
+      <c r="P65" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3981,24 +4749,36 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N66" t="s">
+        <v>22</v>
+      </c>
+      <c r="O66" t="s">
+        <v>22</v>
+      </c>
+      <c r="P66" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -4022,24 +4802,36 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J67" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N67" t="s">
+        <v>22</v>
+      </c>
+      <c r="O67" t="s">
+        <v>22</v>
+      </c>
+      <c r="P67" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -4063,24 +4855,36 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J68" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K68" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N68" t="s">
+        <v>22</v>
+      </c>
+      <c r="O68" t="s">
+        <v>22</v>
+      </c>
+      <c r="P68" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4104,24 +4908,36 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
+        <v>29</v>
+      </c>
+      <c r="J69" t="s">
         <v>19</v>
       </c>
-      <c r="J69" t="s">
-        <v>15</v>
-      </c>
       <c r="K69" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="M69" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N69" t="s">
+        <v>22</v>
+      </c>
+      <c r="O69" t="s">
+        <v>22</v>
+      </c>
+      <c r="P69" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4145,24 +4961,36 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" t="s">
         <v>19</v>
       </c>
-      <c r="J70" t="s">
-        <v>15</v>
-      </c>
       <c r="K70" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N70" t="s">
+        <v>22</v>
+      </c>
+      <c r="O70" t="s">
+        <v>22</v>
+      </c>
+      <c r="P70" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4186,24 +5014,36 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J71" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K71" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N71" t="s">
+        <v>22</v>
+      </c>
+      <c r="O71" t="s">
+        <v>22</v>
+      </c>
+      <c r="P71" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4227,24 +5067,36 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J72" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K72" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L72">
         <v>0</v>
       </c>
       <c r="M72" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N72" t="s">
+        <v>22</v>
+      </c>
+      <c r="O72" t="s">
+        <v>22</v>
+      </c>
+      <c r="P72" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4268,24 +5120,36 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J73" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K73" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N73" t="s">
+        <v>22</v>
+      </c>
+      <c r="O73" t="s">
+        <v>22</v>
+      </c>
+      <c r="P73" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4309,24 +5173,36 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J74" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K74" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L74">
         <v>0</v>
       </c>
       <c r="M74" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N74" t="s">
+        <v>22</v>
+      </c>
+      <c r="O74" t="s">
+        <v>22</v>
+      </c>
+      <c r="P74" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4350,24 +5226,36 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J75" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K75" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L75">
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N75" t="s">
+        <v>22</v>
+      </c>
+      <c r="O75" t="s">
+        <v>22</v>
+      </c>
+      <c r="P75" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -4391,24 +5279,36 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J76" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K76" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N76" t="s">
+        <v>22</v>
+      </c>
+      <c r="O76" t="s">
+        <v>22</v>
+      </c>
+      <c r="P76" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -4432,24 +5332,36 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J77" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K77" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L77">
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="N77" t="s">
+        <v>22</v>
+      </c>
+      <c r="O77" t="s">
+        <v>22</v>
+      </c>
+      <c r="P77" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4473,24 +5385,36 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
+        <v>29</v>
+      </c>
+      <c r="J78" t="s">
         <v>19</v>
       </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
       <c r="K78" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="N78" t="s">
+        <v>22</v>
+      </c>
+      <c r="O78" t="s">
+        <v>22</v>
+      </c>
+      <c r="P78" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4514,24 +5438,36 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J79" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K79" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="N79" t="s">
+        <v>22</v>
+      </c>
+      <c r="O79" t="s">
+        <v>22</v>
+      </c>
+      <c r="P79" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4555,24 +5491,36 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J80" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K80" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
       <c r="M80" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N80" t="s">
+        <v>22</v>
+      </c>
+      <c r="O80" t="s">
+        <v>22</v>
+      </c>
+      <c r="P80" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -4596,24 +5544,36 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J81" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K81" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L81">
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="N81" t="s">
+        <v>22</v>
+      </c>
+      <c r="O81" t="s">
+        <v>22</v>
+      </c>
+      <c r="P81" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -4637,24 +5597,36 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J82" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K82" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="N82" t="s">
+        <v>22</v>
+      </c>
+      <c r="O82" t="s">
+        <v>22</v>
+      </c>
+      <c r="P82" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -4678,24 +5650,36 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J83" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="N83" t="s">
+        <v>22</v>
+      </c>
+      <c r="O83" t="s">
+        <v>22</v>
+      </c>
+      <c r="P83" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>290</v>
+        <v>127</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -4719,24 +5703,36 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
+        <v>29</v>
+      </c>
+      <c r="J84" t="s">
         <v>19</v>
       </c>
-      <c r="J84" t="s">
-        <v>15</v>
-      </c>
       <c r="K84" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L84">
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="N84" t="s">
+        <v>22</v>
+      </c>
+      <c r="O84" t="s">
+        <v>22</v>
+      </c>
+      <c r="P84" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -4760,24 +5756,36 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J85" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K85" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L85">
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="N85" t="s">
+        <v>22</v>
+      </c>
+      <c r="O85" t="s">
+        <v>22</v>
+      </c>
+      <c r="P85" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4801,24 +5809,36 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J86" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K86" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="N86" t="s">
+        <v>22</v>
+      </c>
+      <c r="O86" t="s">
+        <v>22</v>
+      </c>
+      <c r="P86" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4842,24 +5862,36 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J87" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K87" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="N87" t="s">
+        <v>22</v>
+      </c>
+      <c r="O87" t="s">
+        <v>22</v>
+      </c>
+      <c r="P87" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -4883,24 +5915,36 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J88" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K88" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N88" t="s">
+        <v>22</v>
+      </c>
+      <c r="O88" t="s">
+        <v>22</v>
+      </c>
+      <c r="P88" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -4924,24 +5968,36 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J89" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K89" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="N89" t="s">
+        <v>22</v>
+      </c>
+      <c r="O89" t="s">
+        <v>22</v>
+      </c>
+      <c r="P89" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -4965,24 +6021,36 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J90" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K90" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L90">
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="N90" t="s">
+        <v>22</v>
+      </c>
+      <c r="O90" t="s">
+        <v>22</v>
+      </c>
+      <c r="P90" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -5006,24 +6074,36 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J91" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="N91" t="s">
+        <v>22</v>
+      </c>
+      <c r="O91" t="s">
+        <v>22</v>
+      </c>
+      <c r="P91" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -5047,24 +6127,36 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J92" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K92" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L92">
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+      <c r="N92" t="s">
+        <v>22</v>
+      </c>
+      <c r="O92" t="s">
+        <v>22</v>
+      </c>
+      <c r="P92" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -5088,24 +6180,36 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J93" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K93" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L93">
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="N93" t="s">
+        <v>22</v>
+      </c>
+      <c r="O93" t="s">
+        <v>22</v>
+      </c>
+      <c r="P93" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -5129,24 +6233,36 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J94" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K94" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="N94" t="s">
+        <v>22</v>
+      </c>
+      <c r="O94" t="s">
+        <v>22</v>
+      </c>
+      <c r="P94" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -5170,24 +6286,36 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J95" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K95" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L95">
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="N95" t="s">
+        <v>22</v>
+      </c>
+      <c r="O95" t="s">
+        <v>22</v>
+      </c>
+      <c r="P95" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -5211,24 +6339,36 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J96" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K96" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="N96" t="s">
+        <v>22</v>
+      </c>
+      <c r="O96" t="s">
+        <v>22</v>
+      </c>
+      <c r="P96" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5252,24 +6392,36 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
+        <v>29</v>
+      </c>
+      <c r="J97" t="s">
         <v>19</v>
       </c>
-      <c r="J97" t="s">
-        <v>15</v>
-      </c>
       <c r="K97" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L97">
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="N97" t="s">
+        <v>22</v>
+      </c>
+      <c r="O97" t="s">
+        <v>22</v>
+      </c>
+      <c r="P97" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5293,24 +6445,36 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J98" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K98" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="N98" t="s">
+        <v>22</v>
+      </c>
+      <c r="O98" t="s">
+        <v>22</v>
+      </c>
+      <c r="P98" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5334,24 +6498,36 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
+        <v>29</v>
+      </c>
+      <c r="J99" t="s">
         <v>19</v>
       </c>
-      <c r="J99" t="s">
-        <v>15</v>
-      </c>
       <c r="K99" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L99">
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="N99" t="s">
+        <v>22</v>
+      </c>
+      <c r="O99" t="s">
+        <v>22</v>
+      </c>
+      <c r="P99" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5375,24 +6551,36 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J100" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K100" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L100">
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="N100" t="s">
+        <v>22</v>
+      </c>
+      <c r="O100" t="s">
+        <v>22</v>
+      </c>
+      <c r="P100" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5416,24 +6604,36 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J101" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K101" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L101">
         <v>0</v>
       </c>
       <c r="M101" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="N101" t="s">
+        <v>22</v>
+      </c>
+      <c r="O101" t="s">
+        <v>22</v>
+      </c>
+      <c r="P101" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5457,24 +6657,36 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J102" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K102" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L102">
         <v>0</v>
       </c>
       <c r="M102" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="N102" t="s">
+        <v>22</v>
+      </c>
+      <c r="O102" t="s">
+        <v>22</v>
+      </c>
+      <c r="P102" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5498,24 +6710,36 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
+        <v>29</v>
+      </c>
+      <c r="J103" t="s">
         <v>19</v>
       </c>
-      <c r="J103" t="s">
-        <v>15</v>
-      </c>
       <c r="K103" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L103">
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="N103" t="s">
+        <v>22</v>
+      </c>
+      <c r="O103" t="s">
+        <v>22</v>
+      </c>
+      <c r="P103" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5539,24 +6763,36 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J104" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K104" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L104">
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="N104" t="s">
+        <v>22</v>
+      </c>
+      <c r="O104" t="s">
+        <v>22</v>
+      </c>
+      <c r="P104" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5580,24 +6816,36 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J105" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K105" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L105">
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="N105" t="s">
+        <v>22</v>
+      </c>
+      <c r="O105" t="s">
+        <v>22</v>
+      </c>
+      <c r="P105" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -5621,24 +6869,36 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J106" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K106" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="N106" t="s">
+        <v>22</v>
+      </c>
+      <c r="O106" t="s">
+        <v>22</v>
+      </c>
+      <c r="P106" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -5662,24 +6922,36 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J107" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K107" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L107">
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="N107" t="s">
+        <v>22</v>
+      </c>
+      <c r="O107" t="s">
+        <v>22</v>
+      </c>
+      <c r="P107" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -5703,24 +6975,36 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J108" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K108" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L108">
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="N108" t="s">
+        <v>22</v>
+      </c>
+      <c r="O108" t="s">
+        <v>22</v>
+      </c>
+      <c r="P108" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -5744,24 +7028,36 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J109" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K109" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L109">
         <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="N109" t="s">
+        <v>22</v>
+      </c>
+      <c r="O109" t="s">
+        <v>22</v>
+      </c>
+      <c r="P109" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -5785,24 +7081,36 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J110" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K110" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L110">
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N110" t="s">
+        <v>22</v>
+      </c>
+      <c r="O110" t="s">
+        <v>22</v>
+      </c>
+      <c r="P110" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -5826,24 +7134,36 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J111" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K111" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L111">
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="N111" t="s">
+        <v>22</v>
+      </c>
+      <c r="O111" t="s">
+        <v>22</v>
+      </c>
+      <c r="P111" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -5867,24 +7187,36 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J112" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K112" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L112">
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="N112" t="s">
+        <v>22</v>
+      </c>
+      <c r="O112" t="s">
+        <v>22</v>
+      </c>
+      <c r="P112" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -5908,24 +7240,36 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J113" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K113" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L113">
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="N113" t="s">
+        <v>22</v>
+      </c>
+      <c r="O113" t="s">
+        <v>22</v>
+      </c>
+      <c r="P113" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -5949,24 +7293,36 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
+        <v>29</v>
+      </c>
+      <c r="J114" t="s">
         <v>19</v>
       </c>
-      <c r="J114" t="s">
-        <v>15</v>
-      </c>
       <c r="K114" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="N114" t="s">
+        <v>22</v>
+      </c>
+      <c r="O114" t="s">
+        <v>22</v>
+      </c>
+      <c r="P114" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -5990,24 +7346,36 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J115" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K115" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="N115" t="s">
+        <v>22</v>
+      </c>
+      <c r="O115" t="s">
+        <v>22</v>
+      </c>
+      <c r="P115" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6031,24 +7399,36 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J116" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K116" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="N116" t="s">
+        <v>22</v>
+      </c>
+      <c r="O116" t="s">
+        <v>22</v>
+      </c>
+      <c r="P116" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6072,24 +7452,36 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
+        <v>29</v>
+      </c>
+      <c r="J117" t="s">
         <v>19</v>
       </c>
-      <c r="J117" t="s">
-        <v>15</v>
-      </c>
       <c r="K117" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="N117" t="s">
+        <v>22</v>
+      </c>
+      <c r="O117" t="s">
+        <v>22</v>
+      </c>
+      <c r="P117" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6113,24 +7505,36 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
+        <v>29</v>
+      </c>
+      <c r="J118" t="s">
         <v>19</v>
       </c>
-      <c r="J118" t="s">
-        <v>15</v>
-      </c>
       <c r="K118" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="N118" t="s">
+        <v>22</v>
+      </c>
+      <c r="O118" t="s">
+        <v>22</v>
+      </c>
+      <c r="P118" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6154,24 +7558,36 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J119" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K119" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="N119" t="s">
+        <v>22</v>
+      </c>
+      <c r="O119" t="s">
+        <v>22</v>
+      </c>
+      <c r="P119" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6195,24 +7611,36 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J120" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K120" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="N120" t="s">
+        <v>22</v>
+      </c>
+      <c r="O120" t="s">
+        <v>22</v>
+      </c>
+      <c r="P120" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6236,24 +7664,36 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J121" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K121" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="N121" t="s">
+        <v>22</v>
+      </c>
+      <c r="O121" t="s">
+        <v>22</v>
+      </c>
+      <c r="P121" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6277,24 +7717,36 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J122" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K122" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="N122" t="s">
+        <v>22</v>
+      </c>
+      <c r="O122" t="s">
+        <v>22</v>
+      </c>
+      <c r="P122" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6318,24 +7770,36 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J123" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K123" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="N123" t="s">
+        <v>22</v>
+      </c>
+      <c r="O123" t="s">
+        <v>22</v>
+      </c>
+      <c r="P123" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6359,24 +7823,36 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J124" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K124" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="N124" t="s">
+        <v>22</v>
+      </c>
+      <c r="O124" t="s">
+        <v>22</v>
+      </c>
+      <c r="P124" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -6400,24 +7876,36 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
+        <v>29</v>
+      </c>
+      <c r="J125" t="s">
         <v>19</v>
       </c>
-      <c r="J125" t="s">
-        <v>15</v>
-      </c>
       <c r="K125" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="N125" t="s">
+        <v>22</v>
+      </c>
+      <c r="O125" t="s">
+        <v>22</v>
+      </c>
+      <c r="P125" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -6441,24 +7929,36 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J126" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K126" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L126">
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="N126" t="s">
+        <v>22</v>
+      </c>
+      <c r="O126" t="s">
+        <v>22</v>
+      </c>
+      <c r="P126" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -6482,24 +7982,36 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J127" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K127" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L127">
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="N127" t="s">
+        <v>22</v>
+      </c>
+      <c r="O127" t="s">
+        <v>22</v>
+      </c>
+      <c r="P127" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -6523,24 +8035,36 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J128" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K128" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+      <c r="N128" t="s">
+        <v>22</v>
+      </c>
+      <c r="O128" t="s">
+        <v>22</v>
+      </c>
+      <c r="P128" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -6564,24 +8088,36 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J129" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K129" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L129">
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="N129" t="s">
+        <v>22</v>
+      </c>
+      <c r="O129" t="s">
+        <v>22</v>
+      </c>
+      <c r="P129" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -6605,24 +8141,36 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
+        <v>29</v>
+      </c>
+      <c r="J130" t="s">
         <v>19</v>
       </c>
-      <c r="J130" t="s">
-        <v>15</v>
-      </c>
       <c r="K130" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="N130" t="s">
+        <v>22</v>
+      </c>
+      <c r="O130" t="s">
+        <v>22</v>
+      </c>
+      <c r="P130" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -6646,24 +8194,36 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J131" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K131" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="N131" t="s">
+        <v>22</v>
+      </c>
+      <c r="O131" t="s">
+        <v>22</v>
+      </c>
+      <c r="P131" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -6687,24 +8247,36 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J132" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K132" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="N132" t="s">
+        <v>22</v>
+      </c>
+      <c r="O132" t="s">
+        <v>22</v>
+      </c>
+      <c r="P132" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -6728,24 +8300,36 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
+        <v>29</v>
+      </c>
+      <c r="J133" t="s">
         <v>19</v>
       </c>
-      <c r="J133" t="s">
-        <v>15</v>
-      </c>
       <c r="K133" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="N133" t="s">
+        <v>22</v>
+      </c>
+      <c r="O133" t="s">
+        <v>22</v>
+      </c>
+      <c r="P133" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -6769,24 +8353,36 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J134" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K134" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="N134" t="s">
+        <v>22</v>
+      </c>
+      <c r="O134" t="s">
+        <v>22</v>
+      </c>
+      <c r="P134" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -6810,24 +8406,36 @@
         <v>0</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J135" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K135" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="N135" t="s">
+        <v>22</v>
+      </c>
+      <c r="O135" t="s">
+        <v>22</v>
+      </c>
+      <c r="P135" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -6851,24 +8459,36 @@
         <v>0</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J136" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K136" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="N136" t="s">
+        <v>22</v>
+      </c>
+      <c r="O136" t="s">
+        <v>22</v>
+      </c>
+      <c r="P136" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -6892,24 +8512,36 @@
         <v>0</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J137" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K137" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="N137" t="s">
+        <v>22</v>
+      </c>
+      <c r="O137" t="s">
+        <v>22</v>
+      </c>
+      <c r="P137" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -6933,24 +8565,36 @@
         <v>0</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J138" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K138" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="N138" t="s">
+        <v>22</v>
+      </c>
+      <c r="O138" t="s">
+        <v>22</v>
+      </c>
+      <c r="P138" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -6974,24 +8618,36 @@
         <v>0</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J139" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K139" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+      <c r="N139" t="s">
+        <v>22</v>
+      </c>
+      <c r="O139" t="s">
+        <v>22</v>
+      </c>
+      <c r="P139" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -7015,24 +8671,36 @@
         <v>0</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J140" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K140" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="N140" t="s">
+        <v>22</v>
+      </c>
+      <c r="O140" t="s">
+        <v>22</v>
+      </c>
+      <c r="P140" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -7056,24 +8724,36 @@
         <v>0</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J141" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K141" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="N141" t="s">
+        <v>22</v>
+      </c>
+      <c r="O141" t="s">
+        <v>22</v>
+      </c>
+      <c r="P141" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -7097,24 +8777,36 @@
         <v>0</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J142" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K142" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="N142" t="s">
+        <v>22</v>
+      </c>
+      <c r="O142" t="s">
+        <v>22</v>
+      </c>
+      <c r="P142" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -7138,24 +8830,36 @@
         <v>0</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J143" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K143" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="N143" t="s">
+        <v>22</v>
+      </c>
+      <c r="O143" t="s">
+        <v>22</v>
+      </c>
+      <c r="P143" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7179,24 +8883,36 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J144" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K144" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+      <c r="N144" t="s">
+        <v>22</v>
+      </c>
+      <c r="O144" t="s">
+        <v>22</v>
+      </c>
+      <c r="P144" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7220,24 +8936,36 @@
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J145" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K145" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+      <c r="N145" t="s">
+        <v>22</v>
+      </c>
+      <c r="O145" t="s">
+        <v>22</v>
+      </c>
+      <c r="P145" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7261,24 +8989,36 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J146" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K146" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L146">
         <v>0</v>
       </c>
       <c r="M146" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="N146" t="s">
+        <v>22</v>
+      </c>
+      <c r="O146" t="s">
+        <v>22</v>
+      </c>
+      <c r="P146" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7302,24 +9042,36 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J147" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K147" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L147">
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="N147" t="s">
+        <v>22</v>
+      </c>
+      <c r="O147" t="s">
+        <v>22</v>
+      </c>
+      <c r="P147" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7343,24 +9095,36 @@
         <v>0</v>
       </c>
       <c r="I148" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J148" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K148" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L148">
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="N148" t="s">
+        <v>22</v>
+      </c>
+      <c r="O148" t="s">
+        <v>22</v>
+      </c>
+      <c r="P148" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7384,24 +9148,36 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J149" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K149" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L149">
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="N149" t="s">
+        <v>22</v>
+      </c>
+      <c r="O149" t="s">
+        <v>22</v>
+      </c>
+      <c r="P149" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7425,24 +9201,36 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J150" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K150" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L150">
         <v>0</v>
       </c>
       <c r="M150" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+      <c r="N150" t="s">
+        <v>22</v>
+      </c>
+      <c r="O150" t="s">
+        <v>22</v>
+      </c>
+      <c r="P150" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7466,24 +9254,36 @@
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J151" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K151" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L151">
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+      <c r="N151" t="s">
+        <v>22</v>
+      </c>
+      <c r="O151" t="s">
+        <v>22</v>
+      </c>
+      <c r="P151" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7507,24 +9307,36 @@
         <v>0</v>
       </c>
       <c r="I152" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J152" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K152" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L152">
         <v>0</v>
       </c>
       <c r="M152" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="N152" t="s">
+        <v>22</v>
+      </c>
+      <c r="O152" t="s">
+        <v>22</v>
+      </c>
+      <c r="P152" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7548,24 +9360,36 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J153" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K153" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L153">
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="N153" t="s">
+        <v>22</v>
+      </c>
+      <c r="O153" t="s">
+        <v>22</v>
+      </c>
+      <c r="P153" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7589,24 +9413,36 @@
         <v>0</v>
       </c>
       <c r="I154" t="s">
+        <v>29</v>
+      </c>
+      <c r="J154" t="s">
         <v>19</v>
       </c>
-      <c r="J154" t="s">
-        <v>15</v>
-      </c>
       <c r="K154" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L154">
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="N154" t="s">
+        <v>22</v>
+      </c>
+      <c r="O154" t="s">
+        <v>22</v>
+      </c>
+      <c r="P154" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7630,24 +9466,36 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J155" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K155" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L155">
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="N155" t="s">
+        <v>22</v>
+      </c>
+      <c r="O155" t="s">
+        <v>22</v>
+      </c>
+      <c r="P155" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7671,24 +9519,36 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J156" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K156" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L156">
         <v>0</v>
       </c>
       <c r="M156" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="N156" t="s">
+        <v>22</v>
+      </c>
+      <c r="O156" t="s">
+        <v>22</v>
+      </c>
+      <c r="P156" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7712,24 +9572,36 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
+        <v>29</v>
+      </c>
+      <c r="J157" t="s">
         <v>19</v>
       </c>
-      <c r="J157" t="s">
-        <v>15</v>
-      </c>
       <c r="K157" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L157">
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="N157" t="s">
+        <v>22</v>
+      </c>
+      <c r="O157" t="s">
+        <v>22</v>
+      </c>
+      <c r="P157" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7753,24 +9625,36 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J158" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K158" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L158">
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="N158" t="s">
+        <v>22</v>
+      </c>
+      <c r="O158" t="s">
+        <v>22</v>
+      </c>
+      <c r="P158" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B159">
         <v>4</v>
@@ -7794,24 +9678,36 @@
         <v>0</v>
       </c>
       <c r="I159" t="s">
+        <v>29</v>
+      </c>
+      <c r="J159" t="s">
         <v>19</v>
       </c>
-      <c r="J159" t="s">
-        <v>15</v>
-      </c>
       <c r="K159" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L159">
         <v>0</v>
       </c>
       <c r="M159" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+      <c r="N159" t="s">
+        <v>22</v>
+      </c>
+      <c r="O159" t="s">
+        <v>22</v>
+      </c>
+      <c r="P159" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -7835,24 +9731,36 @@
         <v>0</v>
       </c>
       <c r="I160" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J160" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K160" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L160">
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="N160" t="s">
+        <v>22</v>
+      </c>
+      <c r="O160" t="s">
+        <v>22</v>
+      </c>
+      <c r="P160" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -7876,24 +9784,36 @@
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J161" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K161" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L161">
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+      <c r="N161" t="s">
+        <v>22</v>
+      </c>
+      <c r="O161" t="s">
+        <v>22</v>
+      </c>
+      <c r="P161" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -7917,24 +9837,36 @@
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J162" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K162" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L162">
         <v>0</v>
       </c>
       <c r="M162" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="N162" t="s">
+        <v>22</v>
+      </c>
+      <c r="O162" t="s">
+        <v>22</v>
+      </c>
+      <c r="P162" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -7958,24 +9890,36 @@
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J163" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K163" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L163">
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="N163" t="s">
+        <v>22</v>
+      </c>
+      <c r="O163" t="s">
+        <v>22</v>
+      </c>
+      <c r="P163" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -7999,24 +9943,36 @@
         <v>0</v>
       </c>
       <c r="I164" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J164" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K164" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L164">
         <v>0</v>
       </c>
       <c r="M164" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="N164" t="s">
+        <v>22</v>
+      </c>
+      <c r="O164" t="s">
+        <v>22</v>
+      </c>
+      <c r="P164" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -8040,25 +9996,37 @@
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J165" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K165" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L165">
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="N165" t="s">
+        <v>22</v>
+      </c>
+      <c r="O165" t="s">
+        <v>22</v>
+      </c>
+      <c r="P165" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M1 A56:I83 B55:I55 A85:I165 B84:I84 A2:I36 K2:M54 K56:M83 K55:M55 K85:M165 K84:M84 A38:I54 B37:I37" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q1 A2:I36 K2:Q165 A38:I165 B37:I37" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -469,7 +469,7 @@
         <v>1155.8269573717953</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -484,13 +484,13 @@
         <v>AM</v>
       </c>
       <c r="K2" t="str">
-        <v>none</v>
+        <v>major</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-07-05T04:08:18.328Z</v>
+        <v>2026-07-07T13:04:25.872Z</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Take Flyte</v>
+        <v>Entropiq</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -1420,7 +1420,7 @@
         <v>2</v>
       </c>
       <c r="E20">
-        <v>1015.6724304703677</v>
+        <v>1016.3039403297893</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-07-05T04:05:23.392Z</v>
+        <v>2026-07-07T04:08:42.949Z</v>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Huns</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>1015</v>
+        <v>1015.6724304703677</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-02-18T21:21:06.168Z</v>
+        <v>2026-07-05T04:05:23.392Z</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Onyx Ravens</v>
+        <v>The Huns</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>1014.9877256835035</v>
+        <v>1015</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-03-21T04:32:33.790Z</v>
+        <v>2026-02-18T21:21:06.168Z</v>
       </c>
       <c r="N22" t="str">
         <v/>
@@ -1567,19 +1567,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TYLOO</v>
+        <v>Onyx Ravens</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>1014.128742285643</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J23" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K23" t="str">
         <v>none</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-02-19T22:09:16.526Z</v>
+        <v>2026-03-21T04:32:33.790Z</v>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1620,19 +1620,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>OG</v>
+        <v>Counter Logic</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>1013.5266895185538</v>
+        <v>1014.6510123894305</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J24" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K24" t="str">
         <v>none</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-02-19T22:09:03.691Z</v>
+        <v>2026-07-07T04:08:50.601Z</v>
       </c>
       <c r="N24" t="str">
         <v/>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Into the Beach</v>
+        <v>TYLOO</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1011.823225766436</v>
+        <v>1014.128742285643</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J25" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K25" t="str">
         <v>none</v>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-02-19T22:09:16.526Z</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>BESTIA</v>
+        <v>OG</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26">
-        <v>1005.0046329623956</v>
+        <v>1013.5266895185538</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J26" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K26" t="str">
         <v>none</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-02-19T22:09:03.691Z</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>G2</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>1002.6421965170028</v>
+        <v>1011.823225766436</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J27" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K27" t="str">
         <v>none</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v>2026-07-05T04:07:15.376Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FURIA</v>
+        <v>BESTIA</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>1001.9019624181617</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,19 +1885,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Mythic</v>
+        <v>G2</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>1000.942849124707</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J29" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K29" t="str">
         <v>none</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>hoorai</v>
+        <v>FURIA</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>1000.4888979238718</v>
+        <v>1001.9019624181617</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J30" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K30" t="str">
         <v>none</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>00 Nation</v>
+        <v>Mythic</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>1000</v>
+        <v>1000.942849124707</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J31" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K31" t="str">
         <v>none</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>2026-07-05T04:05:49.346Z</v>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,19 +2044,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>100 Thieves</v>
+        <v>hoorai</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>1000</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Astana Dragons</v>
+        <v>00 Nation</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Astralis Talent</v>
+        <v>100 Thieves</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Avangar</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J35" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K35" t="str">
         <v>none</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>BIG Academy</v>
+        <v>Astralis Talent</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bravado</v>
+        <v>Avangar</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Counter Logic</v>
+        <v>Bravado</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J39" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K39" t="str">
         <v>none</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENCE Academy</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ESC</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Flash</v>
+        <v>ESC</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>FLuffy Gangsters</v>
+        <v>Flash</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FlyQuest RED</v>
+        <v>FLuffy Gangsters</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Fnatic</v>
+        <v>FlyQuest RED</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>FORZE</v>
+        <v>Fnatic</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J46" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K46" t="str">
         <v>none</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Gambit</v>
+        <v>FORZE</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J47" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K47" t="str">
         <v>none</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>GATERON</v>
+        <v>Gambit</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J48" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K48" t="str">
         <v>none</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>GhoulsW</v>
+        <v>GATERON</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J49" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K49" t="str">
         <v>none</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HAVU</v>
+        <v>GhoulsW</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Heroic Academy</v>
+        <v>HAVU</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Hesta</v>
+        <v>Heroic Academy</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Kinguin</v>
+        <v>Hesta</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>kONO</v>
+        <v>Kinguin</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J54" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K54" t="str">
         <v>none</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>LGB</v>
+        <v>kONO</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>MAD Lions</v>
+        <v>LGB</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J56" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K56" t="str">
         <v>none</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Misfits</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mousesports</v>
+        <v>Misfits</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MOUZ NXT</v>
+        <v>mousesports</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Movistar KOI</v>
+        <v>MOUZ NXT</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>NIP Impact</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nordix</v>
+        <v>NIP Impact</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>NOVAQ</v>
+        <v>Nordix</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>paiN Academy</v>
+        <v>NOVAQ</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3767,7 +3767,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J64" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K64" t="str">
         <v>none</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Sprout</v>
+        <v>Tsunami</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J71" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K71" t="str">
         <v>none</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Tsunami</v>
+        <v>VeryGames</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>VeryGames</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Vox Eminor</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Wildcard Academy</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J75" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K75" t="str">
         <v>none</v>
@@ -4376,19 +4376,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Lux Tenebris</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J76" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K76" t="str">
         <v>none</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N76" t="str">
         <v/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Spirit Academy</v>
+        <v>True Rippers</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -4456,7 +4456,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J77" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K77" t="str">
         <v>none</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>True Rippers</v>
+        <v>FaZe</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>FaZe</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>iBUYPOWER</v>
+        <v>GODSENT</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -4615,7 +4615,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J80" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K80" t="str">
         <v>none</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>GODSENT</v>
+        <v>M80</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -4653,7 +4653,7 @@
         <v>2</v>
       </c>
       <c r="E81">
-        <v>999.7251809772306</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,19 +4694,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>M80</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>999.672340544519</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4721,7 +4721,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J82" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K82" t="str">
         <v>none</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Chinggis Warriors</v>
+        <v>Orbit</v>
       </c>
       <c r="B83">
         <v>3</v>
@@ -4759,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="E83">
-        <v>999.4408194717619</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
@@ -4800,19 +4800,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Orbit</v>
+        <v>Alliance</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>999.4186945376644</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N84" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alliance</v>
+        <v>Homyno</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -4880,7 +4880,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J85" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K85" t="str">
         <v>none</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N85" t="str">
         <v/>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Homyno</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4933,7 +4933,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J86" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K86" t="str">
         <v>none</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N86" t="str">
         <v/>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>MenaceGG</v>
+        <v>Solid</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4986,7 +4986,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J87" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K87" t="str">
         <v>none</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N87" t="str">
         <v/>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Solid</v>
+        <v>ENCE</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -5039,7 +5039,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J88" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K88" t="str">
         <v>none</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N88" t="str">
         <v/>
@@ -5065,7 +5065,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>ENCE</v>
+        <v>Nexus</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N89" t="str">
         <v/>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nexus</v>
+        <v>MIBR</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -5145,7 +5145,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J90" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K90" t="str">
         <v>none</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N90" t="str">
         <v/>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MIBR</v>
+        <v>Wizards</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -5183,7 +5183,7 @@
         <v>2</v>
       </c>
       <c r="E91">
-        <v>999.4088515186523</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N91" t="str">
         <v/>
@@ -5224,19 +5224,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Wizards</v>
+        <v>RED Canids</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92">
-        <v>999.4062521695108</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N92" t="str">
         <v/>
@@ -5277,19 +5277,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>RED Canids</v>
+        <v>Rebels</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93">
-        <v>999.3397745397444</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J93" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K93" t="str">
         <v>none</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N93" t="str">
         <v/>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Rebels</v>
+        <v>Legacy</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94">
-        <v>999.3232682842747</v>
+        <v>991.3908681786203</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J94" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K94" t="str">
         <v>none</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-07-05T04:07:08.327Z</v>
       </c>
       <c r="N94" t="str">
         <v/>
@@ -5383,19 +5383,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Legacy</v>
+        <v>ad hoc</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>991.3908681786203</v>
+        <v>985</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J95" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K95" t="str">
         <v>none</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-07-05T04:07:08.327Z</v>
+        <v>2026-02-19T00:50:09.060Z</v>
       </c>
       <c r="N95" t="str">
         <v/>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ad hoc</v>
+        <v>SAW</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J96" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K96" t="str">
         <v>none</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-02-19T00:50:09.060Z</v>
+        <v>2026-02-19T00:49:47.596Z</v>
       </c>
       <c r="N96" t="str">
         <v/>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SAW</v>
+        <v>NomadS</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J97" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K97" t="str">
         <v>none</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-02-19T00:49:47.596Z</v>
+        <v>2026-02-19T00:49:35.489Z</v>
       </c>
       <c r="N97" t="str">
         <v/>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>NomadS</v>
+        <v>Outsiders</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J98" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K98" t="str">
         <v>none</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-02-19T00:49:35.489Z</v>
+        <v>2026-02-19T00:49:27.811Z</v>
       </c>
       <c r="N98" t="str">
         <v/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Outsiders</v>
+        <v>Red Viperz</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J99" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K99" t="str">
         <v>none</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-02-19T00:49:27.811Z</v>
+        <v>2026-02-19T00:49:20.687Z</v>
       </c>
       <c r="N99" t="str">
         <v/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Red Viperz</v>
+        <v>The Dice</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J100" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K100" t="str">
         <v>none</v>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-02-19T00:49:20.687Z</v>
+        <v>2026-02-19T00:49:12.765Z</v>
       </c>
       <c r="N100" t="str">
         <v/>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Dice</v>
+        <v>Victores Sumus</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J101" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K101" t="str">
         <v>none</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-02-19T00:49:12.765Z</v>
+        <v>2026-02-19T00:49:00.243Z</v>
       </c>
       <c r="N101" t="str">
         <v/>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Victores Sumus</v>
+        <v>ODDIK</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J102" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K102" t="str">
         <v>none</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-02-19T00:49:00.243Z</v>
+        <v>2026-02-19T00:48:52.026Z</v>
       </c>
       <c r="N102" t="str">
         <v/>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ODDIK</v>
+        <v>Qiang</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J103" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K103" t="str">
         <v>none</v>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-02-19T00:48:52.026Z</v>
+        <v>2026-02-19T00:48:45.055Z</v>
       </c>
       <c r="N103" t="str">
         <v/>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Qiang</v>
+        <v>inSanitY</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-02-19T00:48:45.055Z</v>
+        <v>2026-02-19T00:48:38.129Z</v>
       </c>
       <c r="N104" t="str">
         <v/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>inSanitY</v>
+        <v>Sangal</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-02-19T00:48:38.129Z</v>
+        <v>2026-02-19T00:48:28.102Z</v>
       </c>
       <c r="N105" t="str">
         <v/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Sangal</v>
+        <v>9Pandas</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="str">
-        <v>2026-02-19T00:48:28.102Z</v>
+        <v>2026-02-19T00:48:17.012Z</v>
       </c>
       <c r="N106" t="str">
         <v/>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>9Pandas</v>
+        <v>Gods Reign</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-02-19T00:48:17.012Z</v>
+        <v>2026-02-19T00:48:09.473Z</v>
       </c>
       <c r="N107" t="str">
         <v/>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Gods Reign</v>
+        <v>CatEvil</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-02-19T00:48:09.473Z</v>
+        <v>2026-02-19T00:48:02.110Z</v>
       </c>
       <c r="N108" t="str">
         <v/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>CatEvil</v>
+        <v>Carnival</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-02-19T00:48:02.110Z</v>
+        <v>2026-02-19T00:47:49.161Z</v>
       </c>
       <c r="N109" t="str">
         <v/>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Carnival</v>
+        <v>Evil Geniuses</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-02-19T00:47:49.161Z</v>
+        <v>2026-02-19T00:47:36.482Z</v>
       </c>
       <c r="N110" t="str">
         <v/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Evil Geniuses</v>
+        <v>Vantage</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-02-19T00:47:36.482Z</v>
+        <v>2026-02-19T00:47:28.286Z</v>
       </c>
       <c r="N111" t="str">
         <v/>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Vantage</v>
+        <v>ATOX</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J112" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K112" t="str">
         <v>none</v>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-02-19T00:47:28.286Z</v>
+        <v>2026-02-19T00:47:18.470Z</v>
       </c>
       <c r="N112" t="str">
         <v/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ATOX</v>
+        <v>Skinvault</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J113" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K113" t="str">
         <v>none</v>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-02-19T00:47:18.470Z</v>
+        <v>2026-02-19T00:47:11.265Z</v>
       </c>
       <c r="N113" t="str">
         <v/>
@@ -6390,7 +6390,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Skinvault</v>
+        <v>BC.Game</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-02-19T00:47:11.265Z</v>
+        <v>2026-02-19T00:46:52.846Z</v>
       </c>
       <c r="N114" t="str">
         <v/>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>BC.Game</v>
+        <v>Wings Up</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6470,7 +6470,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J115" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K115" t="str">
         <v>none</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="str">
-        <v>2026-02-19T00:46:52.846Z</v>
+        <v>2026-02-19T00:46:32.115Z</v>
       </c>
       <c r="N115" t="str">
         <v/>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Wings Up</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-02-19T00:46:32.115Z</v>
+        <v>2026-02-19T00:46:08.336Z</v>
       </c>
       <c r="N116" t="str">
         <v/>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Lynn Vision</v>
+        <v>Tricked</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6576,7 +6576,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J117" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K117" t="str">
         <v>none</v>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-02-19T00:46:08.336Z</v>
+        <v>2026-02-19T00:45:42.234Z</v>
       </c>
       <c r="N117" t="str">
         <v/>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Tricked</v>
+        <v>3DMAX</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-02-19T00:45:42.234Z</v>
+        <v>2026-02-19T00:39:02.710Z</v>
       </c>
       <c r="N118" t="str">
         <v/>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3DMAX</v>
+        <v>Venom</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J119" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K119" t="str">
         <v>none</v>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-02-19T00:39:02.710Z</v>
+        <v>2026-02-19T00:38:39.010Z</v>
       </c>
       <c r="N119" t="str">
         <v/>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Venom</v>
+        <v>ARCRED</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J120" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K120" t="str">
         <v>none</v>
@@ -6744,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-02-19T00:38:39.010Z</v>
+        <v>2026-02-19T00:38:03.598Z</v>
       </c>
       <c r="N120" t="str">
         <v/>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ARCRED</v>
+        <v>GamerLegion</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J121" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K121" t="str">
         <v>none</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-02-19T00:38:03.598Z</v>
+        <v>2026-02-19T00:37:47.172Z</v>
       </c>
       <c r="N121" t="str">
         <v/>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>GamerLegion</v>
+        <v>Passion UA</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J122" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K122" t="str">
         <v>none</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-02-19T00:37:47.172Z</v>
+        <v>2026-02-19T00:37:27.234Z</v>
       </c>
       <c r="N122" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Passion UA</v>
+        <v>FlyQuest</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J123" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K123" t="str">
         <v>none</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="str">
-        <v>2026-02-19T00:37:27.234Z</v>
+        <v>2026-02-19T00:37:20.280Z</v>
       </c>
       <c r="N123" t="str">
         <v/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>FlyQuest</v>
+        <v>Envy</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J124" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K124" t="str">
         <v>none</v>
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="str">
-        <v>2026-02-19T00:37:20.280Z</v>
+        <v>2026-02-19T00:37:05.560Z</v>
       </c>
       <c r="N124" t="str">
         <v/>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Envy</v>
+        <v>BIG</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="str">
-        <v>2026-02-19T00:37:05.560Z</v>
+        <v>2026-02-19T00:36:43.463Z</v>
       </c>
       <c r="N125" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>BIG</v>
+        <v>Limitless</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="str">
-        <v>2026-02-19T00:36:43.463Z</v>
+        <v>2026-02-19T00:36:26.343Z</v>
       </c>
       <c r="N126" t="str">
         <v/>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Limitless</v>
+        <v>Galorys</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J127" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K127" t="str">
         <v>none</v>
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="str">
-        <v>2026-02-19T00:36:26.343Z</v>
+        <v>2026-02-19T00:36:18.696Z</v>
       </c>
       <c r="N127" t="str">
         <v/>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Galorys</v>
+        <v>devils.one</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -7159,7 +7159,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J128" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K128" t="str">
         <v>none</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="str">
-        <v>2026-02-19T00:36:18.696Z</v>
+        <v>2026-02-18T21:23:30.347Z</v>
       </c>
       <c r="N128" t="str">
         <v/>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>devils.one</v>
+        <v>Luminosity</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J129" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K129" t="str">
         <v>none</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="str">
-        <v>2026-02-18T21:23:30.347Z</v>
+        <v>2026-02-18T21:23:18.851Z</v>
       </c>
       <c r="N129" t="str">
         <v/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Luminosity</v>
+        <v>Sharks</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J130" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K130" t="str">
         <v>none</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-02-18T21:23:18.851Z</v>
+        <v>2026-02-18T21:23:12.952Z</v>
       </c>
       <c r="N130" t="str">
         <v/>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sharks</v>
+        <v>IHC</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J131" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K131" t="str">
         <v>none</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="str">
-        <v>2026-02-18T21:23:12.952Z</v>
+        <v>2026-02-18T21:23:06.529Z</v>
       </c>
       <c r="N131" t="str">
         <v/>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>IHC</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J132" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K132" t="str">
         <v>none</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="str">
-        <v>2026-02-18T21:23:06.529Z</v>
+        <v>2026-02-18T21:22:57.244Z</v>
       </c>
       <c r="N132" t="str">
         <v/>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Kappa Bar</v>
+        <v>Complexity</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -7424,7 +7424,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J133" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K133" t="str">
         <v>none</v>
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-02-18T21:22:57.244Z</v>
+        <v>2026-02-18T21:22:48.652Z</v>
       </c>
       <c r="N133" t="str">
         <v/>
@@ -7450,7 +7450,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Complexity</v>
+        <v>Case</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J134" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K134" t="str">
         <v>none</v>
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="str">
-        <v>2026-02-18T21:22:48.652Z</v>
+        <v>2026-02-18T21:22:39.402Z</v>
       </c>
       <c r="N134" t="str">
         <v/>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Case</v>
+        <v>Enemy</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-02-18T21:22:39.402Z</v>
+        <v>2026-02-18T21:22:20.745Z</v>
       </c>
       <c r="N135" t="str">
         <v/>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Enemy</v>
+        <v>KRU</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J136" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K136" t="str">
         <v>none</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="str">
-        <v>2026-02-18T21:22:20.745Z</v>
+        <v>2026-02-18T21:22:06.663Z</v>
       </c>
       <c r="N136" t="str">
         <v/>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>KRU</v>
+        <v>Imperial</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="str">
-        <v>2026-02-18T21:22:06.663Z</v>
+        <v>2026-02-18T21:21:57.658Z</v>
       </c>
       <c r="N137" t="str">
         <v/>
@@ -7662,7 +7662,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Imperial</v>
+        <v>paiN</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="str">
-        <v>2026-02-18T21:21:57.658Z</v>
+        <v>2026-02-18T21:21:14.058Z</v>
       </c>
       <c r="N138" t="str">
         <v/>
@@ -7715,7 +7715,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>paiN</v>
+        <v>Vexed</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -7742,7 +7742,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J139" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K139" t="str">
         <v>none</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="str">
-        <v>2026-02-18T21:21:14.058Z</v>
+        <v>2026-02-18T21:19:58.722Z</v>
       </c>
       <c r="N139" t="str">
         <v/>
@@ -7768,19 +7768,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Vexed</v>
+        <v>Dignitas</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140">
         <v>0</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="str">
-        <v>2026-02-18T21:19:58.722Z</v>
+        <v>2026-02-19T21:54:17.535Z</v>
       </c>
       <c r="N140" t="str">
         <v/>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Dignitas</v>
+        <v>LDLC</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="str">
-        <v>2026-02-19T21:54:17.535Z</v>
+        <v>2026-02-19T21:53:53.691Z</v>
       </c>
       <c r="N141" t="str">
         <v/>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>LDLC</v>
+        <v>Aravt</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="str">
-        <v>2026-02-19T21:53:53.691Z</v>
+        <v>2026-02-19T02:51:09.872Z</v>
       </c>
       <c r="N142" t="str">
         <v/>
@@ -7927,7 +7927,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Aravt</v>
+        <v>VP.Prodigy</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="str">
-        <v>2026-02-19T02:51:09.872Z</v>
+        <v>2026-02-19T02:51:03.784Z</v>
       </c>
       <c r="N143" t="str">
         <v/>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>VP.Prodigy</v>
+        <v>Underground</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="str">
-        <v>2026-02-19T02:51:03.784Z</v>
+        <v>2026-02-19T02:47:27.422Z</v>
       </c>
       <c r="N144" t="str">
         <v/>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Entropiq</v>
+        <v>Virtus.pro</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -8060,7 +8060,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J145" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K145" t="str">
         <v>none</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="str">
-        <v>2026-02-19T02:49:25.044Z</v>
+        <v>2026-02-19T02:47:19.575Z</v>
       </c>
       <c r="N145" t="str">
         <v/>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Underground</v>
+        <v>ShindeN</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="str">
-        <v>2026-02-19T02:47:27.422Z</v>
+        <v>2026-02-19T02:36:26.535Z</v>
       </c>
       <c r="N146" t="str">
         <v/>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Virtus.pro</v>
+        <v>Permitta</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="str">
-        <v>2026-02-19T02:47:19.575Z</v>
+        <v>2026-02-19T02:36:17.329Z</v>
       </c>
       <c r="N147" t="str">
         <v/>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>ShindeN</v>
+        <v>Wildcard</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -8219,7 +8219,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J148" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K148" t="str">
         <v>none</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="str">
-        <v>2026-02-19T02:36:26.535Z</v>
+        <v>2026-02-19T02:34:08.116Z</v>
       </c>
       <c r="N148" t="str">
         <v/>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Permitta</v>
+        <v>Astralis</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -8281,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="str">
-        <v>2026-02-19T02:36:17.329Z</v>
+        <v>2026-02-19T02:34:01.822Z</v>
       </c>
       <c r="N149" t="str">
         <v/>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Wildcard</v>
+        <v>Bad News Eagles</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -8325,7 +8325,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J150" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K150" t="str">
         <v>none</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="str">
-        <v>2026-02-19T02:34:08.116Z</v>
+        <v>2026-02-19T01:45:27.335Z</v>
       </c>
       <c r="N150" t="str">
         <v/>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Astralis</v>
+        <v>SK</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -8378,7 +8378,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J151" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K151" t="str">
         <v>none</v>
@@ -8387,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="str">
-        <v>2026-02-19T02:34:01.822Z</v>
+        <v>2026-02-19T01:39:18.535Z</v>
       </c>
       <c r="N151" t="str">
         <v/>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Bad News Eagles</v>
+        <v>ECSTATIC</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -8431,7 +8431,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J152" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K152" t="str">
         <v>none</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="str">
-        <v>2026-02-19T01:45:27.335Z</v>
+        <v>2026-02-19T01:39:12.540Z</v>
       </c>
       <c r="N152" t="str">
         <v/>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SK</v>
+        <v>MIBR Academy</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -8469,7 +8469,7 @@
         <v>2</v>
       </c>
       <c r="E153">
-        <v>984.7039370196626</v>
+        <v>984.075576101157</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J153" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K153" t="str">
         <v>none</v>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="str">
-        <v>2026-02-19T01:39:18.535Z</v>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N153" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ECSTATIC</v>
+        <v>paiN Academy</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -8522,7 +8522,7 @@
         <v>2</v>
       </c>
       <c r="E154">
-        <v>984.7039370196626</v>
+        <v>984.0732769617838</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -8537,7 +8537,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J154" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K154" t="str">
         <v>none</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="str">
-        <v>2026-02-19T01:39:12.540Z</v>
+        <v>2026-07-07T04:08:50.601Z</v>
       </c>
       <c r="N154" t="str">
         <v/>
@@ -8563,19 +8563,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>MIBR Academy</v>
+        <v>TALON</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E155">
-        <v>984.075576101157</v>
+        <v>983.9905713816794</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J155" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K155" t="str">
         <v>none</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-02-28T06:27:14.538Z</v>
       </c>
       <c r="N155" t="str">
         <v/>
@@ -8616,19 +8616,19 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>TALON</v>
+        <v>B8</v>
       </c>
       <c r="B156">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E156">
-        <v>983.9905713816794</v>
+        <v>983.4284201175154</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J156" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K156" t="str">
         <v>none</v>
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="str">
-        <v>2026-02-28T06:27:14.538Z</v>
+        <v>2026-07-05T04:05:49.346Z</v>
       </c>
       <c r="N156" t="str">
         <v/>
@@ -8669,19 +8669,19 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>B8</v>
+        <v>NAVI Junior</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E157">
-        <v>983.4284201175154</v>
+        <v>983.2698348870488</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J157" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K157" t="str">
         <v>none</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v>2026-02-28T06:27:03.939Z</v>
       </c>
       <c r="N157" t="str">
         <v/>
@@ -8722,19 +8722,19 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>NAVI Junior</v>
+        <v>9z</v>
       </c>
       <c r="B158">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E158">
-        <v>983.2698348870488</v>
+        <v>971.3809496889581</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -8749,7 +8749,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J158" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K158" t="str">
         <v>none</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="str">
-        <v>2026-02-28T06:27:03.939Z</v>
+        <v>2026-07-05T04:07:15.376Z</v>
       </c>
       <c r="N158" t="str">
         <v/>
@@ -8775,19 +8775,19 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>9z</v>
+        <v>Ninjas in Pyjamas</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159">
-        <v>971.3809496889581</v>
+        <v>970</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -8802,7 +8802,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J159" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K159" t="str">
         <v>none</v>
@@ -8811,7 +8811,7 @@
         <v>0</v>
       </c>
       <c r="M159" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-02-19T21:53:46.615Z</v>
       </c>
       <c r="N159" t="str">
         <v/>
@@ -8828,7 +8828,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Ninjas in Pyjamas</v>
+        <v>MOUZ</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -8864,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="M160" t="str">
-        <v>2026-02-19T21:53:46.615Z</v>
+        <v>2026-02-19T21:53:40.004Z</v>
       </c>
       <c r="N160" t="str">
         <v/>
@@ -8881,7 +8881,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>MOUZ</v>
+        <v>Aurora</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -8917,7 +8917,7 @@
         <v>0</v>
       </c>
       <c r="M161" t="str">
-        <v>2026-02-19T21:53:40.004Z</v>
+        <v>2026-02-19T21:53:30.387Z</v>
       </c>
       <c r="N161" t="str">
         <v/>
@@ -8934,7 +8934,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Aurora</v>
+        <v>Reason</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="M162" t="str">
-        <v>2026-02-19T21:53:30.387Z</v>
+        <v>2026-02-19T21:53:23.315Z</v>
       </c>
       <c r="N162" t="str">
         <v/>
@@ -8987,7 +8987,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Reason</v>
+        <v>Sprout</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -8999,7 +8999,7 @@
         <v>2</v>
       </c>
       <c r="E163">
-        <v>970</v>
+        <v>969.9715073660867</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -9014,7 +9014,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J163" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K163" t="str">
         <v>none</v>
@@ -9023,7 +9023,7 @@
         <v>0</v>
       </c>
       <c r="M163" t="str">
-        <v>2026-02-19T21:53:23.315Z</v>
+        <v>2026-07-07T04:07:21.355Z</v>
       </c>
       <c r="N163" t="str">
         <v/>

--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -469,7 +469,7 @@
         <v>1155.8269573717953</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>12</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-07-07T13:04:25.872Z</v>
+        <v>2026-07-23T22:29:15.026Z</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -984,19 +984,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Titan</v>
+        <v>FURIA</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>1046.4273525065098</v>
+        <v>1050.7178542874221</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>Tier 3</v>
@@ -1014,13 +1014,13 @@
         <v>AM</v>
       </c>
       <c r="K12" t="str">
-        <v>none</v>
+        <v>regional</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-05-30T04:00:20.081Z</v>
+        <v>2026-07-23T22:29:09.347Z</v>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -1037,19 +1037,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Verdant</v>
+        <v>Titan</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>1038.7190184710753</v>
+        <v>1046.4273525065098</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1064,7 +1064,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J13" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K13" t="str">
         <v>none</v>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-02-28T06:29:24.671Z</v>
+        <v>2026-05-30T04:00:20.081Z</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1090,19 +1090,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>PARIVISION</v>
+        <v>AMKAL</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>1034.630067328374</v>
+        <v>1041.3191963490904</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1117,7 +1117,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J14" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K14" t="str">
         <v>none</v>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-05-01T06:07:06.437Z</v>
+        <v>2026-07-23T22:16:25.593Z</v>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -1143,19 +1143,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Cloud9</v>
+        <v>Verdant</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>1031.0582679094105</v>
+        <v>1038.7190184710753</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J15" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K15" t="str">
         <v>none</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-05-01T06:06:54.331Z</v>
+        <v>2026-02-28T06:29:24.671Z</v>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Heroic</v>
+        <v>PARIVISION</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1208,7 +1208,7 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>1030.413991476608</v>
+        <v>1034.630067328374</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-05-01T06:08:21.905Z</v>
+        <v>2026-05-01T06:07:06.437Z</v>
       </c>
       <c r="N16" t="str">
         <v/>
@@ -1249,19 +1249,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>AMKAL</v>
+        <v>Cloud9</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>1029.6796950897065</v>
+        <v>1031.0582679094105</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J17" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K17" t="str">
         <v>none</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-06-26T13:19:23.768Z</v>
+        <v>2026-05-01T06:06:54.331Z</v>
       </c>
       <c r="N17" t="str">
         <v/>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Bounty Hunters</v>
+        <v>Heroic</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -1311,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>1017.2412711985547</v>
+        <v>1030.413991476608</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-02-28T06:28:59.888Z</v>
+        <v>2026-05-01T06:08:21.905Z</v>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1355,19 +1355,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Spirit</v>
+        <v>Entropiq</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19">
-        <v>1016.7402640066111</v>
+        <v>1029.3999079514006</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J19" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K19" t="str">
         <v>none</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-03-21T04:32:26.020Z</v>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -1408,19 +1408,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Entropiq</v>
+        <v>Bounty Hunters</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>1016.3039403297893</v>
+        <v>1017.2412711985547</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J20" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K20" t="str">
         <v>none</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-07-07T04:08:42.949Z</v>
+        <v>2026-02-28T06:28:59.888Z</v>
       </c>
       <c r="N20" t="str">
         <v/>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Take Flyte</v>
+        <v>Spirit</v>
       </c>
       <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
         <v>3</v>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
       <c r="E21">
-        <v>1015.6724304703677</v>
+        <v>1016.7402640066111</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J21" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K21" t="str">
         <v>none</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-07-05T04:05:23.392Z</v>
+        <v>2026-03-21T04:32:26.020Z</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Into the Beach</v>
+        <v>BESTIA</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>1011.823225766436</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-02-28T06:29:16.752Z</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>BESTIA</v>
+        <v>G2</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>1005.0046329623956</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J28" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K28" t="str">
         <v>none</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-02-28T06:29:16.752Z</v>
+        <v>2026-02-28T06:28:17.433Z</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>G2</v>
+        <v>hoorai</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -1897,7 +1897,7 @@
         <v>4</v>
       </c>
       <c r="E29">
-        <v>1002.6421965170028</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-02-28T06:28:17.433Z</v>
+        <v>2026-02-28T06:28:25.661Z</v>
       </c>
       <c r="N29" t="str">
         <v/>
@@ -1938,19 +1938,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FURIA</v>
+        <v>Take Flyte</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>1001.9019624181617</v>
+        <v>1000.3086743488057</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-07-23T22:14:26.816Z</v>
       </c>
       <c r="N30" t="str">
         <v/>
@@ -1991,19 +1991,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Mythic</v>
+        <v>00 Nation</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>1000.942849124707</v>
+        <v>1000</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2018,7 +2018,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J31" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K31" t="str">
         <v>none</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v/>
       </c>
       <c r="N31" t="str">
         <v/>
@@ -2044,19 +2044,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>hoorai</v>
+        <v>100 Thieves</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1000.4888979238718</v>
+        <v>1000</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-02-28T06:28:25.661Z</v>
+        <v/>
       </c>
       <c r="N32" t="str">
         <v/>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>00 Nation</v>
+        <v>Astana Dragons</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>100 Thieves</v>
+        <v>Astralis Talent</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Astana Dragons</v>
+        <v>Avangar</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J35" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K35" t="str">
         <v>none</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Astralis Talent</v>
+        <v>BIG Academy</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Avangar</v>
+        <v>Bravado</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>BIG Academy</v>
+        <v>Copenhagen Wolves</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bravado</v>
+        <v>ENCE Academy</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J39" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K39" t="str">
         <v>none</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Copenhagen Wolves</v>
+        <v>ESC</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENCE Academy</v>
+        <v>Flash</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ESC</v>
+        <v>FLuffy Gangsters</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Flash</v>
+        <v>FlyQuest RED</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>FLuffy Gangsters</v>
+        <v>Fnatic</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>FlyQuest RED</v>
+        <v>FORZE</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J45" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K45" t="str">
         <v>none</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Fnatic</v>
+        <v>Gambit</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>FORZE</v>
+        <v>GATERON</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Gambit</v>
+        <v>GhoulsW</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>GATERON</v>
+        <v>HAVU</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J49" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K49" t="str">
         <v>none</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>GhoulsW</v>
+        <v>Heroic Academy</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HAVU</v>
+        <v>Hesta</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Heroic Academy</v>
+        <v>Kinguin</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Hesta</v>
+        <v>kONO</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J53" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K53" t="str">
         <v>none</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Kinguin</v>
+        <v>LGB</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J54" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K54" t="str">
         <v>none</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>kONO</v>
+        <v>MAD Lions</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J55" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K55" t="str">
         <v>none</v>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>LGB</v>
+        <v>Misfits</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J56" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K56" t="str">
         <v>none</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>MAD Lions</v>
+        <v>mousesports</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Misfits</v>
+        <v>MOUZ NXT</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>mousesports</v>
+        <v>Movistar KOI</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>MOUZ NXT</v>
+        <v>NIP Impact</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Movistar KOI</v>
+        <v>Nordix</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>NIP Impact</v>
+        <v>NOVAQ</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Nordix</v>
+        <v>QMISTRY</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>NOVAQ</v>
+        <v>Quantum Bellator Fire</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>QMISTRY</v>
+        <v>Rogue</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J65" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K65" t="str">
         <v>none</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quantum Bellator Fire</v>
+        <v>Shika</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J66" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K66" t="str">
         <v>none</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Rogue</v>
+        <v>SKYFURY</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J67" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K67" t="str">
         <v>none</v>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Shika</v>
+        <v>Space Soldiers</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J68" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K68" t="str">
         <v>none</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SKYFURY</v>
+        <v>Tsunami</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Space Soldiers</v>
+        <v>VeryGames</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Tsunami</v>
+        <v>Vox Eminor</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>VeryGames</v>
+        <v>Wildcard Academy</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Vox Eminor</v>
+        <v>Lux Tenebris</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J73" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K73" t="str">
         <v>none</v>
@@ -4270,19 +4270,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Wildcard Academy</v>
+        <v>Spirit Academy</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J74" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K74" t="str">
         <v>none</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>2026-02-19T02:49:35.870Z</v>
       </c>
       <c r="N74" t="str">
         <v/>
@@ -4323,19 +4323,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lux Tenebris</v>
+        <v>True Rippers</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>1000</v>
+        <v>999.7251809772306</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J75" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K75" t="str">
         <v>none</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>2026-02-19T02:47:38.886Z</v>
       </c>
       <c r="N75" t="str">
         <v/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Spirit Academy</v>
+        <v>FaZe</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -4403,7 +4403,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J76" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K76" t="str">
         <v>none</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="str">
-        <v>2026-02-19T02:49:35.870Z</v>
+        <v>2026-02-19T02:36:39.932Z</v>
       </c>
       <c r="N76" t="str">
         <v/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>True Rippers</v>
+        <v>iBUYPOWER</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="str">
-        <v>2026-02-19T02:47:38.886Z</v>
+        <v>2026-02-19T02:36:34.302Z</v>
       </c>
       <c r="N77" t="str">
         <v/>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>FaZe</v>
+        <v>GODSENT</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -4509,7 +4509,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J78" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K78" t="str">
         <v>none</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="str">
-        <v>2026-02-19T02:36:39.932Z</v>
+        <v>2026-02-19T01:39:32.364Z</v>
       </c>
       <c r="N78" t="str">
         <v/>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>iBUYPOWER</v>
+        <v>M80</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -4547,7 +4547,7 @@
         <v>2</v>
       </c>
       <c r="E79">
-        <v>999.7251809772306</v>
+        <v>999.672340544519</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J79" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K79" t="str">
         <v>none</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="str">
-        <v>2026-02-19T02:36:34.302Z</v>
+        <v>2026-02-19T01:45:45.455Z</v>
       </c>
       <c r="N79" t="str">
         <v/>
@@ -4588,19 +4588,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>GODSENT</v>
+        <v>Chinggis Warriors</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>999.7251809772306</v>
+        <v>999.4408194717619</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -4615,7 +4615,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J80" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K80" t="str">
         <v>none</v>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="str">
-        <v>2026-02-19T01:39:32.364Z</v>
+        <v>2026-02-19T22:08:18.806Z</v>
       </c>
       <c r="N80" t="str">
         <v/>
@@ -4641,19 +4641,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>M80</v>
+        <v>Orbit</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81">
-        <v>999.672340544519</v>
+        <v>999.4186945376644</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J81" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K81" t="str">
         <v>none</v>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="str">
-        <v>2026-02-19T01:45:45.455Z</v>
+        <v>2026-02-19T22:08:33.993Z</v>
       </c>
       <c r="N81" t="str">
         <v/>
@@ -4694,19 +4694,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chinggis Warriors</v>
+        <v>Alliance</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>999.4408194717619</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4721,7 +4721,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J82" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K82" t="str">
         <v>none</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="str">
-        <v>2026-02-19T22:08:18.806Z</v>
+        <v>2026-02-19T02:51:22.336Z</v>
       </c>
       <c r="N82" t="str">
         <v/>
@@ -4747,19 +4747,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Orbit</v>
+        <v>Homyno</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83">
-        <v>999.4186945376644</v>
+        <v>999.4088515186523</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J83" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K83" t="str">
         <v>none</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="str">
-        <v>2026-02-19T22:08:33.993Z</v>
+        <v>2026-02-19T02:51:16.607Z</v>
       </c>
       <c r="N83" t="str">
         <v/>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alliance</v>
+        <v>MenaceGG</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="str">
-        <v>2026-02-19T02:51:22.336Z</v>
+        <v>2026-02-19T02:49:44.165Z</v>
       </c>
       <c r="N84" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Homyno</v>
+        <v>Solid</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="str">
-        <v>2026-02-19T02:51:16.607Z</v>
+        <v>2026-02-19T02:47:50.233Z</v>
       </c>
       <c r="N85" t="str">
         <v/>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>MenaceGG</v>
+        <v>ENCE</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="str">
-        <v>2026-02-19T02:49:44.165Z</v>
+        <v>2026-02-19T02:34:19.604Z</v>
       </c>
       <c r="N86" t="str">
         <v/>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Solid</v>
+        <v>Nexus</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4986,7 +4986,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J87" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K87" t="str">
         <v>none</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="str">
-        <v>2026-02-19T02:47:50.233Z</v>
+        <v>2026-02-19T02:34:13.227Z</v>
       </c>
       <c r="N87" t="str">
         <v/>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ENCE</v>
+        <v>MIBR</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -5039,7 +5039,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J88" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K88" t="str">
         <v>none</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="str">
-        <v>2026-02-19T02:34:19.604Z</v>
+        <v>2026-02-19T01:39:50.018Z</v>
       </c>
       <c r="N88" t="str">
         <v/>
@@ -5065,7 +5065,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nexus</v>
+        <v>Wizards</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -5077,7 +5077,7 @@
         <v>2</v>
       </c>
       <c r="E89">
-        <v>999.4088515186523</v>
+        <v>999.4062521695108</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J89" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K89" t="str">
         <v>none</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="str">
-        <v>2026-02-19T02:34:13.227Z</v>
+        <v>2026-02-19T01:45:38.841Z</v>
       </c>
       <c r="N89" t="str">
         <v/>
@@ -5118,19 +5118,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>MIBR</v>
+        <v>RED Canids</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90">
-        <v>999.4088515186523</v>
+        <v>999.3397745397444</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="str">
-        <v>2026-02-19T01:39:50.018Z</v>
+        <v>2026-02-19T22:08:44.661Z</v>
       </c>
       <c r="N90" t="str">
         <v/>
@@ -5171,19 +5171,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Wizards</v>
+        <v>Rebels</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91">
-        <v>999.4062521695108</v>
+        <v>999.3232682842747</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -5198,7 +5198,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J91" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K91" t="str">
         <v>none</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="str">
-        <v>2026-02-19T01:45:38.841Z</v>
+        <v>2026-02-28T06:28:39.554Z</v>
       </c>
       <c r="N91" t="str">
         <v/>
@@ -5224,19 +5224,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>RED Canids</v>
+        <v>Into the Beach</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92">
-        <v>999.3397745397444</v>
+        <v>996.0904918173039</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="str">
-        <v>2026-02-19T22:08:44.661Z</v>
+        <v>2026-07-23T22:12:51.919Z</v>
       </c>
       <c r="N92" t="str">
         <v/>
@@ -5277,19 +5277,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Rebels</v>
+        <v>Mythic</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E93">
-        <v>999.3232682842747</v>
+        <v>986.2948766874508</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J93" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K93" t="str">
         <v>none</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="str">
-        <v>2026-02-28T06:28:39.554Z</v>
+        <v>2026-07-23T22:00:15.992Z</v>
       </c>
       <c r="N93" t="str">
         <v/>
@@ -5330,19 +5330,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Legacy</v>
+        <v>ad hoc</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94">
-        <v>991.3908681786203</v>
+        <v>985</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J94" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K94" t="str">
         <v>none</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="str">
-        <v>2026-07-05T04:07:08.327Z</v>
+        <v>2026-02-19T00:50:09.060Z</v>
       </c>
       <c r="N94" t="str">
         <v/>
@@ -5383,7 +5383,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ad hoc</v>
+        <v>SAW</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J95" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K95" t="str">
         <v>none</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="str">
-        <v>2026-02-19T00:50:09.060Z</v>
+        <v>2026-02-19T00:49:47.596Z</v>
       </c>
       <c r="N95" t="str">
         <v/>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SAW</v>
+        <v>NomadS</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J96" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K96" t="str">
         <v>none</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="str">
-        <v>2026-02-19T00:49:47.596Z</v>
+        <v>2026-02-19T00:49:35.489Z</v>
       </c>
       <c r="N96" t="str">
         <v/>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>NomadS</v>
+        <v>Outsiders</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J97" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K97" t="str">
         <v>none</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="str">
-        <v>2026-02-19T00:49:35.489Z</v>
+        <v>2026-02-19T00:49:27.811Z</v>
       </c>
       <c r="N97" t="str">
         <v/>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Outsiders</v>
+        <v>Red Viperz</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J98" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K98" t="str">
         <v>none</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="str">
-        <v>2026-02-19T00:49:27.811Z</v>
+        <v>2026-02-19T00:49:20.687Z</v>
       </c>
       <c r="N98" t="str">
         <v/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Red Viperz</v>
+        <v>The Dice</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J99" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K99" t="str">
         <v>none</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="str">
-        <v>2026-02-19T00:49:20.687Z</v>
+        <v>2026-02-19T00:49:12.765Z</v>
       </c>
       <c r="N99" t="str">
         <v/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Dice</v>
+        <v>Victores Sumus</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J100" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K100" t="str">
         <v>none</v>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="str">
-        <v>2026-02-19T00:49:12.765Z</v>
+        <v>2026-02-19T00:49:00.243Z</v>
       </c>
       <c r="N100" t="str">
         <v/>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Victores Sumus</v>
+        <v>ODDIK</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J101" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>AM</v>
       </c>
       <c r="K101" t="str">
         <v>none</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="str">
-        <v>2026-02-19T00:49:00.243Z</v>
+        <v>2026-02-19T00:48:52.026Z</v>
       </c>
       <c r="N101" t="str">
         <v/>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ODDIK</v>
+        <v>Qiang</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J102" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K102" t="str">
         <v>none</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="str">
-        <v>2026-02-19T00:48:52.026Z</v>
+        <v>2026-02-19T00:48:45.055Z</v>
       </c>
       <c r="N102" t="str">
         <v/>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Qiang</v>
+        <v>inSanitY</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="str">
-        <v>2026-02-19T00:48:45.055Z</v>
+        <v>2026-02-19T00:48:38.129Z</v>
       </c>
       <c r="N103" t="str">
         <v/>
@@ -5860,7 +5860,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>inSanitY</v>
+        <v>Sangal</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="str">
-        <v>2026-02-19T00:48:38.129Z</v>
+        <v>2026-02-19T00:48:28.102Z</v>
       </c>
       <c r="N104" t="str">
         <v/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Sangal</v>
+        <v>9Pandas</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="str">
-        <v>2026-02-19T00:48:28.102Z</v>
+        <v>2026-02-19T00:48:17.012Z</v>
       </c>
       <c r="N105" t="str">
         <v/>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>9Pandas</v>
+        <v>Gods Reign</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="str">
-        <v>2026-02-19T00:48:17.012Z</v>
+        <v>2026-02-19T00:48:09.473Z</v>
       </c>
       <c r="N106" t="str">
         <v/>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Gods Reign</v>
+        <v>CatEvil</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="str">
-        <v>2026-02-19T00:48:09.473Z</v>
+        <v>2026-02-19T00:48:02.110Z</v>
       </c>
       <c r="N107" t="str">
         <v/>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>CatEvil</v>
+        <v>Carnival</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="str">
-        <v>2026-02-19T00:48:02.110Z</v>
+        <v>2026-02-19T00:47:49.161Z</v>
       </c>
       <c r="N108" t="str">
         <v/>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Carnival</v>
+        <v>Evil Geniuses</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="str">
-        <v>2026-02-19T00:47:49.161Z</v>
+        <v>2026-02-19T00:47:36.482Z</v>
       </c>
       <c r="N109" t="str">
         <v/>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Evil Geniuses</v>
+        <v>Vantage</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="str">
-        <v>2026-02-19T00:47:36.482Z</v>
+        <v>2026-02-19T00:47:28.286Z</v>
       </c>
       <c r="N110" t="str">
         <v/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Vantage</v>
+        <v>ATOX</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J111" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K111" t="str">
         <v>none</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="str">
-        <v>2026-02-19T00:47:28.286Z</v>
+        <v>2026-02-19T00:47:18.470Z</v>
       </c>
       <c r="N111" t="str">
         <v/>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ATOX</v>
+        <v>Skinvault</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J112" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K112" t="str">
         <v>none</v>
@@ -6320,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="str">
-        <v>2026-02-19T00:47:18.470Z</v>
+        <v>2026-02-19T00:47:11.265Z</v>
       </c>
       <c r="N112" t="str">
         <v/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Skinvault</v>
+        <v>BC.Game</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="str">
-        <v>2026-02-19T00:47:11.265Z</v>
+        <v>2026-02-19T00:46:52.846Z</v>
       </c>
       <c r="N113" t="str">
         <v/>
@@ -6390,7 +6390,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>BC.Game</v>
+        <v>Wings Up</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J114" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K114" t="str">
         <v>none</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="str">
-        <v>2026-02-19T00:46:52.846Z</v>
+        <v>2026-02-19T00:46:32.115Z</v>
       </c>
       <c r="N114" t="str">
         <v/>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Wings Up</v>
+        <v>Lynn Vision</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="str">
-        <v>2026-02-19T00:46:32.115Z</v>
+        <v>2026-02-19T00:46:08.336Z</v>
       </c>
       <c r="N115" t="str">
         <v/>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Lynn Vision</v>
+        <v>Tricked</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J116" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K116" t="str">
         <v>none</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="str">
-        <v>2026-02-19T00:46:08.336Z</v>
+        <v>2026-02-19T00:45:42.234Z</v>
       </c>
       <c r="N116" t="str">
         <v/>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Tricked</v>
+        <v>3DMAX</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="str">
-        <v>2026-02-19T00:45:42.234Z</v>
+        <v>2026-02-19T00:39:02.710Z</v>
       </c>
       <c r="N117" t="str">
         <v/>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3DMAX</v>
+        <v>Venom</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J118" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K118" t="str">
         <v>none</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="str">
-        <v>2026-02-19T00:39:02.710Z</v>
+        <v>2026-02-19T00:38:39.010Z</v>
       </c>
       <c r="N118" t="str">
         <v/>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Venom</v>
+        <v>ARCRED</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J119" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K119" t="str">
         <v>none</v>
@@ -6691,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="str">
-        <v>2026-02-19T00:38:39.010Z</v>
+        <v>2026-02-19T00:38:03.598Z</v>
       </c>
       <c r="N119" t="str">
         <v/>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ARCRED</v>
+        <v>GamerLegion</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J120" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K120" t="str">
         <v>none</v>
@@ -6744,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="str">
-        <v>2026-02-19T00:38:03.598Z</v>
+        <v>2026-02-19T00:37:47.172Z</v>
       </c>
       <c r="N120" t="str">
         <v/>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>GamerLegion</v>
+        <v>Passion UA</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J121" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K121" t="str">
         <v>none</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="str">
-        <v>2026-02-19T00:37:47.172Z</v>
+        <v>2026-02-19T00:37:27.234Z</v>
       </c>
       <c r="N121" t="str">
         <v/>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Passion UA</v>
+        <v>FlyQuest</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J122" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K122" t="str">
         <v>none</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="str">
-        <v>2026-02-19T00:37:27.234Z</v>
+        <v>2026-02-19T00:37:20.280Z</v>
       </c>
       <c r="N122" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>FlyQuest</v>
+        <v>Envy</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J123" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K123" t="str">
         <v>none</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="str">
-        <v>2026-02-19T00:37:20.280Z</v>
+        <v>2026-02-19T00:37:05.560Z</v>
       </c>
       <c r="N123" t="str">
         <v/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Envy</v>
+        <v>BIG</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="str">
-        <v>2026-02-19T00:37:05.560Z</v>
+        <v>2026-02-19T00:36:43.463Z</v>
       </c>
       <c r="N124" t="str">
         <v/>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>BIG</v>
+        <v>Limitless</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="str">
-        <v>2026-02-19T00:36:43.463Z</v>
+        <v>2026-02-19T00:36:26.343Z</v>
       </c>
       <c r="N125" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Limitless</v>
+        <v>Galorys</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J126" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K126" t="str">
         <v>none</v>
@@ -7062,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="str">
-        <v>2026-02-19T00:36:26.343Z</v>
+        <v>2026-02-19T00:36:18.696Z</v>
       </c>
       <c r="N126" t="str">
         <v/>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Galorys</v>
+        <v>devils.one</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J127" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K127" t="str">
         <v>none</v>
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="str">
-        <v>2026-02-19T00:36:18.696Z</v>
+        <v>2026-02-18T21:23:30.347Z</v>
       </c>
       <c r="N127" t="str">
         <v/>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>devils.one</v>
+        <v>Luminosity</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -7159,7 +7159,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J128" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K128" t="str">
         <v>none</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="str">
-        <v>2026-02-18T21:23:30.347Z</v>
+        <v>2026-02-18T21:23:18.851Z</v>
       </c>
       <c r="N128" t="str">
         <v/>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Luminosity</v>
+        <v>Sharks</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J129" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K129" t="str">
         <v>none</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="str">
-        <v>2026-02-18T21:23:18.851Z</v>
+        <v>2026-02-18T21:23:12.952Z</v>
       </c>
       <c r="N129" t="str">
         <v/>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Sharks</v>
+        <v>IHC</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J130" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K130" t="str">
         <v>none</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="str">
-        <v>2026-02-18T21:23:12.952Z</v>
+        <v>2026-02-18T21:23:06.529Z</v>
       </c>
       <c r="N130" t="str">
         <v/>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>IHC</v>
+        <v>Kappa Bar</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J131" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K131" t="str">
         <v>none</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="str">
-        <v>2026-02-18T21:23:06.529Z</v>
+        <v>2026-02-18T21:22:57.244Z</v>
       </c>
       <c r="N131" t="str">
         <v/>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Kappa Bar</v>
+        <v>Complexity</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J132" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K132" t="str">
         <v>none</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="str">
-        <v>2026-02-18T21:22:57.244Z</v>
+        <v>2026-02-18T21:22:48.652Z</v>
       </c>
       <c r="N132" t="str">
         <v/>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Complexity</v>
+        <v>Case</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -7424,7 +7424,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J133" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K133" t="str">
         <v>none</v>
@@ -7433,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="str">
-        <v>2026-02-18T21:22:48.652Z</v>
+        <v>2026-02-18T21:22:39.402Z</v>
       </c>
       <c r="N133" t="str">
         <v/>
@@ -7450,7 +7450,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Case</v>
+        <v>Enemy</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="str">
-        <v>2026-02-18T21:22:39.402Z</v>
+        <v>2026-02-18T21:22:20.745Z</v>
       </c>
       <c r="N134" t="str">
         <v/>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Enemy</v>
+        <v>KRU</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -7530,7 +7530,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J135" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K135" t="str">
         <v>none</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="str">
-        <v>2026-02-18T21:22:20.745Z</v>
+        <v>2026-02-18T21:22:06.663Z</v>
       </c>
       <c r="N135" t="str">
         <v/>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>KRU</v>
+        <v>Imperial</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="str">
-        <v>2026-02-18T21:22:06.663Z</v>
+        <v>2026-02-18T21:21:57.658Z</v>
       </c>
       <c r="N136" t="str">
         <v/>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Imperial</v>
+        <v>paiN</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="str">
-        <v>2026-02-18T21:21:57.658Z</v>
+        <v>2026-02-18T21:21:14.058Z</v>
       </c>
       <c r="N137" t="str">
         <v/>
@@ -7662,7 +7662,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>paiN</v>
+        <v>Vexed</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J138" t="str">
-        <v>AM</v>
+        <v>EU</v>
       </c>
       <c r="K138" t="str">
         <v>none</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="str">
-        <v>2026-02-18T21:21:14.058Z</v>
+        <v>2026-02-18T21:19:58.722Z</v>
       </c>
       <c r="N138" t="str">
         <v/>
@@ -7715,19 +7715,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Vexed</v>
+        <v>Dignitas</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139">
-        <v>985</v>
+        <v>984.7039370196626</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="str">
-        <v>2026-02-18T21:19:58.722Z</v>
+        <v>2026-02-19T21:54:17.535Z</v>
       </c>
       <c r="N139" t="str">
         <v/>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dignitas</v>
+        <v>LDLC</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="str">
-        <v>2026-02-19T21:54:17.535Z</v>
+        <v>2026-02-19T21:53:53.691Z</v>
       </c>
       <c r="N140" t="str">
         <v/>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>LDLC</v>
+        <v>Aravt</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="str">
-        <v>2026-02-19T21:53:53.691Z</v>
+        <v>2026-02-19T02:51:09.872Z</v>
       </c>
       <c r="N141" t="str">
         <v/>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Aravt</v>
+        <v>VP.Prodigy</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="str">
-        <v>2026-02-19T02:51:09.872Z</v>
+        <v>2026-02-19T02:51:03.784Z</v>
       </c>
       <c r="N142" t="str">
         <v/>
@@ -7927,7 +7927,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>VP.Prodigy</v>
+        <v>Underground</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="str">
-        <v>2026-02-19T02:51:03.784Z</v>
+        <v>2026-02-19T02:47:27.422Z</v>
       </c>
       <c r="N143" t="str">
         <v/>
@@ -7980,7 +7980,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Underground</v>
+        <v>Virtus.pro</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="str">
-        <v>2026-02-19T02:47:27.422Z</v>
+        <v>2026-02-19T02:47:19.575Z</v>
       </c>
       <c r="N144" t="str">
         <v/>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Virtus.pro</v>
+        <v>ShindeN</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="str">
-        <v>2026-02-19T02:47:19.575Z</v>
+        <v>2026-02-19T02:36:26.535Z</v>
       </c>
       <c r="N145" t="str">
         <v/>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ShindeN</v>
+        <v>Permitta</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="str">
-        <v>2026-02-19T02:36:26.535Z</v>
+        <v>2026-02-19T02:36:17.329Z</v>
       </c>
       <c r="N146" t="str">
         <v/>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Permitta</v>
+        <v>Wildcard</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -8166,7 +8166,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J147" t="str">
-        <v>EU</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K147" t="str">
         <v>none</v>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="str">
-        <v>2026-02-19T02:36:17.329Z</v>
+        <v>2026-02-19T02:34:08.116Z</v>
       </c>
       <c r="N147" t="str">
         <v/>
@@ -8192,7 +8192,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wildcard</v>
+        <v>Astralis</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -8219,7 +8219,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J148" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K148" t="str">
         <v>none</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="str">
-        <v>2026-02-19T02:34:08.116Z</v>
+        <v>2026-02-19T02:34:01.822Z</v>
       </c>
       <c r="N148" t="str">
         <v/>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Astralis</v>
+        <v>Bad News Eagles</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -8272,7 +8272,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J149" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K149" t="str">
         <v>none</v>
@@ -8281,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="str">
-        <v>2026-02-19T02:34:01.822Z</v>
+        <v>2026-02-19T01:45:27.335Z</v>
       </c>
       <c r="N149" t="str">
         <v/>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Bad News Eagles</v>
+        <v>SK</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -8325,7 +8325,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J150" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K150" t="str">
         <v>none</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="str">
-        <v>2026-02-19T01:45:27.335Z</v>
+        <v>2026-02-19T01:39:18.535Z</v>
       </c>
       <c r="N150" t="str">
         <v/>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SK</v>
+        <v>ECSTATIC</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -8378,7 +8378,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J151" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K151" t="str">
         <v>none</v>
@@ -8387,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="str">
-        <v>2026-02-19T01:39:18.535Z</v>
+        <v>2026-02-19T01:39:12.540Z</v>
       </c>
       <c r="N151" t="str">
         <v/>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ECSTATIC</v>
+        <v>MIBR Academy</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -8416,7 +8416,7 @@
         <v>2</v>
       </c>
       <c r="E152">
-        <v>984.7039370196626</v>
+        <v>984.075576101157</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J152" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K152" t="str">
         <v>none</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="str">
-        <v>2026-02-19T01:39:12.540Z</v>
+        <v>2026-06-26T13:19:31.639Z</v>
       </c>
       <c r="N152" t="str">
         <v/>
@@ -8457,19 +8457,19 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>MIBR Academy</v>
+        <v>TALON</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E153">
-        <v>984.075576101157</v>
+        <v>983.9905713816794</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J153" t="str">
-        <v>AM</v>
+        <v>AS/SIS/ESEA</v>
       </c>
       <c r="K153" t="str">
         <v>none</v>
@@ -8493,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="str">
-        <v>2026-06-26T13:19:31.639Z</v>
+        <v>2026-02-28T06:27:14.538Z</v>
       </c>
       <c r="N153" t="str">
         <v/>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>paiN Academy</v>
+        <v>B8</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -8522,7 +8522,7 @@
         <v>2</v>
       </c>
       <c r="E154">
-        <v>984.0732769617838</v>
+        <v>983.4284201175154</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="str">
-        <v>2026-07-07T04:08:50.601Z</v>
+        <v>2026-07-05T04:05:49.346Z</v>
       </c>
       <c r="N154" t="str">
         <v/>
@@ -8563,19 +8563,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>TALON</v>
+        <v>NAVI Junior</v>
       </c>
       <c r="B155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E155">
-        <v>983.9905713816794</v>
+        <v>983.2698348870488</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J155" t="str">
-        <v>AS/SIS/ESEA</v>
+        <v>EU</v>
       </c>
       <c r="K155" t="str">
         <v>none</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="str">
-        <v>2026-02-28T06:27:14.538Z</v>
+        <v>2026-02-28T06:27:03.939Z</v>
       </c>
       <c r="N155" t="str">
         <v/>
@@ -8616,19 +8616,19 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>B8</v>
+        <v>Legacy</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E156">
-        <v>983.4284201175154</v>
+        <v>976.9354856610739</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="str">
-        <v>2026-07-05T04:05:49.346Z</v>
+        <v>2026-07-23T22:02:02.134Z</v>
       </c>
       <c r="N156" t="str">
         <v/>
@@ -8669,19 +8669,19 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>NAVI Junior</v>
+        <v>9z</v>
       </c>
       <c r="B157">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E157">
-        <v>983.2698348870488</v>
+        <v>971.3809496889581</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>Tier 3</v>
       </c>
       <c r="J157" t="str">
-        <v>EU</v>
+        <v>AM</v>
       </c>
       <c r="K157" t="str">
         <v>none</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="str">
-        <v>2026-02-28T06:27:03.939Z</v>
+        <v>2026-07-05T04:07:15.376Z</v>
       </c>
       <c r="N157" t="str">
         <v/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>9z</v>
+        <v>paiN Academy</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -8734,7 +8734,7 @@
         <v>3</v>
       </c>
       <c r="E158">
-        <v>971.3809496889581</v>
+        <v>971.0310326935038</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="str">
-        <v>2026-07-05T04:07:15.376Z</v>
+        <v>2026-07-23T22:01:33.382Z</v>
       </c>
       <c r="N158" t="str">
         <v/>

--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_8827063F2148FD68F261021F3850A425A12DB200" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C389021-36EB-4BFD-849F-F009EB04BECF}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_8827063F2148FD68F261021F3850A425A12DB200" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{733C7BDC-4D67-4259-96B3-7A5D2178CC40}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1330,9 +1330,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q166"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
         <v>20</v>
@@ -1438,7 +1438,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>65</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>77</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>97</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>98</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>99</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>101</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>102</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>103</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>105</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>107</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>108</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>109</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>110</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>111</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>112</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>113</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>114</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>115</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>116</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>117</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>118</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>119</v>
       </c>
@@ -4936,7 +4936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>120</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>121</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>122</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>123</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>124</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>125</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>127</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>129</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>131</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>135</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>137</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>139</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>141</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>143</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>145</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>147</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>149</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>151</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>153</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>155</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>157</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>159</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>161</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>163</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>165</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>167</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>169</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>171</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>173</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>175</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>177</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>179</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>181</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>183</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>185</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>187</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>189</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>191</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>193</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>195</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>197</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>199</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>201</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>203</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>205</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>207</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>209</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>211</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>213</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>215</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>217</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>219</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>221</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>223</v>
       </c>
@@ -7851,7 +7851,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>225</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>227</v>
       </c>
@@ -7957,7 +7957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>229</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>231</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>233</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>235</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>237</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>239</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>241</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>243</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>245</v>
       </c>
@@ -8434,7 +8434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>247</v>
       </c>
@@ -8487,7 +8487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>249</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>251</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>253</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>255</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>257</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>259</v>
       </c>
@@ -8805,7 +8805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>261</v>
       </c>
@@ -8858,7 +8858,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>263</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>265</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>267</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>269</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>271</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>273</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>275</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>277</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>279</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>281</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>283</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>285</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>287</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>289</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>291</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>293</v>
       </c>
@@ -9706,7 +9706,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>295</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>297</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>299</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>301</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>303</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>305</v>
       </c>
@@ -10024,7 +10024,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="165" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>307</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>309</v>
       </c>
@@ -10133,7 +10133,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q1 A3:Q166 A2:E2 G2:Q2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q1 A3:Q166 A2:E2 G2:I2 K2:Q2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/file/old.xlsx
+++ b/file/old.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/faa3f9bfbb5dc780/Documentos/GitHub/ck-tools/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_8827063F2148FD68F261021F3850A425A12DB200" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{733C7BDC-4D67-4259-96B3-7A5D2178CC40}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_8827063FEF68FD417060021F3850A425A12DBD70" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F58D24EA-3271-4926-B42D-AB565CE69DBC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="327">
   <si>
     <t>Team</t>
   </si>
@@ -223,6 +223,102 @@
     <t>2026-02-18T21:21:06.168Z</t>
   </si>
   <si>
+    <t>MAD Lions</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:39:12.741Z</t>
+  </si>
+  <si>
+    <t>Fnatic</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:39:19.440Z</t>
+  </si>
+  <si>
+    <t>ENCE Academy</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:41:42.732Z</t>
+  </si>
+  <si>
+    <t>SKYFURY</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:41:55.808Z</t>
+  </si>
+  <si>
+    <t>BIG Academy</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:42:06.941Z</t>
+  </si>
+  <si>
+    <t>mousesports</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:42:44.510Z</t>
+  </si>
+  <si>
+    <t>Gambit</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:42:49.775Z</t>
+  </si>
+  <si>
+    <t>Wildcard Academy</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:42:58.796Z</t>
+  </si>
+  <si>
+    <t>VeryGames</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:43:07.819Z</t>
+  </si>
+  <si>
+    <t>Astana Dragons</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:43:19.675Z</t>
+  </si>
+  <si>
+    <t>Copenhagen Wolves</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:43:50.812Z</t>
+  </si>
+  <si>
+    <t>Misfits</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:43:58.246Z</t>
+  </si>
+  <si>
+    <t>Kinguin</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:44:09.112Z</t>
+  </si>
+  <si>
+    <t>Space Soldiers</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:44:15.749Z</t>
+  </si>
+  <si>
+    <t>Movistar KOI</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:44:22.588Z</t>
+  </si>
+  <si>
+    <t>Vox Eminor</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:44:28.360Z</t>
+  </si>
+  <si>
     <t>Onyx Ravens</t>
   </si>
   <si>
@@ -268,253 +364,205 @@
     <t>Take Flyte</t>
   </si>
   <si>
+    <t>Avangar</t>
+  </si>
+  <si>
+    <t>Bravado</t>
+  </si>
+  <si>
+    <t>FORZE</t>
+  </si>
+  <si>
+    <t>GATERON</t>
+  </si>
+  <si>
+    <t>Hesta</t>
+  </si>
+  <si>
+    <t>kONO</t>
+  </si>
+  <si>
+    <t>LGB</t>
+  </si>
+  <si>
+    <t>Rogue</t>
+  </si>
+  <si>
+    <t>Shika</t>
+  </si>
+  <si>
+    <t>Tsunami</t>
+  </si>
+  <si>
+    <t>Lux Tenebris</t>
+  </si>
+  <si>
+    <t>Spirit Academy</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:49:35.870Z</t>
+  </si>
+  <si>
+    <t>True Rippers</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:47:38.886Z</t>
+  </si>
+  <si>
+    <t>FaZe</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:36:39.932Z</t>
+  </si>
+  <si>
+    <t>iBUYPOWER</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:36:34.302Z</t>
+  </si>
+  <si>
+    <t>GODSENT</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:39:32.364Z</t>
+  </si>
+  <si>
+    <t>M80</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:45:45.455Z</t>
+  </si>
+  <si>
+    <t>Chinggis Warriors</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:08:18.806Z</t>
+  </si>
+  <si>
+    <t>Orbit</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:08:33.993Z</t>
+  </si>
+  <si>
+    <t>Alliance</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:51:22.336Z</t>
+  </si>
+  <si>
+    <t>Homyno</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:51:16.607Z</t>
+  </si>
+  <si>
+    <t>MenaceGG</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:49:44.165Z</t>
+  </si>
+  <si>
+    <t>Solid</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:47:50.233Z</t>
+  </si>
+  <si>
+    <t>ENCE</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:34:19.604Z</t>
+  </si>
+  <si>
+    <t>Nexus</t>
+  </si>
+  <si>
+    <t>2026-02-19T02:34:13.227Z</t>
+  </si>
+  <si>
+    <t>MIBR</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:39:50.018Z</t>
+  </si>
+  <si>
+    <t>Wizards</t>
+  </si>
+  <si>
+    <t>2026-02-19T01:45:38.841Z</t>
+  </si>
+  <si>
+    <t>RED Canids</t>
+  </si>
+  <si>
+    <t>2026-02-19T22:08:44.661Z</t>
+  </si>
+  <si>
+    <t>Rebels</t>
+  </si>
+  <si>
+    <t>2026-02-28T06:28:39.554Z</t>
+  </si>
+  <si>
+    <t>Into the Beach</t>
+  </si>
+  <si>
+    <t>2026-07-23T22:12:51.919Z</t>
+  </si>
+  <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>2026-07-23T22:00:15.992Z</t>
+  </si>
+  <si>
+    <t>GhoulsW</t>
+  </si>
+  <si>
+    <t>HAVU</t>
+  </si>
+  <si>
+    <t>FLuffy Gangsters</t>
+  </si>
+  <si>
+    <t>Flash</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
     <t>00 Nation</t>
   </si>
   <si>
+    <t>Quantum Bellator Fire</t>
+  </si>
+  <si>
+    <t>Astralis Talent</t>
+  </si>
+  <si>
+    <t>Nordix</t>
+  </si>
+  <si>
+    <t>NOVAQ</t>
+  </si>
+  <si>
+    <t>QMISTRY</t>
+  </si>
+  <si>
+    <t>MOUZ NXT</t>
+  </si>
+  <si>
+    <t>FlyQuest RED</t>
+  </si>
+  <si>
     <t>100 Thieves</t>
   </si>
   <si>
-    <t>Astana Dragons</t>
-  </si>
-  <si>
-    <t>Astralis Talent</t>
-  </si>
-  <si>
-    <t>Avangar</t>
-  </si>
-  <si>
-    <t>BIG Academy</t>
-  </si>
-  <si>
-    <t>Bravado</t>
-  </si>
-  <si>
-    <t>Copenhagen Wolves</t>
-  </si>
-  <si>
-    <t>ENCE Academy</t>
-  </si>
-  <si>
-    <t>ESC</t>
-  </si>
-  <si>
-    <t>Flash</t>
-  </si>
-  <si>
-    <t>FLuffy Gangsters</t>
-  </si>
-  <si>
-    <t>FlyQuest RED</t>
-  </si>
-  <si>
-    <t>Fnatic</t>
-  </si>
-  <si>
-    <t>FORZE</t>
-  </si>
-  <si>
-    <t>Gambit</t>
-  </si>
-  <si>
-    <t>GATERON</t>
-  </si>
-  <si>
-    <t>GhoulsW</t>
-  </si>
-  <si>
-    <t>HAVU</t>
+    <t>NIP Impact</t>
   </si>
   <si>
     <t>Heroic Academy</t>
-  </si>
-  <si>
-    <t>Hesta</t>
-  </si>
-  <si>
-    <t>Kinguin</t>
-  </si>
-  <si>
-    <t>kONO</t>
-  </si>
-  <si>
-    <t>LGB</t>
-  </si>
-  <si>
-    <t>MAD Lions</t>
-  </si>
-  <si>
-    <t>Misfits</t>
-  </si>
-  <si>
-    <t>mousesports</t>
-  </si>
-  <si>
-    <t>MOUZ NXT</t>
-  </si>
-  <si>
-    <t>Movistar KOI</t>
-  </si>
-  <si>
-    <t>NIP Impact</t>
-  </si>
-  <si>
-    <t>Nordix</t>
-  </si>
-  <si>
-    <t>NOVAQ</t>
-  </si>
-  <si>
-    <t>QMISTRY</t>
-  </si>
-  <si>
-    <t>Quantum Bellator Fire</t>
-  </si>
-  <si>
-    <t>Rogue</t>
-  </si>
-  <si>
-    <t>Shika</t>
-  </si>
-  <si>
-    <t>SKYFURY</t>
-  </si>
-  <si>
-    <t>Space Soldiers</t>
-  </si>
-  <si>
-    <t>Tsunami</t>
-  </si>
-  <si>
-    <t>VeryGames</t>
-  </si>
-  <si>
-    <t>Vox Eminor</t>
-  </si>
-  <si>
-    <t>Wildcard Academy</t>
-  </si>
-  <si>
-    <t>Lux Tenebris</t>
-  </si>
-  <si>
-    <t>Spirit Academy</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:49:35.870Z</t>
-  </si>
-  <si>
-    <t>True Rippers</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:47:38.886Z</t>
-  </si>
-  <si>
-    <t>FaZe</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:36:39.932Z</t>
-  </si>
-  <si>
-    <t>iBUYPOWER</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:36:34.302Z</t>
-  </si>
-  <si>
-    <t>GODSENT</t>
-  </si>
-  <si>
-    <t>2026-02-19T01:39:32.364Z</t>
-  </si>
-  <si>
-    <t>M80</t>
-  </si>
-  <si>
-    <t>2026-02-19T01:45:45.455Z</t>
-  </si>
-  <si>
-    <t>Chinggis Warriors</t>
-  </si>
-  <si>
-    <t>2026-02-19T22:08:18.806Z</t>
-  </si>
-  <si>
-    <t>Orbit</t>
-  </si>
-  <si>
-    <t>2026-02-19T22:08:33.993Z</t>
-  </si>
-  <si>
-    <t>Alliance</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:51:22.336Z</t>
-  </si>
-  <si>
-    <t>Homyno</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:51:16.607Z</t>
-  </si>
-  <si>
-    <t>MenaceGG</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:49:44.165Z</t>
-  </si>
-  <si>
-    <t>Solid</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:47:50.233Z</t>
-  </si>
-  <si>
-    <t>ENCE</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:34:19.604Z</t>
-  </si>
-  <si>
-    <t>Nexus</t>
-  </si>
-  <si>
-    <t>2026-02-19T02:34:13.227Z</t>
-  </si>
-  <si>
-    <t>MIBR</t>
-  </si>
-  <si>
-    <t>2026-02-19T01:39:50.018Z</t>
-  </si>
-  <si>
-    <t>Wizards</t>
-  </si>
-  <si>
-    <t>2026-02-19T01:45:38.841Z</t>
-  </si>
-  <si>
-    <t>RED Canids</t>
-  </si>
-  <si>
-    <t>2026-02-19T22:08:44.661Z</t>
-  </si>
-  <si>
-    <t>Rebels</t>
-  </si>
-  <si>
-    <t>2026-02-28T06:28:39.554Z</t>
-  </si>
-  <si>
-    <t>Into the Beach</t>
-  </si>
-  <si>
-    <t>2026-07-23T22:12:51.919Z</t>
-  </si>
-  <si>
-    <t>Mythic</t>
-  </si>
-  <si>
-    <t>2026-07-23T22:00:15.992Z</t>
   </si>
   <si>
     <t>ad hoc</t>
@@ -1005,6 +1053,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2503,16 +2555,16 @@
         <v>67</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1014.9877256835035</v>
+        <v>1015</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2527,7 +2579,7 @@
         <v>31</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K23" t="s">
         <v>25</v>
@@ -2556,16 +2608,16 @@
         <v>69</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>1014.6510123894305</v>
+        <v>1015</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2580,7 +2632,7 @@
         <v>31</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K24" t="s">
         <v>25</v>
@@ -2609,16 +2661,16 @@
         <v>71</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1014.1287422856431</v>
+        <v>1015</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2633,7 +2685,7 @@
         <v>31</v>
       </c>
       <c r="J25" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K25" t="s">
         <v>25</v>
@@ -2662,16 +2714,16 @@
         <v>73</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>1013.5266895185538</v>
+        <v>1015</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2715,16 +2767,16 @@
         <v>75</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1005.0046329623956</v>
+        <v>1015</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2739,7 +2791,7 @@
         <v>31</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K27" t="s">
         <v>25</v>
@@ -2768,16 +2820,16 @@
         <v>77</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>1002.6421965170028</v>
+        <v>1015</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2821,16 +2873,16 @@
         <v>79</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>1000.4888979238718</v>
+        <v>1015</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2874,16 +2926,16 @@
         <v>81</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1000.3086743488057</v>
+        <v>1015</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2898,7 +2950,7 @@
         <v>31</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K30" t="s">
         <v>25</v>
@@ -2907,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="N30" t="s">
         <v>22</v>
@@ -2924,19 +2976,19 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2960,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="N31" t="s">
         <v>22</v>
@@ -2977,19 +3029,19 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -3013,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="N32" t="s">
         <v>22</v>
@@ -3030,19 +3082,19 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3066,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="N33" t="s">
         <v>22</v>
@@ -3083,19 +3135,19 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -3119,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="N34" t="s">
         <v>22</v>
@@ -3136,19 +3188,19 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3163,7 +3215,7 @@
         <v>31</v>
       </c>
       <c r="J35" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K35" t="s">
         <v>25</v>
@@ -3172,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="N35" t="s">
         <v>22</v>
@@ -3189,19 +3241,19 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -3225,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="N36" t="s">
         <v>22</v>
@@ -3242,19 +3294,19 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -3269,7 +3321,7 @@
         <v>31</v>
       </c>
       <c r="J37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K37" t="s">
         <v>25</v>
@@ -3278,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="N37" t="s">
         <v>22</v>
@@ -3295,19 +3347,19 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3331,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="N38" t="s">
         <v>22</v>
@@ -3348,19 +3400,19 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E39">
-        <v>1000</v>
+        <v>1014.9877256835035</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -3375,7 +3427,7 @@
         <v>31</v>
       </c>
       <c r="J39" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s">
         <v>25</v>
@@ -3384,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="N39" t="s">
         <v>22</v>
@@ -3401,19 +3453,19 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>1000</v>
+        <v>1014.6510123894305</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -3428,7 +3480,7 @@
         <v>31</v>
       </c>
       <c r="J40" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s">
         <v>25</v>
@@ -3437,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="N40" t="s">
         <v>22</v>
@@ -3454,19 +3506,19 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>1000</v>
+        <v>1014.1287422856431</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -3481,7 +3533,7 @@
         <v>31</v>
       </c>
       <c r="J41" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K41" t="s">
         <v>25</v>
@@ -3490,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="N41" t="s">
         <v>22</v>
@@ -3507,19 +3559,19 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>1000</v>
+        <v>1013.5266895185538</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -3543,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="N42" t="s">
         <v>22</v>
@@ -3560,19 +3612,19 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>1000</v>
+        <v>1005.0046329623956</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -3587,7 +3639,7 @@
         <v>31</v>
       </c>
       <c r="J43" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s">
         <v>25</v>
@@ -3596,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="N43" t="s">
         <v>22</v>
@@ -3613,19 +3665,19 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>1000</v>
+        <v>1002.6421965170028</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -3649,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="N44" t="s">
         <v>22</v>
@@ -3666,19 +3718,19 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>1000</v>
+        <v>1000.4888979238718</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3693,7 +3745,7 @@
         <v>31</v>
       </c>
       <c r="J45" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K45" t="s">
         <v>25</v>
@@ -3702,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="N45" t="s">
         <v>22</v>
@@ -3719,19 +3771,19 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>1000</v>
+        <v>1000.3086743488057</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3746,7 +3798,7 @@
         <v>31</v>
       </c>
       <c r="J46" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s">
         <v>25</v>
@@ -3755,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="N46" t="s">
         <v>22</v>
@@ -3772,7 +3824,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3825,7 +3877,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3852,7 +3904,7 @@
         <v>31</v>
       </c>
       <c r="J48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K48" t="s">
         <v>25</v>
@@ -3878,7 +3930,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3905,7 +3957,7 @@
         <v>31</v>
       </c>
       <c r="J49" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K49" t="s">
         <v>25</v>
@@ -3931,7 +3983,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3958,7 +4010,7 @@
         <v>31</v>
       </c>
       <c r="J50" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K50" t="s">
         <v>25</v>
@@ -3984,7 +4036,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4037,7 +4089,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4064,7 +4116,7 @@
         <v>31</v>
       </c>
       <c r="J52" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K52" t="s">
         <v>25</v>
@@ -4090,7 +4142,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4143,7 +4195,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4196,7 +4248,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -4223,7 +4275,7 @@
         <v>31</v>
       </c>
       <c r="J55" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K55" t="s">
         <v>25</v>
@@ -4249,7 +4301,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -4302,7 +4354,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -4329,7 +4381,7 @@
         <v>31</v>
       </c>
       <c r="J57" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K57" t="s">
         <v>25</v>
@@ -4355,19 +4407,19 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>1000</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -4382,7 +4434,7 @@
         <v>31</v>
       </c>
       <c r="J58" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K58" t="s">
         <v>25</v>
@@ -4391,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="N58" t="s">
         <v>22</v>
@@ -4408,19 +4460,19 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E59">
-        <v>1000</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -4444,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="N59" t="s">
         <v>22</v>
@@ -4461,19 +4513,19 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>1000</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4497,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="N60" t="s">
         <v>22</v>
@@ -4514,19 +4566,19 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>1000</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -4550,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="N61" t="s">
         <v>22</v>
@@ -4567,19 +4619,19 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>1000</v>
+        <v>999.72518097723059</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4594,7 +4646,7 @@
         <v>31</v>
       </c>
       <c r="J62" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K62" t="s">
         <v>25</v>
@@ -4603,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="N62" t="s">
         <v>22</v>
@@ -4620,19 +4672,19 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>1000</v>
+        <v>999.67234054451899</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -4647,7 +4699,7 @@
         <v>31</v>
       </c>
       <c r="J63" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K63" t="s">
         <v>25</v>
@@ -4656,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="N63" t="s">
         <v>22</v>
@@ -4673,19 +4725,19 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>1000</v>
+        <v>999.44081947176187</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -4700,7 +4752,7 @@
         <v>31</v>
       </c>
       <c r="J64" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K64" t="s">
         <v>25</v>
@@ -4709,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="N64" t="s">
         <v>22</v>
@@ -4726,19 +4778,19 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>1000</v>
+        <v>999.41869453766435</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -4753,7 +4805,7 @@
         <v>31</v>
       </c>
       <c r="J65" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K65" t="s">
         <v>25</v>
@@ -4762,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="N65" t="s">
         <v>22</v>
@@ -4779,19 +4831,19 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>1000</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4806,7 +4858,7 @@
         <v>31</v>
       </c>
       <c r="J66" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K66" t="s">
         <v>25</v>
@@ -4815,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="N66" t="s">
         <v>22</v>
@@ -4832,19 +4884,19 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67">
-        <v>1000</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4859,7 +4911,7 @@
         <v>31</v>
       </c>
       <c r="J67" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K67" t="s">
         <v>25</v>
@@ -4868,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="N67" t="s">
         <v>22</v>
@@ -4885,19 +4937,19 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>1000</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -4921,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="N68" t="s">
         <v>22</v>
@@ -4938,19 +4990,19 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>1000</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4965,7 +5017,7 @@
         <v>31</v>
       </c>
       <c r="J69" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K69" t="s">
         <v>25</v>
@@ -4974,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="N69" t="s">
         <v>22</v>
@@ -4991,19 +5043,19 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>1000</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -5027,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="N70" t="s">
         <v>22</v>
@@ -5044,19 +5096,19 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71">
-        <v>1000</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -5080,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="N71" t="s">
         <v>22</v>
@@ -5097,19 +5149,19 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>1000</v>
+        <v>999.40885151865234</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -5124,7 +5176,7 @@
         <v>31</v>
       </c>
       <c r="J72" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K72" t="s">
         <v>25</v>
@@ -5133,7 +5185,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="s">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="N72" t="s">
         <v>22</v>
@@ -5150,19 +5202,19 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>1000</v>
+        <v>999.40625216951082</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -5186,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="N73" t="s">
         <v>22</v>
@@ -5203,19 +5255,19 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74">
-        <v>999.72518097723059</v>
+        <v>999.33977453974444</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -5230,7 +5282,7 @@
         <v>31</v>
       </c>
       <c r="J74" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K74" t="s">
         <v>25</v>
@@ -5239,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="N74" t="s">
         <v>22</v>
@@ -5256,19 +5308,19 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E75">
-        <v>999.72518097723059</v>
+        <v>999.32326828427472</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -5292,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="N75" t="s">
         <v>22</v>
@@ -5309,7 +5361,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -5321,7 +5373,7 @@
         <v>2</v>
       </c>
       <c r="E76">
-        <v>999.72518097723059</v>
+        <v>996.09049181730393</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5336,7 +5388,7 @@
         <v>31</v>
       </c>
       <c r="J76" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K76" t="s">
         <v>25</v>
@@ -5345,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="N76" t="s">
         <v>22</v>
@@ -5362,7 +5414,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -5371,10 +5423,10 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>999.72518097723059</v>
+        <v>986.29487668745082</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -5389,7 +5441,7 @@
         <v>31</v>
       </c>
       <c r="J77" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K77" t="s">
         <v>25</v>
@@ -5398,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="N77" t="s">
         <v>22</v>
@@ -5415,19 +5467,19 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>999.72518097723059</v>
+        <v>985</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -5442,7 +5494,7 @@
         <v>31</v>
       </c>
       <c r="J78" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K78" t="s">
         <v>25</v>
@@ -5451,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="N78" t="s">
         <v>22</v>
@@ -5468,19 +5520,19 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>999.67234054451899</v>
+        <v>985</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -5495,7 +5547,7 @@
         <v>31</v>
       </c>
       <c r="J79" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K79" t="s">
         <v>25</v>
@@ -5504,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="N79" t="s">
         <v>22</v>
@@ -5521,19 +5573,19 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>999.44081947176187</v>
+        <v>985</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5548,7 +5600,7 @@
         <v>31</v>
       </c>
       <c r="J80" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K80" t="s">
         <v>25</v>
@@ -5557,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="N80" t="s">
         <v>22</v>
@@ -5574,19 +5626,19 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>999.41869453766435</v>
+        <v>985</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -5610,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="N81" t="s">
         <v>22</v>
@@ -5627,19 +5679,19 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>999.40885151865234</v>
+        <v>985</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -5663,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="N82" t="s">
         <v>22</v>
@@ -5680,19 +5732,19 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>999.40885151865234</v>
+        <v>985</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -5707,7 +5759,7 @@
         <v>31</v>
       </c>
       <c r="J83" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K83" t="s">
         <v>25</v>
@@ -5716,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="N83" t="s">
         <v>22</v>
@@ -5733,19 +5785,19 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>999.40885151865234</v>
+        <v>985</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -5769,7 +5821,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="N84" t="s">
         <v>22</v>
@@ -5786,19 +5838,19 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>999.40885151865234</v>
+        <v>985</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5813,7 +5865,7 @@
         <v>31</v>
       </c>
       <c r="J85" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K85" t="s">
         <v>25</v>
@@ -5822,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="N85" t="s">
         <v>22</v>
@@ -5839,19 +5891,19 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>999.40885151865234</v>
+        <v>985</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -5875,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="N86" t="s">
         <v>22</v>
@@ -5892,19 +5944,19 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>999.40885151865234</v>
+        <v>985</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -5928,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="N87" t="s">
         <v>22</v>
@@ -5945,19 +5997,19 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>999.40885151865234</v>
+        <v>985</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -5972,7 +6024,7 @@
         <v>31</v>
       </c>
       <c r="J88" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K88" t="s">
         <v>25</v>
@@ -5981,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="N88" t="s">
         <v>22</v>
@@ -5998,19 +6050,19 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>999.40625216951082</v>
+        <v>985</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -6025,7 +6077,7 @@
         <v>31</v>
       </c>
       <c r="J89" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K89" t="s">
         <v>25</v>
@@ -6034,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="N89" t="s">
         <v>22</v>
@@ -6051,19 +6103,19 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>999.33977453974444</v>
+        <v>985</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -6078,7 +6130,7 @@
         <v>31</v>
       </c>
       <c r="J90" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K90" t="s">
         <v>25</v>
@@ -6087,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="N90" t="s">
         <v>22</v>
@@ -6104,19 +6156,19 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91">
-        <v>999.32326828427472</v>
+        <v>985</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -6140,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="N91" t="s">
         <v>22</v>
@@ -6157,19 +6209,19 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92">
-        <v>996.09049181730393</v>
+        <v>985</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6184,7 +6236,7 @@
         <v>31</v>
       </c>
       <c r="J92" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K92" t="s">
         <v>25</v>
@@ -6193,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="N92" t="s">
         <v>22</v>
@@ -6210,19 +6262,19 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>986.29487668745082</v>
+        <v>985</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -6237,7 +6289,7 @@
         <v>31</v>
       </c>
       <c r="J93" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K93" t="s">
         <v>25</v>
@@ -6246,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="N93" t="s">
         <v>22</v>
@@ -6263,7 +6315,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -6299,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="N94" t="s">
         <v>22</v>
@@ -6316,7 +6368,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -6352,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="N95" t="s">
         <v>22</v>
@@ -6369,7 +6421,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -6405,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="N96" t="s">
         <v>22</v>
@@ -6422,7 +6474,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -6458,7 +6510,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="N97" t="s">
         <v>22</v>
@@ -6475,7 +6527,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -6511,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="N98" t="s">
         <v>22</v>
@@ -6528,7 +6580,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -6564,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="N99" t="s">
         <v>22</v>
@@ -6581,7 +6633,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -6617,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N100" t="s">
         <v>22</v>
@@ -6634,7 +6686,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -6670,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="N101" t="s">
         <v>22</v>
@@ -6687,7 +6739,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -6723,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="N102" t="s">
         <v>22</v>
@@ -6740,7 +6792,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -6776,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="N103" t="s">
         <v>22</v>
@@ -6793,7 +6845,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -6829,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="N104" t="s">
         <v>22</v>
@@ -6846,7 +6898,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -6882,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="N105" t="s">
         <v>22</v>
@@ -6899,7 +6951,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -6935,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="N106" t="s">
         <v>22</v>
@@ -6952,7 +7004,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -6988,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="N107" t="s">
         <v>22</v>
@@ -7005,7 +7057,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -7041,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="N108" t="s">
         <v>22</v>
@@ -7058,7 +7110,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -7094,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="N109" t="s">
         <v>22</v>
@@ -7111,7 +7163,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -7147,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="N110" t="s">
         <v>22</v>
@@ -7164,7 +7216,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -7200,7 +7252,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N111" t="s">
         <v>22</v>
@@ -7217,7 +7269,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -7253,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="N112" t="s">
         <v>22</v>
@@ -7270,7 +7322,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -7306,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="N113" t="s">
         <v>22</v>
@@ -7323,7 +7375,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -7359,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="N114" t="s">
         <v>22</v>
@@ -7376,7 +7428,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -7412,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="N115" t="s">
         <v>22</v>
@@ -7429,7 +7481,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -7465,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="N116" t="s">
         <v>22</v>
@@ -7482,7 +7534,7 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -7518,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="N117" t="s">
         <v>22</v>
@@ -7535,7 +7587,7 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -7571,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="N118" t="s">
         <v>22</v>
@@ -7588,7 +7640,7 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -7624,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="N119" t="s">
         <v>22</v>
@@ -7641,7 +7693,7 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -7677,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="N120" t="s">
         <v>22</v>
@@ -7694,7 +7746,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -7730,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="N121" t="s">
         <v>22</v>
@@ -7747,7 +7799,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -7783,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
@@ -7800,7 +7852,7 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -7836,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
@@ -7853,7 +7905,7 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -7889,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
@@ -7906,7 +7958,7 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -7942,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="N125" t="s">
         <v>22</v>
@@ -7959,7 +8011,7 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -7995,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="N126" t="s">
         <v>22</v>
@@ -8012,7 +8064,7 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -8048,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="N127" t="s">
         <v>22</v>
@@ -8065,7 +8117,7 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -8101,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="N128" t="s">
         <v>22</v>
@@ -8118,7 +8170,7 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8154,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="N129" t="s">
         <v>22</v>
@@ -8171,7 +8223,7 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8207,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="N130" t="s">
         <v>22</v>
@@ -8224,7 +8276,7 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8260,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="N131" t="s">
         <v>22</v>
@@ -8277,7 +8329,7 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8313,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="N132" t="s">
         <v>22</v>
@@ -8330,7 +8382,7 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8366,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="N133" t="s">
         <v>22</v>
@@ -8383,7 +8435,7 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8419,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
@@ -8436,7 +8488,7 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8472,7 +8524,7 @@
         <v>0</v>
       </c>
       <c r="M135" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
@@ -8489,7 +8541,7 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8525,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
@@ -8542,7 +8594,7 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8578,7 +8630,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="N137" t="s">
         <v>22</v>
@@ -8595,7 +8647,7 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8631,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="N138" t="s">
         <v>22</v>
@@ -8648,7 +8700,7 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -8684,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="N139" t="s">
         <v>22</v>
@@ -8701,7 +8753,7 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -8737,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="N140" t="s">
         <v>22</v>
@@ -8754,7 +8806,7 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -8790,7 +8842,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="N141" t="s">
         <v>22</v>
@@ -8807,7 +8859,7 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -8843,7 +8895,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="N142" t="s">
         <v>22</v>
@@ -8860,7 +8912,7 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -8896,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="N143" t="s">
         <v>22</v>
@@ -8913,7 +8965,7 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -8949,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="N144" t="s">
         <v>22</v>
@@ -8966,7 +9018,7 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -9002,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="N145" t="s">
         <v>22</v>
@@ -9019,7 +9071,7 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -9055,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="M146" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="N146" t="s">
         <v>22</v>
@@ -9072,7 +9124,7 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -9108,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="N147" t="s">
         <v>22</v>
@@ -9125,7 +9177,7 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -9161,7 +9213,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="N148" t="s">
         <v>22</v>
@@ -9178,7 +9230,7 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -9214,7 +9266,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="N149" t="s">
         <v>22</v>
@@ -9231,7 +9283,7 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -9267,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="N150" t="s">
         <v>22</v>
@@ -9284,7 +9336,7 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -9320,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="N151" t="s">
         <v>22</v>
@@ -9337,7 +9389,7 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -9373,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="M152" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="N152" t="s">
         <v>22</v>
@@ -9390,7 +9442,7 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B153">
         <v>4</v>
@@ -9426,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="M153" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="N153" t="s">
         <v>22</v>
@@ -9443,7 +9495,7 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -9479,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="N154" t="s">
         <v>22</v>
@@ -9496,7 +9548,7 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B155">
         <v>5</v>
@@ -9532,7 +9584,7 @@
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="N155" t="s">
         <v>22</v>
@@ -9549,7 +9601,7 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B156">
         <v>2</v>
@@ -9585,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="M156" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="N156" t="s">
         <v>22</v>
@@ -9602,7 +9654,7 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -9638,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="N157" t="s">
         <v>22</v>
@@ -9655,7 +9707,7 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -9691,7 +9743,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="N158" t="s">
         <v>22</v>
@@ -9708,7 +9760,7 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -9744,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="M159" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="N159" t="s">
         <v>22</v>
@@ -9761,7 +9813,7 @@
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -9797,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="N160" t="s">
         <v>22</v>
@@ -9814,7 +9866,7 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -9850,7 +9902,7 @@
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="N161" t="s">
         <v>22</v>
@@ -9867,7 +9919,7 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -9903,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="M162" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="N162" t="s">
         <v>22</v>
@@ -9920,7 +9972,7 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -9956,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="N163" t="s">
         <v>22</v>
@@ -9973,7 +10025,7 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -10009,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="M164" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="N164" t="s">
         <v>22</v>
@@ -10026,7 +10078,7 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -10062,7 +10114,7 @@
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="N165" t="s">
         <v>22</v>
@@ -10079,7 +10131,7 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -10115,7 +10167,7 @@
         <v>0</v>
       </c>
       <c r="M166" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="N166" t="s">
         <v>22</v>
